--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -88,244 +88,244 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L13</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>A_L30</t>
+  </si>
+  <si>
+    <t>B_L17</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
     <t>C_L02</t>
   </si>
   <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L17</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>X_L99</t>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L28</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L04</t>
   </si>
   <si>
     <t>A_L28</t>
   </si>
   <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>C_L28</t>
   </si>
   <si>
     <t>A_L05</t>
   </si>
   <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>A_L30</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L16</t>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L11</t>
   </si>
   <si>
     <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L28</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L13</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L23</t>
   </si>
   <si>
     <t>C</t>
@@ -780,49 +780,49 @@
         <v>104</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S2">
         <v>6</v>
@@ -875,28 +875,28 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3">
         <v>6</v>
@@ -928,49 +928,49 @@
         <v>105</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -1002,49 +1002,49 @@
         <v>105</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S5">
         <v>6</v>
@@ -1150,49 +1150,49 @@
         <v>106</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P7">
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -1224,49 +1224,49 @@
         <v>106</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8">
         <v>6</v>
@@ -1298,49 +1298,49 @@
         <v>105</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1372,31 +1372,31 @@
         <v>104</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1405,16 +1405,16 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>6</v>
@@ -1446,31 +1446,31 @@
         <v>104</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1482,13 +1482,13 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <v>6</v>
@@ -1544,16 +1544,16 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>4</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>5</v>
@@ -1615,28 +1615,28 @@
         <v>2</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S13">
         <v>6</v>
@@ -1668,37 +1668,37 @@
         <v>105</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <v>5</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1710,7 +1710,7 @@
         <v>5</v>
       </c>
       <c r="R14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S14">
         <v>6</v>
@@ -1763,28 +1763,28 @@
         <v>2</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>6</v>
@@ -1890,49 +1890,49 @@
         <v>105</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -1964,25 +1964,25 @@
         <v>104</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <v>4</v>
@@ -2038,49 +2038,49 @@
         <v>106</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>6</v>
@@ -2118,43 +2118,43 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2186,25 +2186,25 @@
         <v>105</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -2260,7 +2260,7 @@
         <v>105</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2272,7 +2272,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -2355,28 +2355,28 @@
         <v>1</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>6</v>
@@ -2408,49 +2408,49 @@
         <v>105</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>6</v>
@@ -2482,46 +2482,46 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S25">
         <v>6</v>
@@ -2553,49 +2553,49 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
         <v>6</v>
@@ -2701,7 +2701,7 @@
         <v>105</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2710,40 +2710,40 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>6</v>
@@ -2775,49 +2775,49 @@
         <v>104</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>6</v>
@@ -2849,7 +2849,7 @@
         <v>105</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2858,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -2870,13 +2870,13 @@
         <v>1</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L30">
         <v>5</v>
       </c>
       <c r="M30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -2888,10 +2888,10 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>6</v>
@@ -2950,7 +2950,7 @@
         <v>5</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>4</v>
@@ -2959,13 +2959,13 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>6</v>
@@ -3000,10 +3000,10 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3015,31 +3015,31 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>6</v>
@@ -3166,28 +3166,28 @@
         <v>1</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>6</v>
@@ -3246,7 +3246,7 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>5</v>
@@ -3261,7 +3261,7 @@
         <v>4</v>
       </c>
       <c r="R35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S35">
         <v>6</v>
@@ -3367,49 +3367,49 @@
         <v>106</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S37">
         <v>6</v>
@@ -3684,28 +3684,28 @@
         <v>4</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S41">
         <v>6</v>
@@ -3737,31 +3737,31 @@
         <v>104</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M42">
         <v>5</v>
@@ -3773,10 +3773,10 @@
         <v>5</v>
       </c>
       <c r="P42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R42">
         <v>5</v>
@@ -3811,43 +3811,43 @@
         <v>104</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43">
         <v>5</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M43">
         <v>5</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>5</v>
       </c>
       <c r="P43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q43">
         <v>5</v>
@@ -3906,28 +3906,28 @@
         <v>3</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L44">
         <v>5</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>5</v>
       </c>
       <c r="O44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P44">
         <v>5</v>
       </c>
       <c r="Q44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S44">
         <v>6</v>
@@ -3980,28 +3980,28 @@
         <v>3</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S45">
         <v>6</v>
@@ -4033,46 +4033,46 @@
         <v>106</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K46">
         <v>5</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46">
         <v>5</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O46">
         <v>5</v>
       </c>
       <c r="P46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R46">
         <v>5</v>
@@ -4128,16 +4128,16 @@
         <v>5</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N47">
         <v>5</v>
       </c>
       <c r="O47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P47">
         <v>5</v>
@@ -4146,7 +4146,7 @@
         <v>5</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S47">
         <v>6</v>
@@ -4184,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -4196,28 +4196,28 @@
         <v>1</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S48">
         <v>6</v>
@@ -4255,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -4267,31 +4267,31 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S49">
         <v>6</v>
@@ -4344,28 +4344,28 @@
         <v>3</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S50">
         <v>6</v>
@@ -4397,49 +4397,49 @@
         <v>105</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S51">
         <v>6</v>
@@ -4548,46 +4548,46 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S53">
         <v>6</v>
@@ -4640,28 +4640,28 @@
         <v>1</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S54">
         <v>6</v>
@@ -4717,7 +4717,7 @@
         <v>5</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M55">
         <v>5</v>
@@ -4726,16 +4726,16 @@
         <v>4</v>
       </c>
       <c r="O55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S55">
         <v>6</v>
@@ -4936,28 +4936,28 @@
         <v>4</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>5</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S58">
         <v>6</v>
@@ -4989,28 +4989,28 @@
         <v>105</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -5022,7 +5022,7 @@
         <v>5</v>
       </c>
       <c r="O59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P59">
         <v>5</v>
@@ -5063,49 +5063,49 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S60">
         <v>6</v>
@@ -5137,49 +5137,49 @@
         <v>106</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61">
         <v>1</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S61">
         <v>6</v>
@@ -5211,28 +5211,28 @@
         <v>104</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L62">
         <v>5</v>
@@ -5285,49 +5285,49 @@
         <v>105</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S63">
         <v>6</v>
@@ -5359,34 +5359,34 @@
         <v>106</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K64">
         <v>5</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -5395,13 +5395,13 @@
         <v>5</v>
       </c>
       <c r="P64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S64">
         <v>6</v>
@@ -5445,37 +5445,37 @@
         <v>1</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S65">
         <v>6</v>
@@ -5531,10 +5531,10 @@
         <v>5</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N66">
         <v>5</v>
@@ -5546,10 +5546,10 @@
         <v>5</v>
       </c>
       <c r="Q66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S66">
         <v>6</v>
@@ -5581,49 +5581,49 @@
         <v>104</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S67">
         <v>6</v>
@@ -5655,49 +5655,49 @@
         <v>105</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S68">
         <v>6</v>
@@ -5729,28 +5729,28 @@
         <v>106</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L69">
         <v>5</v>
@@ -5803,34 +5803,34 @@
         <v>106</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N70">
         <v>5</v>
@@ -5842,10 +5842,10 @@
         <v>5</v>
       </c>
       <c r="Q70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S70">
         <v>6</v>
@@ -5877,28 +5877,28 @@
         <v>104</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L71">
         <v>5</v>
@@ -5907,19 +5907,19 @@
         <v>5</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O71">
         <v>5</v>
       </c>
       <c r="P71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S71">
         <v>6</v>
@@ -5951,49 +5951,49 @@
         <v>104</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S72">
         <v>6</v>
@@ -6049,7 +6049,7 @@
         <v>5</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M73">
         <v>5</v>
@@ -6064,10 +6064,10 @@
         <v>5</v>
       </c>
       <c r="Q73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S73">
         <v>6</v>
@@ -6099,25 +6099,25 @@
         <v>106</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K74">
         <v>5</v>
@@ -6126,7 +6126,7 @@
         <v>5</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -6173,16 +6173,16 @@
         <v>104</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -6191,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K75">
         <v>5</v>
@@ -6200,22 +6200,22 @@
         <v>5</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>5</v>
       </c>
       <c r="P75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q75">
         <v>5</v>
       </c>
       <c r="R75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S75">
         <v>6</v>
@@ -6268,7 +6268,7 @@
         <v>3</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L76">
         <v>4</v>
@@ -6469,49 +6469,49 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S79">
         <v>6</v>
@@ -6691,49 +6691,49 @@
         <v>106</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q82">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S82">
         <v>6</v>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -88,253 +88,253 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
     <t>C_L03</t>
   </si>
   <si>
-    <t>B_L21</t>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>B_L24</t>
   </si>
   <si>
     <t>B_L16</t>
   </si>
   <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>A_L29</t>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L21</t>
   </si>
   <si>
     <t>A_L23</t>
   </si>
   <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L13</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
     <t>A_L01</t>
   </si>
   <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>A_L30</t>
-  </si>
-  <si>
-    <t>B_L17</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L28</t>
-  </si>
-  <si>
     <t>C_L24</t>
   </si>
   <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
     <t>C_L06</t>
   </si>
   <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
     <t>A_L05</t>
   </si>
   <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L24</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>C</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
 </sst>
 </file>
@@ -780,64 +780,64 @@
         <v>104</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S2">
         <v>6</v>
       </c>
       <c r="T2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="X2">
         <v>5</v>
@@ -851,67 +851,67 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N3">
         <v>3</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="X3">
         <v>5</v>
@@ -925,70 +925,70 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>6</v>
       </c>
       <c r="T4">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W4">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -1002,55 +1002,55 @@
         <v>105</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>6</v>
       </c>
       <c r="T5">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -1059,10 +1059,10 @@
         <v>3</v>
       </c>
       <c r="W5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1073,19 +1073,19 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1097,34 +1097,34 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>6</v>
       </c>
       <c r="T6">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="U6">
         <v>1</v>
@@ -1133,7 +1133,7 @@
         <v>4</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1150,55 +1150,55 @@
         <v>106</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
       <c r="T7">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1224,19 +1224,19 @@
         <v>106</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>5</v>
@@ -1245,10 +1245,10 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>2</v>
@@ -1257,31 +1257,31 @@
         <v>2</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8">
         <v>6</v>
       </c>
       <c r="T8">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1295,16 +1295,16 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1313,31 +1313,31 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>2</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>7</v>
@@ -1346,19 +1346,19 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="U9">
         <v>2</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W9">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1381,58 +1381,58 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S10">
         <v>6</v>
       </c>
       <c r="T10">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1443,16 +1443,16 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1461,7 +1461,7 @@
         <v>2</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -1470,43 +1470,43 @@
         <v>4</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>4</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>6</v>
       </c>
       <c r="T11">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="U11">
         <v>1</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W11">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1520,64 +1520,64 @@
         <v>105</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>3</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S12">
         <v>6</v>
       </c>
       <c r="T12">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="U12">
         <v>2</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X12">
         <v>4</v>
@@ -1591,70 +1591,70 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>6</v>
       </c>
       <c r="T13">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13">
         <v>3</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1665,13 +1665,13 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -1680,55 +1680,55 @@
         <v>3</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14">
         <v>4</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S14">
         <v>6</v>
       </c>
       <c r="T14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U14">
         <v>1</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1742,67 +1742,67 @@
         <v>106</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>7</v>
       </c>
       <c r="M15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>6</v>
       </c>
       <c r="T15">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U15">
         <v>1</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1816,25 +1816,25 @@
         <v>105</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16">
         <v>5</v>
@@ -1846,37 +1846,37 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q16">
         <v>5</v>
       </c>
       <c r="R16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S16">
         <v>6</v>
       </c>
       <c r="T16">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16">
         <v>3</v>
       </c>
       <c r="W16">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1890,64 +1890,64 @@
         <v>105</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S17">
         <v>6</v>
       </c>
       <c r="T17">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17">
         <v>4</v>
       </c>
       <c r="W17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -1964,34 +1964,34 @@
         <v>104</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>4</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -2000,28 +2000,28 @@
         <v>4</v>
       </c>
       <c r="P18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>6</v>
       </c>
       <c r="T18">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U18">
         <v>1</v>
       </c>
       <c r="V18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2044,10 +2044,10 @@
         <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -2056,13 +2056,13 @@
         <v>3</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2071,13 +2071,13 @@
         <v>4</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>5</v>
@@ -2086,19 +2086,19 @@
         <v>6</v>
       </c>
       <c r="T19">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="U19">
         <v>1</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W19">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2112,64 +2112,64 @@
         <v>104</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S20">
         <v>6</v>
       </c>
       <c r="T20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="U20">
         <v>1</v>
       </c>
       <c r="V20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2183,58 +2183,58 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>5</v>
       </c>
       <c r="R21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>6</v>
       </c>
       <c r="T21">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2243,7 +2243,7 @@
         <v>3</v>
       </c>
       <c r="W21">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2260,46 +2260,46 @@
         <v>105</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>3</v>
       </c>
       <c r="L22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P22">
         <v>2</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <v>3</v>
@@ -2308,16 +2308,16 @@
         <v>6</v>
       </c>
       <c r="T22">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U22">
         <v>1</v>
       </c>
       <c r="V22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W22">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2331,13 +2331,13 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2349,96 +2349,96 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>6</v>
       </c>
       <c r="T23">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W23">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="X23">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>2</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>5</v>
@@ -2447,63 +2447,66 @@
         <v>4</v>
       </c>
       <c r="Q24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S24">
         <v>6</v>
       </c>
       <c r="T24">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="U24">
         <v>2</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>3</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>4</v>
@@ -2512,45 +2515,45 @@
         <v>5</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>6</v>
       </c>
       <c r="T25">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="U25">
         <v>1</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W25">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:24">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2565,140 +2568,140 @@
         <v>2</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>6</v>
       </c>
       <c r="T26">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26">
         <v>4</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="X26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
         <v>106</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27">
         <v>3</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27">
         <v>3</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27">
         <v>6</v>
       </c>
       <c r="T27">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27">
         <v>4</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2713,140 +2716,140 @@
         <v>1</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>1</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P28">
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>6</v>
       </c>
       <c r="T28">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28">
         <v>3</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:24">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
         <v>104</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29">
         <v>4</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>6</v>
       </c>
       <c r="T29">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W29">
         <v>10</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -2864,63 +2867,63 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>4</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
       <c r="T30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="U30">
         <v>1</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:24">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -2929,40 +2932,40 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -2971,155 +2974,155 @@
         <v>6</v>
       </c>
       <c r="T31">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W31">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S32">
         <v>6</v>
       </c>
       <c r="T32">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="U32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V32">
         <v>3</v>
       </c>
       <c r="W32">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33">
         <v>4</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>5</v>
       </c>
       <c r="Q33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S33">
         <v>6</v>
       </c>
       <c r="T33">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U33">
         <v>1</v>
@@ -3128,7 +3131,7 @@
         <v>4</v>
       </c>
       <c r="W33">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3136,13 +3139,13 @@
     </row>
     <row r="34" spans="1:24">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -3157,13 +3160,13 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34">
         <v>7</v>
@@ -3193,36 +3196,36 @@
         <v>6</v>
       </c>
       <c r="T34">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U34">
         <v>1</v>
       </c>
       <c r="V34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W34">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:24">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
         <v>2</v>
@@ -3231,7 +3234,7 @@
         <v>3</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35">
         <v>3</v>
@@ -3240,34 +3243,34 @@
         <v>3</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S35">
         <v>6</v>
       </c>
       <c r="T35">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="U35">
         <v>1</v>
@@ -3276,95 +3279,92 @@
         <v>3</v>
       </c>
       <c r="W35">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>2</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M36">
         <v>4</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S36">
         <v>6</v>
       </c>
-      <c r="T36">
-        <v>54</v>
-      </c>
       <c r="U36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36">
         <v>3</v>
       </c>
       <c r="W36">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="X36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -3373,40 +3373,40 @@
         <v>3</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>6</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R37">
         <v>6</v>
@@ -3421,39 +3421,39 @@
         <v>1</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W37">
         <v>7</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>3</v>
@@ -3462,22 +3462,22 @@
         <v>3</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O38">
         <v>4</v>
       </c>
       <c r="P38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -3489,81 +3489,81 @@
         <v>6</v>
       </c>
       <c r="T38">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U38">
         <v>1</v>
       </c>
       <c r="V38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X38">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:24">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
         <v>106</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S39">
         <v>6</v>
       </c>
       <c r="T39">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="U39">
         <v>1</v>
@@ -3572,63 +3572,63 @@
         <v>3</v>
       </c>
       <c r="W39">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C40" t="s">
         <v>104</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>5</v>
       </c>
       <c r="O40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>4</v>
       </c>
       <c r="Q40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>5</v>
@@ -3637,16 +3637,16 @@
         <v>6</v>
       </c>
       <c r="T40">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="U40">
         <v>1</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="X40">
         <v>4</v>
@@ -3654,31 +3654,31 @@
     </row>
     <row r="41" spans="1:24">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41">
         <v>4</v>
@@ -3687,22 +3687,22 @@
         <v>5</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>5</v>
       </c>
       <c r="P41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R41">
         <v>4</v>
@@ -3711,7 +3711,7 @@
         <v>6</v>
       </c>
       <c r="T41">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="U41">
         <v>1</v>
@@ -3720,122 +3720,122 @@
         <v>3</v>
       </c>
       <c r="W41">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="X41">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:24">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>4</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q42">
         <v>4</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S42">
         <v>6</v>
       </c>
       <c r="T42">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42">
         <v>3</v>
       </c>
       <c r="W42">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X42">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>5</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>5</v>
@@ -3844,22 +3844,22 @@
         <v>4</v>
       </c>
       <c r="O43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>5</v>
       </c>
       <c r="R43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S43">
         <v>6</v>
       </c>
       <c r="T43">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U43">
         <v>1</v>
@@ -3868,18 +3868,18 @@
         <v>4</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X43">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:24">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
         <v>106</v>
@@ -3900,49 +3900,49 @@
         <v>4</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44">
         <v>3</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44">
         <v>6</v>
       </c>
       <c r="N44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S44">
         <v>6</v>
       </c>
       <c r="T44">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V44">
         <v>3</v>
       </c>
       <c r="W44">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="X44">
         <v>5</v>
@@ -3950,22 +3950,22 @@
     </row>
     <row r="45" spans="1:24">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -3974,31 +3974,31 @@
         <v>4</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45">
         <v>4</v>
       </c>
       <c r="L45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N45">
         <v>5</v>
       </c>
       <c r="O45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R45">
         <v>5</v>
@@ -4007,297 +4007,300 @@
         <v>6</v>
       </c>
       <c r="T45">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U45">
         <v>1</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W45">
-        <v>8</v>
-      </c>
-      <c r="X45">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S46">
         <v>6</v>
       </c>
+      <c r="T46">
+        <v>38</v>
+      </c>
       <c r="U46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W46">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X46">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C47" t="s">
         <v>106</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S47">
         <v>6</v>
       </c>
       <c r="T47">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="U47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V47">
         <v>3</v>
       </c>
+      <c r="W47">
+        <v>1</v>
+      </c>
       <c r="X47">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M48">
         <v>6</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S48">
         <v>6</v>
       </c>
       <c r="T48">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W48">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X48">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:24">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
         <v>104</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S49">
         <v>6</v>
       </c>
       <c r="T49">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U49">
         <v>1</v>
@@ -4306,63 +4309,63 @@
         <v>3</v>
       </c>
       <c r="W49">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X49">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:24">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L50">
         <v>6</v>
       </c>
       <c r="M50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P50">
         <v>6</v>
       </c>
       <c r="Q50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R50">
         <v>7</v>
@@ -4374,24 +4377,24 @@
         <v>36</v>
       </c>
       <c r="U50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W50">
         <v>7</v>
       </c>
       <c r="X50">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
         <v>105</v>
@@ -4403,69 +4406,69 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S51">
         <v>6</v>
       </c>
       <c r="T51">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="U51">
         <v>1</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W51">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="X51">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C52" t="s">
         <v>104</v>
@@ -4474,43 +4477,43 @@
         <v>2</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52">
         <v>3</v>
       </c>
       <c r="K52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M52">
         <v>4</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R52">
         <v>4</v>
@@ -4519,33 +4522,33 @@
         <v>6</v>
       </c>
       <c r="T52">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="U52">
         <v>1</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W52">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X52">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:24">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C53" t="s">
         <v>104</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -4554,81 +4557,81 @@
         <v>1</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q53">
         <v>4</v>
       </c>
       <c r="R53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S53">
         <v>6</v>
       </c>
       <c r="T53">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="U53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W53">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="X53">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:24">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -4640,117 +4643,117 @@
         <v>1</v>
       </c>
       <c r="K54">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q54">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S54">
         <v>6</v>
       </c>
       <c r="T54">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="U54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W54">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X54">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:24">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>2</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55">
         <v>5</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M55">
         <v>5</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S55">
         <v>6</v>
       </c>
       <c r="T55">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="U55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V55">
         <v>3</v>
       </c>
       <c r="W55">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="X55">
         <v>4</v>
@@ -4758,58 +4761,58 @@
     </row>
     <row r="56" spans="1:24">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
         <v>105</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S56">
         <v>6</v>
@@ -4818,7 +4821,7 @@
         <v>37</v>
       </c>
       <c r="U56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V56">
         <v>2</v>
@@ -4827,69 +4830,69 @@
         <v>11</v>
       </c>
       <c r="X56">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:24">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C57" t="s">
         <v>105</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N57">
         <v>5</v>
       </c>
       <c r="O57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S57">
         <v>6</v>
       </c>
       <c r="T57">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="U57">
         <v>1</v>
@@ -4898,63 +4901,63 @@
         <v>3</v>
       </c>
       <c r="W57">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X57">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:24">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D58">
         <v>2</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58">
         <v>3</v>
       </c>
       <c r="H58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R58">
         <v>4</v>
@@ -4963,54 +4966,54 @@
         <v>6</v>
       </c>
       <c r="T58">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X58">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:24">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -5019,10 +5022,10 @@
         <v>5</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P59">
         <v>5</v>
@@ -5037,63 +5040,63 @@
         <v>6</v>
       </c>
       <c r="T59">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="U59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W59">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="X59">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:24">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60">
         <v>5</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O60">
         <v>5</v>
@@ -5102,60 +5105,60 @@
         <v>5</v>
       </c>
       <c r="Q60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S60">
         <v>6</v>
       </c>
       <c r="T60">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="U60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X60">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:24">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
         <v>106</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61">
         <v>6</v>
@@ -5164,10 +5167,10 @@
         <v>5</v>
       </c>
       <c r="M61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -5185,54 +5188,54 @@
         <v>6</v>
       </c>
       <c r="T61">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W61">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X61">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:24">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
         <v>104</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L62">
         <v>5</v>
@@ -5241,7 +5244,7 @@
         <v>5</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>5</v>
@@ -5250,51 +5253,51 @@
         <v>5</v>
       </c>
       <c r="Q62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S62">
         <v>6</v>
       </c>
       <c r="T62">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="U62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V62">
         <v>4</v>
       </c>
       <c r="W62">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="X62">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:24">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63">
         <v>3</v>
@@ -5303,66 +5306,66 @@
         <v>3</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q63">
         <v>4</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S63">
         <v>6</v>
       </c>
       <c r="T63">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W63">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="X63">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:24">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
         <v>106</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64">
         <v>4</v>
@@ -5377,13 +5380,13 @@
         <v>4</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64">
         <v>5</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M64">
         <v>4</v>
@@ -5407,104 +5410,104 @@
         <v>6</v>
       </c>
       <c r="T64">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="U64">
         <v>1</v>
       </c>
       <c r="V64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W64">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="X64">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:24">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S65">
         <v>6</v>
       </c>
       <c r="T65">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="U65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W65">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X65">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:24">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -5522,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -5537,13 +5540,13 @@
         <v>6</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q66">
         <v>6</v>
@@ -5555,146 +5558,146 @@
         <v>6</v>
       </c>
       <c r="T66">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U66">
         <v>1</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X66">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:24">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C67" t="s">
         <v>104</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L67">
         <v>6</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S67">
         <v>6</v>
       </c>
       <c r="T67">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U67">
         <v>1</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W67">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X67">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:24">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L68">
         <v>6</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R68">
         <v>6</v>
@@ -5703,36 +5706,36 @@
         <v>6</v>
       </c>
       <c r="T68">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="U68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W68">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="X68">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:24">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F69">
         <v>3</v>
@@ -5741,7 +5744,7 @@
         <v>3</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I69">
         <v>3</v>
@@ -5756,78 +5759,75 @@
         <v>5</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S69">
         <v>6</v>
       </c>
       <c r="T69">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="U69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W69">
-        <v>6</v>
-      </c>
-      <c r="X69">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:24">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M70">
         <v>4</v>
@@ -5842,63 +5842,63 @@
         <v>5</v>
       </c>
       <c r="Q70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S70">
         <v>6</v>
       </c>
       <c r="T70">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="U70">
         <v>1</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W70">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X70">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:24">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C71" t="s">
         <v>104</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71">
         <v>3</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L71">
         <v>5</v>
@@ -5907,63 +5907,63 @@
         <v>5</v>
       </c>
       <c r="N71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P71">
         <v>4</v>
       </c>
       <c r="Q71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S71">
         <v>6</v>
       </c>
       <c r="T71">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="U71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V71">
         <v>3</v>
       </c>
       <c r="W71">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="X71">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:24">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I72">
         <v>3</v>
@@ -5972,96 +5972,96 @@
         <v>3</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O72">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S72">
         <v>6</v>
       </c>
       <c r="T72">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="U72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W72">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="X72">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:24">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73">
         <v>1</v>
       </c>
       <c r="K73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L73">
         <v>6</v>
       </c>
       <c r="M73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q73">
         <v>6</v>
@@ -6073,137 +6073,137 @@
         <v>6</v>
       </c>
       <c r="T73">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V73">
         <v>3</v>
       </c>
       <c r="W73">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X73">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:24">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S74">
         <v>6</v>
       </c>
       <c r="T74">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W74">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X74">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:24">
       <c r="A75" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M75">
         <v>4</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O75">
         <v>5</v>
@@ -6212,7 +6212,7 @@
         <v>4</v>
       </c>
       <c r="Q75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R75">
         <v>4</v>
@@ -6221,33 +6221,33 @@
         <v>6</v>
       </c>
       <c r="T75">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V75">
         <v>4</v>
       </c>
       <c r="W75">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X75">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:24">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76">
         <v>4</v>
@@ -6256,10 +6256,10 @@
         <v>3</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I76">
         <v>4</v>
@@ -6268,28 +6268,28 @@
         <v>3</v>
       </c>
       <c r="K76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S76">
         <v>6</v>
@@ -6298,13 +6298,13 @@
         <v>37</v>
       </c>
       <c r="U76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W76">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X76">
         <v>5</v>
@@ -6312,25 +6312,25 @@
     </row>
     <row r="77" spans="1:24">
       <c r="A77" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C77" t="s">
         <v>104</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F77">
         <v>2</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77">
         <v>2</v>
@@ -6339,16 +6339,16 @@
         <v>3</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K77">
         <v>4</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N77">
         <v>4</v>
@@ -6357,19 +6357,19 @@
         <v>4</v>
       </c>
       <c r="P77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S77">
         <v>6</v>
       </c>
       <c r="T77">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="U77">
         <v>1</v>
@@ -6378,211 +6378,211 @@
         <v>4</v>
       </c>
       <c r="W77">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="X77">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:24">
       <c r="A78" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78">
         <v>2</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78">
         <v>2</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L78">
         <v>4</v>
       </c>
       <c r="M78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N78">
         <v>5</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
         <v>6</v>
       </c>
       <c r="T78">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="U78">
         <v>2</v>
       </c>
       <c r="V78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="X78">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:24">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N79">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S79">
         <v>6</v>
       </c>
       <c r="T79">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="U79">
         <v>2</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W79">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X79">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:24">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>4</v>
       </c>
       <c r="P80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R80">
         <v>4</v>
@@ -6591,30 +6591,30 @@
         <v>6</v>
       </c>
       <c r="T80">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="U80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W80">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="X80">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:24">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C81" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -6623,7 +6623,7 @@
         <v>3</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -6644,10 +6644,10 @@
         <v>4</v>
       </c>
       <c r="M81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O81">
         <v>3</v>
@@ -6656,57 +6656,57 @@
         <v>4</v>
       </c>
       <c r="Q81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S81">
         <v>6</v>
       </c>
       <c r="T81">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="U81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V81">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W81">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="X81">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:24">
       <c r="A82" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D82">
         <v>2</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J82">
         <v>2</v>
@@ -6715,31 +6715,31 @@
         <v>5</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P82">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S82">
         <v>6</v>
       </c>
       <c r="T82">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U82">
         <v>1</v>
@@ -6748,10 +6748,10 @@
         <v>3</v>
       </c>
       <c r="W82">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X82">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -100,232 +100,232 @@
     <t>B_L10</t>
   </si>
   <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
     <t>B_L05</t>
   </si>
   <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
     <t>C_L20</t>
   </si>
   <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L23</t>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L10</t>
   </si>
   <si>
     <t>C_L13</t>
   </si>
   <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L05</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L05</t>
   </si>
   <si>
     <t>A</t>
@@ -780,34 +780,34 @@
         <v>104</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N2">
         <v>5</v>
@@ -816,31 +816,31 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S2">
         <v>6</v>
       </c>
       <c r="T2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X2">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -854,67 +854,67 @@
         <v>104</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -928,31 +928,31 @@
         <v>104</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -961,7 +961,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>5</v>
@@ -976,16 +976,16 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="U4">
         <v>1</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1002,13 +1002,13 @@
         <v>105</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1020,7 +1020,7 @@
         <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -1035,34 +1035,34 @@
         <v>7</v>
       </c>
       <c r="O5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>6</v>
       </c>
       <c r="T5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>3</v>
       </c>
       <c r="W5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1082,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1091,52 +1091,52 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S6">
         <v>6</v>
       </c>
       <c r="T6">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="U6">
         <v>1</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1153,52 +1153,52 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
       <c r="T7">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1227,64 +1227,64 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>5</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q8">
         <v>3</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S8">
         <v>6</v>
       </c>
       <c r="T8">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="U8">
         <v>1</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1298,31 +1298,31 @@
         <v>104</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -1340,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="R9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1355,10 +1355,10 @@
         <v>4</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1372,34 +1372,34 @@
         <v>104</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>4</v>
@@ -1411,28 +1411,28 @@
         <v>5</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>6</v>
       </c>
       <c r="T10">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="U10">
         <v>1</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W10">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1446,67 +1446,67 @@
         <v>105</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q11">
         <v>4</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <v>6</v>
       </c>
       <c r="T11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="U11">
         <v>1</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1520,67 +1520,67 @@
         <v>105</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>6</v>
       </c>
       <c r="T12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1594,67 +1594,67 @@
         <v>106</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S13">
         <v>6</v>
       </c>
       <c r="T13">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="U13">
         <v>2</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W13">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="X13">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1665,70 +1665,70 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>6</v>
       </c>
       <c r="T14">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14">
         <v>2</v>
       </c>
       <c r="W14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1742,34 +1742,34 @@
         <v>106</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -1781,28 +1781,28 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>6</v>
       </c>
       <c r="T15">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W15">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1816,25 +1816,25 @@
         <v>105</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <v>5</v>
@@ -1846,37 +1846,37 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>5</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>6</v>
       </c>
       <c r="T16">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16">
         <v>3</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1890,67 +1890,67 @@
         <v>105</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>6</v>
       </c>
       <c r="T17">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1964,46 +1964,46 @@
         <v>104</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -2012,19 +2012,19 @@
         <v>6</v>
       </c>
       <c r="T18">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2041,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -2053,19 +2053,19 @@
         <v>2</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>4</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19">
         <v>4</v>
@@ -2074,31 +2074,31 @@
         <v>4</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S19">
         <v>6</v>
       </c>
       <c r="T19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2112,64 +2112,64 @@
         <v>104</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <v>3</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P20">
         <v>3</v>
       </c>
       <c r="Q20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
         <v>6</v>
       </c>
       <c r="T20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U20">
         <v>1</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2186,19 +2186,19 @@
         <v>106</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>3</v>
@@ -2210,7 +2210,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -2219,13 +2219,13 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21">
         <v>5</v>
@@ -2237,16 +2237,13 @@
         <v>46</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W21">
         <v>17</v>
-      </c>
-      <c r="X21">
-        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:24">
@@ -2260,55 +2257,55 @@
         <v>105</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <v>3</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>2</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>6</v>
       </c>
       <c r="T22">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="U22">
         <v>1</v>
@@ -2317,10 +2314,10 @@
         <v>3</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2334,67 +2331,67 @@
         <v>106</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S23">
         <v>6</v>
       </c>
       <c r="T23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W23">
         <v>1</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2411,19 +2408,19 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2438,37 +2435,37 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24">
         <v>4</v>
       </c>
       <c r="Q24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S24">
         <v>6</v>
       </c>
       <c r="T24">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U24">
         <v>2</v>
       </c>
       <c r="V24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W24">
         <v>1</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2482,34 +2479,34 @@
         <v>104</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>6</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -2521,7 +2518,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25">
         <v>6</v>
@@ -2530,19 +2527,19 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U25">
         <v>1</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:24">
@@ -2556,46 +2553,46 @@
         <v>106</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R26">
         <v>5</v>
@@ -2604,19 +2601,19 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="U26">
         <v>1</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W26">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="X26">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2630,37 +2627,37 @@
         <v>106</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>3</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L27">
         <v>3</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>3</v>
@@ -2669,28 +2666,28 @@
         <v>3</v>
       </c>
       <c r="Q27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
         <v>6</v>
       </c>
       <c r="T27">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W27">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -2704,67 +2701,67 @@
         <v>104</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S28">
         <v>6</v>
       </c>
       <c r="T28">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="U28">
         <v>1</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="X28">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2775,13 +2772,13 @@
         <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -2790,34 +2787,34 @@
         <v>3</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -2829,87 +2826,87 @@
         <v>40</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30">
         <v>2</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M30">
         <v>4</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
       <c r="T30">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="U30">
         <v>1</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -2917,16 +2914,16 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
         <v>104</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2938,13 +2935,13 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31">
         <v>7</v>
@@ -2956,193 +2953,193 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>7</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>7</v>
       </c>
       <c r="R31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>6</v>
       </c>
       <c r="T31">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="U31">
         <v>1</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S32">
         <v>6</v>
       </c>
       <c r="T32">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U32">
         <v>1</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W32">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X32">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
         <v>104</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
         <v>2</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>5</v>
       </c>
       <c r="Q33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>6</v>
       </c>
       <c r="T33">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="U33">
         <v>1</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
         <v>106</v>
@@ -3151,52 +3148,52 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>2</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S34">
         <v>6</v>
       </c>
       <c r="T34">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="U34">
         <v>1</v>
@@ -3205,72 +3202,72 @@
         <v>3</v>
       </c>
       <c r="W34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X34">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:24">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
         <v>105</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>2</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S35">
         <v>6</v>
       </c>
       <c r="T35">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="U35">
         <v>1</v>
@@ -3279,51 +3276,51 @@
         <v>3</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -3335,33 +3332,36 @@
         <v>3</v>
       </c>
       <c r="Q36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S36">
         <v>6</v>
       </c>
+      <c r="T36">
+        <v>40</v>
+      </c>
       <c r="U36">
         <v>2</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W36">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
         <v>105</v>
@@ -3379,25 +3379,25 @@
         <v>3</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37">
         <v>2</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37">
         <v>6</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>6</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -3409,22 +3409,22 @@
         <v>6</v>
       </c>
       <c r="R37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S37">
         <v>6</v>
       </c>
       <c r="T37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="U37">
         <v>1</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="38" spans="1:24">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
         <v>105</v>
@@ -3456,40 +3456,40 @@
         <v>4</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>3</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S38">
         <v>6</v>
       </c>
       <c r="T38">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="U38">
         <v>1</v>
@@ -3498,18 +3498,18 @@
         <v>3</v>
       </c>
       <c r="W38">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:24">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
         <v>106</v>
@@ -3524,10 +3524,10 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -3536,75 +3536,72 @@
         <v>2</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>6</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>5</v>
       </c>
       <c r="O39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S39">
         <v>6</v>
       </c>
-      <c r="T39">
-        <v>28</v>
-      </c>
       <c r="U39">
         <v>1</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X39">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
         <v>104</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J40">
         <v>3</v>
@@ -3613,114 +3610,114 @@
         <v>5</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S40">
         <v>6</v>
       </c>
       <c r="T40">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U40">
         <v>1</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W40">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="X40">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:24">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
         <v>106</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>5</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>5</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S41">
         <v>6</v>
       </c>
       <c r="T41">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="U41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V41">
         <v>3</v>
       </c>
       <c r="W41">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="X41">
         <v>3</v>
@@ -3728,84 +3725,84 @@
     </row>
     <row r="42" spans="1:24">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
         <v>106</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>4</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S42">
         <v>6</v>
       </c>
       <c r="T42">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="U42">
         <v>1</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W42">
         <v>8</v>
       </c>
       <c r="X42">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
         <v>105</v>
@@ -3814,37 +3811,37 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K43">
         <v>5</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P43">
         <v>5</v>
@@ -3859,16 +3856,16 @@
         <v>6</v>
       </c>
       <c r="T43">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="U43">
         <v>1</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W43">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="X43">
         <v>4</v>
@@ -3876,37 +3873,37 @@
     </row>
     <row r="44" spans="1:24">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
         <v>106</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -3915,84 +3912,84 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S44">
         <v>6</v>
       </c>
       <c r="T44">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U44">
         <v>1</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X44">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:24">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
         <v>106</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45">
         <v>4</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N45">
         <v>5</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P45">
         <v>5</v>
@@ -4007,7 +4004,7 @@
         <v>6</v>
       </c>
       <c r="T45">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="U45">
         <v>1</v>
@@ -4016,107 +4013,110 @@
         <v>3</v>
       </c>
       <c r="W45">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="X45">
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
         <v>105</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46">
         <v>2</v>
       </c>
       <c r="K46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S46">
         <v>6</v>
       </c>
       <c r="T46">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="U46">
         <v>2</v>
       </c>
       <c r="V46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W46">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X46">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>106</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G47">
         <v>4</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I47">
         <v>4</v>
@@ -4125,66 +4125,66 @@
         <v>3</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S47">
         <v>6</v>
       </c>
       <c r="T47">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="U47">
         <v>2</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W47">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X47">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
         <v>105</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48">
         <v>3</v>
@@ -4193,49 +4193,49 @@
         <v>3</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q48">
         <v>4</v>
       </c>
       <c r="R48">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S48">
         <v>6</v>
       </c>
       <c r="T48">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W48">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X48">
         <v>7</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="49" spans="1:24">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
         <v>104</v>
@@ -4258,179 +4258,179 @@
         <v>3</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49">
         <v>3</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S49">
         <v>6</v>
       </c>
       <c r="T49">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="U49">
         <v>1</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W49">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="X49">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:24">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C50" t="s">
         <v>106</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S50">
         <v>6</v>
       </c>
       <c r="T50">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W50">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="X50">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
         <v>105</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51">
         <v>5</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>5</v>
@@ -4439,7 +4439,7 @@
         <v>5</v>
       </c>
       <c r="Q51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R51">
         <v>5</v>
@@ -4448,27 +4448,27 @@
         <v>6</v>
       </c>
       <c r="T51">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="U51">
         <v>1</v>
       </c>
       <c r="V51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W51">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="X51">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C52" t="s">
         <v>104</v>
@@ -4477,40 +4477,40 @@
         <v>2</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I52">
         <v>2</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q52">
         <v>4</v>
@@ -4522,149 +4522,149 @@
         <v>6</v>
       </c>
       <c r="T52">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W52">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X52">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:24">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
         <v>104</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q53">
         <v>4</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S53">
         <v>6</v>
       </c>
       <c r="T53">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="U53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W53">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X53">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:24">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
         <v>105</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S54">
         <v>6</v>
@@ -4673,87 +4673,87 @@
         <v>36</v>
       </c>
       <c r="U54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W54">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X54">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:24">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s">
         <v>105</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G55">
         <v>2</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55">
         <v>2</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
         <v>6</v>
       </c>
       <c r="T55">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="U55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="X55">
         <v>4</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="56" spans="1:24">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
         <v>105</v>
@@ -4773,31 +4773,31 @@
         <v>2</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L56">
         <v>4</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N56">
         <v>5</v>
@@ -4809,25 +4809,25 @@
         <v>5</v>
       </c>
       <c r="Q56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S56">
         <v>6</v>
       </c>
       <c r="T56">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="U56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W56">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="X56">
         <v>6</v>
@@ -4835,105 +4835,105 @@
     </row>
     <row r="57" spans="1:24">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
         <v>105</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S57">
         <v>6</v>
       </c>
       <c r="T57">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U57">
         <v>1</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W57">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X57">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:24">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
         <v>105</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58">
         <v>3</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -4942,22 +4942,22 @@
         <v>4</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R58">
         <v>4</v>
@@ -4966,42 +4966,42 @@
         <v>6</v>
       </c>
       <c r="T58">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="U58">
         <v>1</v>
       </c>
       <c r="V58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W58">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="X58">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:24">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
         <v>104</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H59">
         <v>4</v>
@@ -5013,54 +5013,54 @@
         <v>3</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N59">
         <v>4</v>
       </c>
       <c r="O59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S59">
         <v>6</v>
       </c>
       <c r="T59">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="U59">
         <v>1</v>
       </c>
       <c r="V59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W59">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="X59">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:24">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C60" t="s">
         <v>106</v>
@@ -5078,102 +5078,102 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>1</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S60">
         <v>6</v>
       </c>
       <c r="T60">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="U60">
         <v>1</v>
       </c>
       <c r="V60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W60">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="X60">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:24">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61">
         <v>4</v>
       </c>
       <c r="I61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P61">
         <v>5</v>
@@ -5187,73 +5187,70 @@
       <c r="S61">
         <v>6</v>
       </c>
-      <c r="T61">
-        <v>40</v>
-      </c>
       <c r="U61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W61">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X61">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:24">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
         <v>104</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N62">
         <v>4</v>
       </c>
       <c r="O62">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R62">
         <v>4</v>
@@ -5262,36 +5259,36 @@
         <v>6</v>
       </c>
       <c r="T62">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="U62">
         <v>2</v>
       </c>
       <c r="V62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W62">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X62">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:24">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C63" t="s">
         <v>106</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -5303,49 +5300,49 @@
         <v>3</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P63">
         <v>4</v>
       </c>
       <c r="Q63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S63">
         <v>6</v>
       </c>
       <c r="T63">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="U63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V63">
         <v>3</v>
       </c>
       <c r="W63">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X63">
         <v>5</v>
@@ -5353,10 +5350,10 @@
     </row>
     <row r="64" spans="1:24">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
         <v>106</v>
@@ -5365,126 +5362,126 @@
         <v>3</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q64">
         <v>4</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
         <v>6</v>
       </c>
       <c r="T64">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W64">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="X64">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:24">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
         <v>104</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S65">
         <v>6</v>
       </c>
       <c r="T65">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U65">
         <v>2</v>
@@ -5493,155 +5490,155 @@
         <v>5</v>
       </c>
       <c r="W65">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="X65">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:24">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C66" t="s">
         <v>104</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S66">
         <v>6</v>
       </c>
       <c r="T66">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U66">
         <v>1</v>
       </c>
       <c r="V66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X66">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:24">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C67" t="s">
         <v>104</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S67">
         <v>6</v>
       </c>
       <c r="T67">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V67">
         <v>3</v>
       </c>
       <c r="W67">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X67">
         <v>6</v>
@@ -5649,10 +5646,10 @@
     </row>
     <row r="68" spans="1:24">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C68" t="s">
         <v>104</v>
@@ -5664,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -5679,34 +5676,34 @@
         <v>1</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N68">
         <v>7</v>
       </c>
       <c r="O68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P68">
         <v>7</v>
       </c>
       <c r="Q68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S68">
         <v>6</v>
       </c>
       <c r="T68">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U68">
         <v>1</v>
@@ -5715,60 +5712,60 @@
         <v>3</v>
       </c>
       <c r="W68">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X68">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:24">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C69" t="s">
         <v>105</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>3</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K69">
         <v>6</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
         <v>7</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q69">
         <v>6</v>
@@ -5780,30 +5777,33 @@
         <v>6</v>
       </c>
       <c r="T69">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="U69">
         <v>1</v>
       </c>
       <c r="V69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W69">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="X69">
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:24">
       <c r="A70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C70" t="s">
         <v>105</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -5818,28 +5818,28 @@
         <v>2</v>
       </c>
       <c r="I70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70">
         <v>4</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M70">
         <v>4</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q70">
         <v>5</v>
@@ -5851,27 +5851,27 @@
         <v>6</v>
       </c>
       <c r="T70">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="U70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W70">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="X70">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:24">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C71" t="s">
         <v>104</v>
@@ -5883,58 +5883,58 @@
         <v>2</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q71">
         <v>5</v>
       </c>
       <c r="R71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S71">
         <v>6</v>
       </c>
       <c r="T71">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U71">
         <v>1</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W71">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X71">
         <v>6</v>
@@ -5942,40 +5942,40 @@
     </row>
     <row r="72" spans="1:24">
       <c r="A72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C72" t="s">
         <v>105</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M72">
         <v>7</v>
@@ -5993,66 +5993,66 @@
         <v>6</v>
       </c>
       <c r="R72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S72">
         <v>6</v>
       </c>
       <c r="T72">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="U72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V72">
         <v>3</v>
       </c>
       <c r="W72">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="X72">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:24">
       <c r="A73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
         <v>106</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73">
         <v>2</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>3</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L73">
         <v>6</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N73">
         <v>6</v>
@@ -6061,10 +6061,10 @@
         <v>7</v>
       </c>
       <c r="P73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R73">
         <v>6</v>
@@ -6073,7 +6073,7 @@
         <v>6</v>
       </c>
       <c r="T73">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="U73">
         <v>1</v>
@@ -6082,7 +6082,7 @@
         <v>3</v>
       </c>
       <c r="W73">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X73">
         <v>7</v>
@@ -6090,28 +6090,28 @@
     </row>
     <row r="74" spans="1:24">
       <c r="A74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
         <v>104</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74">
         <v>1</v>
@@ -6120,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="K74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L74">
         <v>7</v>
@@ -6147,113 +6147,113 @@
         <v>6</v>
       </c>
       <c r="T74">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="U74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W74">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="X74">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:24">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C75" t="s">
         <v>105</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K75">
         <v>4</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S75">
         <v>6</v>
       </c>
       <c r="T75">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="U75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W75">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="X75">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:24">
       <c r="A76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C76" t="s">
         <v>104</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76">
         <v>2</v>
@@ -6262,10 +6262,10 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K76">
         <v>7</v>
@@ -6289,96 +6289,96 @@
         <v>7</v>
       </c>
       <c r="R76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S76">
         <v>6</v>
       </c>
       <c r="T76">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="U76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V76">
         <v>4</v>
       </c>
       <c r="W76">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="X76">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:24">
       <c r="A77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C77" t="s">
         <v>104</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>2</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77">
         <v>3</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O77">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P77">
         <v>5</v>
       </c>
       <c r="Q77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S77">
         <v>6</v>
       </c>
       <c r="T77">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="U77">
         <v>1</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W77">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="X77">
         <v>6</v>
@@ -6386,10 +6386,10 @@
     </row>
     <row r="78" spans="1:24">
       <c r="A78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C78" t="s">
         <v>104</v>
@@ -6398,7 +6398,7 @@
         <v>3</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78">
         <v>2</v>
@@ -6407,34 +6407,34 @@
         <v>3</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L78">
         <v>4</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R78">
         <v>3</v>
@@ -6443,81 +6443,81 @@
         <v>6</v>
       </c>
       <c r="T78">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W78">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X78">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:24">
       <c r="A79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
         <v>106</v>
       </c>
       <c r="D79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E79">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O79">
         <v>3</v>
       </c>
       <c r="P79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S79">
         <v>6</v>
       </c>
       <c r="T79">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="U79">
         <v>2</v>
@@ -6526,36 +6526,36 @@
         <v>3</v>
       </c>
       <c r="W79">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="X79">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:24">
       <c r="A80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C80" t="s">
         <v>106</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I80">
         <v>2</v>
@@ -6564,99 +6564,99 @@
         <v>1</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M80">
         <v>5</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S80">
         <v>6</v>
       </c>
       <c r="T80">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="U80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W80">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X80">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:24">
       <c r="A81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C81" t="s">
         <v>104</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G81">
         <v>3</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R81">
         <v>5</v>
@@ -6665,16 +6665,16 @@
         <v>6</v>
       </c>
       <c r="T81">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V81">
         <v>3</v>
       </c>
       <c r="W81">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X81">
         <v>4</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="82" spans="1:24">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="B82" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C82" t="s">
         <v>104</v>
@@ -6694,7 +6694,7 @@
         <v>2</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -6703,31 +6703,31 @@
         <v>2</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K82">
         <v>5</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q82">
         <v>5</v>
@@ -6739,19 +6739,19 @@
         <v>6</v>
       </c>
       <c r="T82">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="U82">
         <v>1</v>
       </c>
       <c r="V82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W82">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X82">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -76,244 +76,244 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L19</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L15</t>
   </si>
   <si>
     <t>A_L07</t>
   </si>
   <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L22</t>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L14</t>
   </si>
   <si>
     <t>B_L20</t>
   </si>
   <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>A_L25</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L22</t>
   </si>
   <si>
     <t>C_L03</t>
   </si>
   <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L18</t>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -833,22 +833,22 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -880,37 +880,37 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -1010,31 +1010,31 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1081,22 +1081,22 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1128,37 +1128,37 @@
         <v>102</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1252,37 +1252,37 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1314,37 +1314,37 @@
         <v>101</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1438,37 +1438,37 @@
         <v>102</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1515,22 +1515,22 @@
         <v>4</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1624,19 +1624,19 @@
         <v>101</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1686,19 +1686,19 @@
         <v>101</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
         <v>4</v>
@@ -1748,37 +1748,37 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1869,37 +1869,37 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -1931,37 +1931,37 @@
         <v>102</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -1993,37 +1993,37 @@
         <v>101</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2055,37 +2055,37 @@
         <v>102</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2176,37 +2176,37 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2238,37 +2238,37 @@
         <v>102</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2362,7 +2362,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2371,28 +2371,28 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2421,40 +2421,40 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2548,37 +2548,37 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2610,37 +2610,37 @@
         <v>102</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2672,37 +2672,37 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -2873,22 +2873,22 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -2920,37 +2920,37 @@
         <v>101</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -2997,22 +2997,22 @@
         <v>2</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3044,37 +3044,37 @@
         <v>102</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3106,37 +3106,37 @@
         <v>100</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3245,13 +3245,13 @@
         <v>2</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42">
         <v>7</v>
@@ -3260,7 +3260,7 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3307,22 +3307,22 @@
         <v>2</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3416,37 +3416,37 @@
         <v>102</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O45">
         <v>6</v>
@@ -3664,37 +3664,37 @@
         <v>100</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3723,7 +3723,7 @@
         <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3741,22 +3741,22 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -3791,31 +3791,31 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>6</v>
@@ -3847,37 +3847,37 @@
         <v>100</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -3974,34 +3974,34 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4219,19 +4219,19 @@
         <v>101</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58">
         <v>6</v>
@@ -4281,37 +4281,37 @@
         <v>100</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4358,22 +4358,22 @@
         <v>3</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O60">
         <v>6</v>
@@ -4405,19 +4405,19 @@
         <v>101</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61">
         <v>6</v>
@@ -4529,37 +4529,37 @@
         <v>102</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4591,37 +4591,37 @@
         <v>102</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
@@ -4715,37 +4715,37 @@
         <v>100</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
@@ -4777,37 +4777,37 @@
         <v>100</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -4963,37 +4963,37 @@
         <v>101</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
@@ -5087,37 +5087,37 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O72">
         <v>6</v>
@@ -5211,37 +5211,37 @@
         <v>100</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>7</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K74">
         <v>7</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M74">
         <v>7</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5273,22 +5273,22 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75">
         <v>7</v>
@@ -5297,10 +5297,10 @@
         <v>7</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N75">
         <v>7</v>
@@ -5335,19 +5335,19 @@
         <v>100</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76">
         <v>4</v>
@@ -5397,37 +5397,37 @@
         <v>100</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J77">
         <v>7</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>6</v>
@@ -5583,37 +5583,37 @@
         <v>102</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O80">
         <v>6</v>
@@ -5707,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -5722,22 +5722,22 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O82">
         <v>6</v>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -76,244 +76,244 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L15</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
     <t>A_L20</t>
   </si>
   <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>A_L30</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
     <t>A_L08</t>
   </si>
   <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>B_L13</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
     <t>B_L10</t>
   </si>
   <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L25</t>
+    <t>C_L27</t>
   </si>
   <si>
     <t>A_L11</t>
   </si>
   <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -759,7 +759,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -768,43 +768,43 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -821,19 +821,19 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>7</v>
@@ -842,31 +842,31 @@
         <v>7</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3">
         <v>7</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -880,55 +880,55 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -942,55 +942,52 @@
         <v>101</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>2</v>
-      </c>
-      <c r="S5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1004,52 +1001,52 @@
         <v>101</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1066,55 +1063,52 @@
         <v>102</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>3</v>
-      </c>
-      <c r="S7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1131,40 +1125,40 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1173,10 +1167,10 @@
         <v>3</v>
       </c>
       <c r="S8">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1193,16 +1187,16 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -1211,34 +1205,34 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>6</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1258,19 +1252,19 @@
         <v>4</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -1279,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>4</v>
@@ -1288,19 +1282,19 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1314,43 +1308,43 @@
         <v>101</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>3</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -1359,10 +1353,10 @@
         <v>3</v>
       </c>
       <c r="S11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1376,34 +1370,34 @@
         <v>101</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
         <v>5</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1412,19 +1406,19 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S12">
         <v>12</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1438,52 +1432,52 @@
         <v>102</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1500,43 +1494,43 @@
         <v>101</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14">
         <v>4</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1545,10 +1539,10 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1559,58 +1553,58 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1624,43 +1618,43 @@
         <v>101</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1669,10 +1663,10 @@
         <v>3</v>
       </c>
       <c r="S16">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1686,55 +1680,55 @@
         <v>101</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1748,34 +1742,34 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>4</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1784,19 +1778,19 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q18">
         <v>1</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1810,52 +1804,55 @@
         <v>102</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
+      <c r="P19">
+        <v>28</v>
+      </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>3</v>
       </c>
       <c r="S19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1869,13 +1866,13 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -1884,37 +1881,37 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
         <v>3</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="T20">
         <v>4</v>
@@ -1931,43 +1928,43 @@
         <v>102</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -1976,10 +1973,10 @@
         <v>3</v>
       </c>
       <c r="S21">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1993,34 +1990,34 @@
         <v>101</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>4</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2029,19 +2026,19 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -2055,46 +2052,46 @@
         <v>102</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23">
         <v>3</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23">
         <v>3</v>
@@ -2123,46 +2120,49 @@
         <v>2</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>4</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <v>3</v>
       </c>
       <c r="S24">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="T24">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2176,34 +2176,34 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>6</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>6</v>
@@ -2212,7 +2212,7 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q25">
         <v>2</v>
@@ -2221,10 +2221,10 @@
         <v>4</v>
       </c>
       <c r="S25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2238,10 +2238,10 @@
         <v>102</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2253,40 +2253,40 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2300,10 +2300,10 @@
         <v>102</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -2312,7 +2312,7 @@
         <v>2</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>4</v>
@@ -2336,19 +2336,19 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27">
         <v>3</v>
       </c>
       <c r="S27">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2362,55 +2362,55 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S28">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2421,37 +2421,37 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29">
         <v>5</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29">
         <v>4</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2460,27 +2460,24 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
-      <c r="S29">
-        <v>4</v>
-      </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
         <v>102</v>
@@ -2492,285 +2489,285 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
         <v>100</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:20">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
         <v>102</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>3</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
         <v>4</v>
       </c>
       <c r="S32">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
         <v>100</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>7</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q33">
         <v>1</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
         <v>102</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34">
         <v>2</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>6</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2779,60 +2776,60 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
         <v>101</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>3</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>6</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>6</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -2841,7 +2838,7 @@
         <v>4</v>
       </c>
       <c r="S35">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -2849,43 +2846,43 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
         <v>102</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>3</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>4</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N36">
         <v>4</v>
@@ -2894,116 +2891,116 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
         <v>3</v>
       </c>
       <c r="S36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
         <v>101</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="Q37">
         <v>2</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
         <v>101</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>6</v>
@@ -3018,140 +3015,140 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
         <v>102</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
         <v>100</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
         <v>3</v>
       </c>
       <c r="S40">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -3159,58 +3156,58 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
         <v>102</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J41">
         <v>6</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S41">
         <v>13</v>
@@ -3221,10 +3218,10 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
         <v>102</v>
@@ -3233,31 +3230,31 @@
         <v>2</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42">
         <v>2</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>6</v>
@@ -3269,51 +3266,51 @@
         <v>41</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S42">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43">
         <v>5</v>
       </c>
       <c r="J43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L43">
         <v>4</v>
@@ -3322,13 +3319,13 @@
         <v>4</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -3337,18 +3334,18 @@
         <v>4</v>
       </c>
       <c r="S43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
         <v>102</v>
@@ -3357,60 +3354,60 @@
         <v>3</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44">
         <v>3</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44">
         <v>5</v>
       </c>
       <c r="L44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S44">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
         <v>102</v>
@@ -3422,7 +3419,7 @@
         <v>3</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -3431,48 +3428,48 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S45">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
         <v>101</v>
@@ -3481,40 +3478,40 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3523,39 +3520,39 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C47" t="s">
         <v>102</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J47">
         <v>5</v>
@@ -3564,13 +3561,13 @@
         <v>5</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -3579,137 +3576,137 @@
         <v>34</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C48" t="s">
         <v>101</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M48">
         <v>5</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q48">
         <v>1</v>
       </c>
       <c r="R48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S48">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T48">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C49" t="s">
         <v>100</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49">
         <v>2</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J49">
         <v>6</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="T49">
         <v>4</v>
@@ -3717,137 +3714,140 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
         <v>102</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
         <v>4</v>
       </c>
       <c r="S50">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="T50">
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>101</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" t="s">
         <v>100</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3856,34 +3856,34 @@
         <v>2</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q52">
         <v>2</v>
@@ -3892,51 +3892,51 @@
         <v>3</v>
       </c>
       <c r="S52">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C53" t="s">
         <v>100</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J53">
         <v>4</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>4</v>
       </c>
       <c r="S53">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="T53">
         <v>5</v>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C54" t="s">
         <v>101</v>
@@ -3974,22 +3974,22 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>5</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K54">
         <v>6</v>
@@ -3998,7 +3998,7 @@
         <v>5</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N54">
         <v>5</v>
@@ -4007,7 +4007,7 @@
         <v>6</v>
       </c>
       <c r="P54">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4016,18 +4016,18 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T54">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
         <v>101</v>
@@ -4042,13 +4042,13 @@
         <v>2</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J55">
         <v>5</v>
@@ -4060,36 +4060,36 @@
         <v>5</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S55">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="T55">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C56" t="s">
         <v>101</v>
@@ -4101,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -4110,7 +4110,7 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J56">
         <v>5</v>
@@ -4119,28 +4119,28 @@
         <v>5</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T56">
         <v>6</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s">
         <v>101</v>
@@ -4166,34 +4166,34 @@
         <v>3</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H57">
         <v>4</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q57">
         <v>1</v>
@@ -4202,18 +4202,18 @@
         <v>3</v>
       </c>
       <c r="S57">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T57">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
         <v>101</v>
@@ -4222,190 +4222,190 @@
         <v>2</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
         <v>100</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S59">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T59">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s">
         <v>102</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T60">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
         <v>101</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4417,10 +4417,10 @@
         <v>2</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J61">
         <v>6</v>
@@ -4432,98 +4432,98 @@
         <v>6</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R61">
         <v>3</v>
       </c>
       <c r="S61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
         <v>100</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62">
         <v>6</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62">
         <v>5</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q62">
         <v>2</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
         <v>102</v>
@@ -4532,87 +4532,87 @@
         <v>2</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C64" t="s">
         <v>102</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64">
         <v>2</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L64">
         <v>4</v>
@@ -4621,13 +4621,13 @@
         <v>5</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q64">
         <v>1</v>
@@ -4636,24 +4636,24 @@
         <v>3</v>
       </c>
       <c r="S64">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="T64">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s">
         <v>100</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -4662,34 +4662,34 @@
         <v>2</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M65">
         <v>4</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q65">
         <v>1</v>
@@ -4698,142 +4698,142 @@
         <v>4</v>
       </c>
       <c r="S65">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C66" t="s">
         <v>100</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T66">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
         <v>100</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>3</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J67">
         <v>5</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
         <v>3</v>
       </c>
       <c r="S67">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="T67">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
         <v>100</v>
@@ -4845,57 +4845,57 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>2</v>
       </c>
       <c r="I68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
         <v>101</v>
@@ -4913,72 +4913,72 @@
         <v>1</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69">
         <v>4</v>
       </c>
       <c r="S69">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T69">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
         <v>101</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70">
         <v>3</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70">
         <v>4</v>
@@ -4987,19 +4987,19 @@
         <v>4</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M70">
         <v>3</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q70">
         <v>1</v>
@@ -5011,77 +5011,77 @@
         <v>18</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s">
         <v>100</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71">
         <v>4</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71">
         <v>5</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T71">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C72" t="s">
         <v>101</v>
@@ -5090,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5102,99 +5102,99 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S72">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C73" t="s">
         <v>102</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T73">
         <v>5</v>
@@ -5211,46 +5211,46 @@
         <v>100</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R74">
         <v>3</v>
@@ -5259,7 +5259,7 @@
         <v>15</v>
       </c>
       <c r="T74">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -5279,49 +5279,49 @@
         <v>2</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75">
         <v>2</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S75">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -5338,52 +5338,52 @@
         <v>4</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76">
         <v>3</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -5400,52 +5400,52 @@
         <v>2</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J77">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S77">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -5459,13 +5459,13 @@
         <v>100</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78">
         <v>3</v>
@@ -5474,28 +5474,28 @@
         <v>3</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q78">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         <v>4</v>
       </c>
       <c r="S78">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="T78">
         <v>5</v>
@@ -5521,55 +5521,55 @@
         <v>102</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M79">
         <v>6</v>
       </c>
       <c r="N79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -5583,13 +5583,13 @@
         <v>102</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -5598,40 +5598,40 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="T80">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -5645,16 +5645,16 @@
         <v>100</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -5663,37 +5663,37 @@
         <v>6</v>
       </c>
       <c r="J81">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S81">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T81">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -5707,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -5722,40 +5722,40 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K82">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S82">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T82">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -76,244 +76,244 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L15</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L30</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L19</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L28</t>
+  </si>
+  <si>
+    <t>A_L02</t>
   </si>
   <si>
     <t>C_L11</t>
   </si>
   <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>B_L07</t>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L15</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L13</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>A_L30</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L13</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -756,7 +756,7 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -765,46 +765,43 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
-      <c r="P2">
-        <v>47</v>
-      </c>
       <c r="Q2">
         <v>2</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -818,52 +815,52 @@
         <v>100</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T3">
         <v>7</v>
@@ -880,10 +877,10 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -895,40 +892,40 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -942,52 +939,55 @@
         <v>101</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="S5">
+        <v>12</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1001,43 +1001,43 @@
         <v>101</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1046,10 +1046,10 @@
         <v>4</v>
       </c>
       <c r="S6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1063,31 +1063,31 @@
         <v>102</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1099,16 +1099,19 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1122,34 +1125,34 @@
         <v>102</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -1158,19 +1161,19 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1184,55 +1187,55 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
         <v>3</v>
       </c>
       <c r="S9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1255,46 +1258,46 @@
         <v>4</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1308,52 +1311,52 @@
         <v>101</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1370,19 +1373,19 @@
         <v>101</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>5</v>
@@ -1391,13 +1394,13 @@
         <v>4</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1406,19 +1409,19 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1432,55 +1435,55 @@
         <v>102</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1494,43 +1497,43 @@
         <v>101</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1539,7 +1542,7 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14">
         <v>4</v>
@@ -1553,58 +1556,58 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1618,55 +1621,55 @@
         <v>101</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1680,55 +1683,55 @@
         <v>101</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Q17">
         <v>2</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1742,55 +1745,55 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q18">
         <v>1</v>
       </c>
       <c r="R18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1804,19 +1807,19 @@
         <v>102</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -1825,22 +1828,22 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
       <c r="P19">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -1849,10 +1852,10 @@
         <v>3</v>
       </c>
       <c r="S19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1866,52 +1869,52 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="T20">
         <v>4</v>
@@ -1928,7 +1931,7 @@
         <v>102</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1937,46 +1940,46 @@
         <v>3</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1990,25 +1993,25 @@
         <v>101</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>3</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>4</v>
@@ -2017,7 +2020,7 @@
         <v>4</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2026,19 +2029,19 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>3</v>
       </c>
       <c r="S22">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -2052,43 +2055,43 @@
         <v>102</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>4</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23">
         <v>3</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="Q23">
         <v>2</v>
@@ -2097,10 +2100,10 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -2114,28 +2117,28 @@
         <v>102</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -2150,19 +2153,19 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q24">
         <v>2</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2179,13 +2182,13 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>3</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -2194,16 +2197,16 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>5</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>6</v>
@@ -2221,10 +2224,10 @@
         <v>4</v>
       </c>
       <c r="S25">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2238,13 +2241,13 @@
         <v>102</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2253,10 +2256,10 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -2268,25 +2271,25 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2300,22 +2303,22 @@
         <v>102</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -2336,19 +2339,19 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2362,19 +2365,19 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>7</v>
@@ -2383,34 +2386,34 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>6</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2424,7 +2427,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>4</v>
@@ -2433,10 +2436,10 @@
         <v>4</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>5</v>
@@ -2448,10 +2451,10 @@
         <v>4</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2460,7 +2463,7 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -2468,70 +2471,73 @@
       <c r="R29">
         <v>3</v>
       </c>
+      <c r="S29">
+        <v>28</v>
+      </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -2551,46 +2557,46 @@
         <v>3</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31">
         <v>5</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -2610,40 +2616,40 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q32">
         <v>2</v>
@@ -2652,10 +2658,10 @@
         <v>4</v>
       </c>
       <c r="S32">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -2669,52 +2675,52 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
         <v>3</v>
       </c>
       <c r="S33">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T33">
         <v>4</v>
@@ -2731,55 +2737,55 @@
         <v>102</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M34">
         <v>6</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S34">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -2793,7 +2799,7 @@
         <v>101</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -2808,40 +2814,40 @@
         <v>3</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -2855,34 +2861,34 @@
         <v>102</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36">
         <v>4</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
         <v>4</v>
@@ -2891,19 +2897,19 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
         <v>3</v>
       </c>
       <c r="S36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -2917,7 +2923,7 @@
         <v>101</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2926,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2935,7 +2941,7 @@
         <v>5</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K37">
         <v>6</v>
@@ -2944,10 +2950,10 @@
         <v>4</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -2956,16 +2962,16 @@
         <v>33</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <v>3</v>
       </c>
       <c r="S37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -2979,13 +2985,13 @@
         <v>101</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
         <v>4</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -2994,28 +3000,28 @@
         <v>4</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q38">
         <v>1</v>
@@ -3024,10 +3030,10 @@
         <v>4</v>
       </c>
       <c r="S38">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -3041,43 +3047,43 @@
         <v>102</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q39">
         <v>1</v>
@@ -3086,10 +3092,10 @@
         <v>3</v>
       </c>
       <c r="S39">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -3118,10 +3124,10 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>6</v>
@@ -3139,19 +3145,19 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -3171,25 +3177,25 @@
         <v>2</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41">
         <v>4</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M41">
         <v>5</v>
@@ -3201,16 +3207,16 @@
         <v>6</v>
       </c>
       <c r="P41">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S41">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T41">
         <v>5</v>
@@ -3227,7 +3233,7 @@
         <v>102</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -3236,7 +3242,7 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>2</v>
@@ -3245,25 +3251,25 @@
         <v>5</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>6</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="Q42">
         <v>2</v>
@@ -3272,10 +3278,10 @@
         <v>3</v>
       </c>
       <c r="S42">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -3286,58 +3292,58 @@
         <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H43">
         <v>3</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -3354,7 +3360,7 @@
         <v>3</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -3363,43 +3369,43 @@
         <v>3</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44">
         <v>5</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S44">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="T44">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -3416,16 +3422,16 @@
         <v>3</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45">
         <v>4</v>
@@ -3434,7 +3440,7 @@
         <v>3</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L45">
         <v>3</v>
@@ -3443,13 +3449,13 @@
         <v>4</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Q45">
         <v>1</v>
@@ -3458,10 +3464,10 @@
         <v>4</v>
       </c>
       <c r="S45">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -3475,28 +3481,28 @@
         <v>101</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -3505,13 +3511,13 @@
         <v>4</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3520,10 +3526,10 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3540,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47">
         <v>2</v>
@@ -3549,25 +3555,25 @@
         <v>2</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I47">
         <v>4</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -3579,13 +3585,13 @@
         <v>1</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T47">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -3599,43 +3605,43 @@
         <v>101</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3644,10 +3650,10 @@
         <v>3</v>
       </c>
       <c r="S48">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T48">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -3661,52 +3667,49 @@
         <v>100</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M49">
         <v>5</v>
       </c>
       <c r="N49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
-      <c r="P49">
-        <v>53</v>
-      </c>
       <c r="Q49">
         <v>1</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T49">
         <v>4</v>
@@ -3723,55 +3726,55 @@
         <v>102</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>3</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q50">
         <v>2</v>
       </c>
       <c r="R50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S50">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T50">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -3785,55 +3788,55 @@
         <v>101</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>4</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51">
         <v>4</v>
       </c>
       <c r="L51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -3847,55 +3850,55 @@
         <v>100</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52">
         <v>2</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -3909,34 +3912,34 @@
         <v>100</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>6</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -3945,16 +3948,16 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S53">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="T53">
         <v>5</v>
@@ -3971,16 +3974,16 @@
         <v>101</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
         <v>2</v>
@@ -3992,22 +3995,22 @@
         <v>4</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4016,7 +4019,7 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54">
         <v>4</v>
@@ -4033,19 +4036,19 @@
         <v>101</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55">
         <v>5</v>
@@ -4057,19 +4060,19 @@
         <v>5</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4078,10 +4081,10 @@
         <v>4</v>
       </c>
       <c r="S55">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T55">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -4095,7 +4098,7 @@
         <v>101</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56">
         <v>4</v>
@@ -4107,40 +4110,40 @@
         <v>3</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56">
         <v>4</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T56">
         <v>6</v>
@@ -4157,43 +4160,43 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L57">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="Q57">
         <v>1</v>
@@ -4202,10 +4205,10 @@
         <v>3</v>
       </c>
       <c r="S57">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -4219,55 +4222,55 @@
         <v>101</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58">
         <v>4</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T58">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -4296,40 +4299,40 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L59">
         <v>7</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T59">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -4343,28 +4346,28 @@
         <v>102</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J60">
         <v>4</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L60">
         <v>4</v>
@@ -4373,25 +4376,25 @@
         <v>5</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
         <v>5</v>
       </c>
       <c r="T60">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -4405,55 +4408,55 @@
         <v>101</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S61">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -4467,7 +4470,7 @@
         <v>100</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>4</v>
@@ -4479,43 +4482,43 @@
         <v>3</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J62">
         <v>5</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="T62">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -4529,55 +4532,52 @@
         <v>102</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
-      <c r="P63">
-        <v>44</v>
-      </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -4591,22 +4591,22 @@
         <v>102</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J64">
         <v>5</v>
@@ -4615,31 +4615,31 @@
         <v>4</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M64">
         <v>5</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="Q64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -4653,19 +4653,19 @@
         <v>100</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65">
         <v>4</v>
@@ -4674,13 +4674,13 @@
         <v>5</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L65">
         <v>5</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N65">
         <v>5</v>
@@ -4689,19 +4689,19 @@
         <v>6</v>
       </c>
       <c r="P65">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -4715,55 +4715,55 @@
         <v>100</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J66">
         <v>5</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L66">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T66">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -4780,52 +4780,52 @@
         <v>2</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q67">
         <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S67">
+        <v>9</v>
+      </c>
+      <c r="T67">
         <v>8</v>
-      </c>
-      <c r="T67">
-        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -4839,13 +4839,13 @@
         <v>100</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -4860,13 +4860,13 @@
         <v>6</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L68">
         <v>6</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N68">
         <v>5</v>
@@ -4875,19 +4875,19 @@
         <v>6</v>
       </c>
       <c r="P68">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="T68">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -4901,25 +4901,25 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69">
         <v>4</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69">
         <v>4</v>
@@ -4928,7 +4928,7 @@
         <v>4</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N69">
         <v>4</v>
@@ -4937,7 +4937,7 @@
         <v>6</v>
       </c>
       <c r="P69">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -4946,10 +4946,10 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T69">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -4972,43 +4972,43 @@
         <v>3</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R70">
         <v>3</v>
       </c>
       <c r="S70">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T70">
         <v>5</v>
@@ -5025,10 +5025,10 @@
         <v>100</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>3</v>
@@ -5037,43 +5037,43 @@
         <v>4</v>
       </c>
       <c r="H71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71">
         <v>3</v>
       </c>
       <c r="S71">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T71">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -5087,55 +5087,55 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72">
         <v>3</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S72">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T72">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -5149,43 +5149,43 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73">
         <v>2</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K73">
         <v>4</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M73">
         <v>5</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="Q73">
         <v>1</v>
@@ -5194,10 +5194,10 @@
         <v>3</v>
       </c>
       <c r="S73">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -5211,52 +5211,52 @@
         <v>100</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S74">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T74">
         <v>6</v>
@@ -5273,55 +5273,55 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T75">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -5335,52 +5335,52 @@
         <v>100</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J76">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N76">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S76">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="T76">
         <v>5</v>
@@ -5397,7 +5397,7 @@
         <v>100</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>2</v>
@@ -5406,46 +5406,46 @@
         <v>1</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
         <v>4</v>
       </c>
       <c r="S77">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T77">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -5459,52 +5459,52 @@
         <v>100</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>3</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J78">
         <v>5</v>
       </c>
       <c r="K78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S78">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="T78">
         <v>5</v>
@@ -5527,13 +5527,13 @@
         <v>3</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I79">
         <v>4</v>
@@ -5545,10 +5545,10 @@
         <v>4</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -5563,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S79">
         <v>13</v>
@@ -5583,55 +5583,55 @@
         <v>102</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T80">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -5645,7 +5645,7 @@
         <v>100</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -5660,40 +5660,40 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L81">
         <v>6</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81">
         <v>3</v>
       </c>
       <c r="S81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T81">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -5707,55 +5707,55 @@
         <v>100</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K82">
         <v>7</v>
       </c>
       <c r="L82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Q82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R82">
         <v>3</v>
       </c>
       <c r="S82">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="T82">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,235 +82,235 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
     <t>A_L15</t>
   </si>
   <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L14</t>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
   </si>
   <si>
     <t>B_L09</t>
   </si>
   <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
     <t>C_L20</t>
   </si>
   <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
     <t>C_L26</t>
   </si>
   <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L18</t>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>A_L01</t>
   </si>
   <si>
     <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
   </si>
   <si>
     <t>C_L06</t>
@@ -768,61 +768,61 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,13 +836,13 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -851,46 +851,46 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -916,49 +916,49 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,13 +972,13 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -987,46 +987,46 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1040,37 +1040,37 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1082,16 +1082,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1108,61 +1108,61 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,43 +1244,43 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1289,16 +1289,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,61 +1312,58 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>5</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
-      <c r="P10">
-        <v>43</v>
-      </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1380,31 +1377,31 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1416,25 +1413,25 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1448,58 +1445,58 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1516,61 +1513,61 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1584,7 +1581,7 @@
         <v>104</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1593,52 +1590,52 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <v>3</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1652,10 +1649,10 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>2</v>
@@ -1667,43 +1664,46 @@
         <v>2</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>7.4</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,10 +1717,10 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -1735,40 +1735,40 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1785,7 +1785,7 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -1794,49 +1794,49 @@
         <v>2</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>6</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1859,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1868,28 +1868,28 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>5</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>6</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1898,16 +1898,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,37 +1921,37 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <v>4</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1960,19 +1960,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1989,58 +1989,58 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2060,10 +2060,10 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -2072,46 +2072,46 @@
         <v>2</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,55 +2128,55 @@
         <v>2</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,10 +2193,10 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -2205,49 +2205,49 @@
         <v>3</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2264,25 +2264,25 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2291,7 +2291,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2306,13 +2306,16 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="T24">
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2326,34 +2329,34 @@
         <v>103</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25">
         <v>4</v>
@@ -2362,25 +2365,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2394,10 +2397,10 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2406,10 +2409,10 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -2430,22 +2433,22 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,7 +2468,7 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -2477,43 +2480,43 @@
         <v>3</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2533,58 +2536,58 @@
         <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2598,146 +2601,146 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>4</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H30">
         <v>6</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2746,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>7</v>
@@ -2758,7 +2761,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -2770,131 +2773,131 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q31">
         <v>2</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32">
         <v>4</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>16</v>
       </c>
       <c r="V32">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>5</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -2906,7 +2909,7 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2915,30 +2918,30 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2947,25 +2950,25 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>6</v>
@@ -2974,7 +2977,7 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2983,7 +2986,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -2992,27 +2995,27 @@
         <v>12</v>
       </c>
       <c r="V34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -3021,96 +3024,96 @@
         <v>4</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>4</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3119,81 +3122,81 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>2</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3201,67 +3204,67 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38">
         <v>4</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>3</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M38">
         <v>4</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38">
         <v>3</v>
       </c>
       <c r="S38">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3269,108 +3272,108 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>3</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K40">
         <v>4</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M40">
         <v>3</v>
@@ -3382,107 +3385,107 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I41">
         <v>6</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>6</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>6</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -3491,22 +3494,22 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>7</v>
@@ -3518,22 +3521,22 @@
         <v>6</v>
       </c>
       <c r="P42">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S42">
-        <v>10.2</v>
+        <v>3.3</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V42">
         <v>4</v>
@@ -3541,10 +3544,10 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
@@ -3568,93 +3571,93 @@
         <v>5</v>
       </c>
       <c r="J43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44">
         <v>5</v>
       </c>
       <c r="N44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3663,10 +3666,10 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
         <v>13</v>
@@ -3677,78 +3680,78 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -3757,40 +3760,40 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3799,42 +3802,42 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I47">
         <v>3</v>
@@ -3843,63 +3846,63 @@
         <v>3</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L47">
         <v>4</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>12.7</v>
+        <v>5.7</v>
       </c>
       <c r="T47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>103</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -3908,25 +3911,25 @@
         <v>4</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L48">
         <v>4</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3935,92 +3938,92 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>10.6</v>
+        <v>3.6</v>
       </c>
       <c r="T48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U48">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U49">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -4041,75 +4044,75 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S50">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J51">
         <v>4</v>
@@ -4121,16 +4124,16 @@
         <v>5</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4139,149 +4142,149 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U51">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U52">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S53">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T53">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V53">
         <v>3</v>
@@ -4289,43 +4292,43 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>5</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N54">
         <v>5</v>
@@ -4334,7 +4337,7 @@
         <v>6</v>
       </c>
       <c r="P54">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4343,13 +4346,13 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="T54">
         <v>6</v>
       </c>
       <c r="U54">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4357,10 +4360,10 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -4378,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55">
         <v>7</v>
@@ -4393,42 +4396,42 @@
         <v>7</v>
       </c>
       <c r="M55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S55">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="T55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U55">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V55">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
@@ -4440,22 +4443,22 @@
         <v>4</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I56">
         <v>6</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -4464,28 +4467,28 @@
         <v>6</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="T56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V56">
         <v>3</v>
@@ -4502,58 +4505,58 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L57">
         <v>4</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S57">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="T57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U57">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4570,13 +4573,13 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -4585,43 +4588,43 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M58">
         <v>5</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U58">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4638,34 +4641,34 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>4</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H59">
         <v>4</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L59">
         <v>4</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N59">
         <v>4</v>
@@ -4674,25 +4677,25 @@
         <v>6</v>
       </c>
       <c r="P59">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S59">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="T59">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4706,28 +4709,28 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -4742,22 +4745,22 @@
         <v>6</v>
       </c>
       <c r="P60">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T60">
         <v>6</v>
       </c>
       <c r="U60">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>4</v>
@@ -4774,43 +4777,43 @@
         <v>104</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
         <v>3</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4818,14 +4821,11 @@
       <c r="R61">
         <v>3</v>
       </c>
-      <c r="S61">
-        <v>3.9</v>
-      </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4845,55 +4845,55 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
         <v>2</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J62">
         <v>6</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4916,7 +4916,7 @@
         <v>2</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -4928,40 +4928,40 @@
         <v>4</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63">
         <v>4</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,61 +4978,61 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64">
         <v>2</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S64">
-        <v>6.4</v>
+        <v>9.9</v>
       </c>
       <c r="T64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V64">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5046,61 +5046,61 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V65">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,7 +5114,7 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -5132,40 +5132,43 @@
         <v>5</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
+      <c r="P66">
+        <v>37</v>
+      </c>
       <c r="Q66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V66">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5182,13 +5185,13 @@
         <v>3</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67">
         <v>3</v>
@@ -5200,13 +5203,13 @@
         <v>6</v>
       </c>
       <c r="K67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N67">
         <v>5</v>
@@ -5215,25 +5218,25 @@
         <v>6</v>
       </c>
       <c r="P67">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q67">
         <v>2</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S67">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U67">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,58 +5250,58 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S68">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5315,61 +5318,61 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>4</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69">
         <v>4</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M69">
         <v>3</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S69">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T69">
         <v>6</v>
       </c>
       <c r="U69">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V69">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5392,49 +5395,49 @@
         <v>5</v>
       </c>
       <c r="G70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S70">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5451,43 +5454,43 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I71">
         <v>5</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M71">
         <v>5</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5496,16 +5499,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="T71">
         <v>3</v>
       </c>
       <c r="U71">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,7 +5522,7 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5534,46 +5537,46 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M72">
         <v>6</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S72">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U72">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V72">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,61 +5590,61 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,43 +5658,43 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74">
         <v>3</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74">
         <v>7</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K74">
         <v>7</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M74">
         <v>7</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q74">
         <v>2</v>
@@ -5700,16 +5703,16 @@
         <v>3</v>
       </c>
       <c r="S74">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="T74">
         <v>5</v>
       </c>
       <c r="U74">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5723,61 +5726,61 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>3</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S75">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U75">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5791,10 +5794,10 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -5806,43 +5809,43 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U76">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V76">
         <v>4</v>
@@ -5859,61 +5862,61 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>7</v>
       </c>
       <c r="J77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K77">
         <v>5</v>
       </c>
       <c r="L77">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M77">
         <v>6</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S77">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T77">
         <v>5</v>
       </c>
       <c r="U77">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5930,55 +5933,55 @@
         <v>3</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M78">
         <v>3</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S78">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T78">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V78">
         <v>3</v>
@@ -5995,16 +5998,16 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>3</v>
@@ -6013,25 +6016,25 @@
         <v>4</v>
       </c>
       <c r="J79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6040,16 +6043,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U79">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,34 +6066,34 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I80">
         <v>7</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80">
         <v>7</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N80">
         <v>6</v>
@@ -6099,25 +6102,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="T80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U80">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6131,7 +6134,7 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -6140,52 +6143,52 @@
         <v>3</v>
       </c>
       <c r="G81">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H81">
         <v>2</v>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S81">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="T81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U81">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V81">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6199,52 +6202,49 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J82">
         <v>4</v>
       </c>
       <c r="K82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R82">
-        <v>2</v>
-      </c>
-      <c r="S82">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T82">
         <v>5</v>
@@ -6253,7 +6253,7 @@
         <v>22</v>
       </c>
       <c r="V82">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,244 +82,244 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
-    <t>A_L14</t>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L19</t>
   </si>
   <si>
     <t>A_L21</t>
   </si>
   <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
   </si>
   <si>
     <t>C_L05</t>
   </si>
   <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
     <t>A_L04</t>
   </si>
   <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>A_L29</t>
   </si>
   <si>
     <t>A</t>
@@ -851,22 +851,22 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -904,37 +904,37 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -987,22 +987,22 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1312,19 +1312,19 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1392,22 +1392,22 @@
         <v>2</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1445,37 +1445,37 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1528,22 +1528,22 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1581,37 +1581,37 @@
         <v>104</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1649,37 +1649,37 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1717,19 +1717,19 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1785,37 +1785,37 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1853,37 +1853,37 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1921,37 +1921,37 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -2057,37 +2057,37 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2125,37 +2125,37 @@
         <v>103</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>7</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2193,19 +2193,19 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>4</v>
@@ -2326,7 +2326,7 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2465,37 +2465,37 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2598,40 +2598,40 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2737,37 +2737,37 @@
         <v>102</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>7</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2873,25 +2873,25 @@
         <v>102</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>7</v>
@@ -2903,7 +2903,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -3024,22 +3024,22 @@
         <v>4</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3077,37 +3077,37 @@
         <v>104</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3145,19 +3145,19 @@
         <v>103</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37">
         <v>5</v>
@@ -3290,28 +3290,28 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3349,37 +3349,37 @@
         <v>102</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3902,28 +3902,28 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -3961,19 +3961,19 @@
         <v>102</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>4</v>
@@ -4165,37 +4165,37 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -4316,22 +4316,22 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4369,37 +4369,37 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J55">
         <v>7</v>
       </c>
       <c r="K55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
@@ -4573,37 +4573,37 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O58">
         <v>6</v>
@@ -4641,37 +4641,37 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4709,37 +4709,37 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
@@ -4774,7 +4774,7 @@
         <v>80</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -4792,22 +4792,22 @@
         <v>2</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -4910,19 +4910,19 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63">
         <v>4</v>
@@ -4978,19 +4978,19 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64">
         <v>7</v>
@@ -5046,37 +5046,37 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5114,37 +5114,37 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O66">
         <v>6</v>
@@ -5179,40 +5179,40 @@
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -5333,22 +5333,22 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5386,37 +5386,37 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
@@ -5454,37 +5454,37 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O71">
         <v>6</v>
@@ -5658,37 +5658,37 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5726,37 +5726,37 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M75">
         <v>7</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5794,19 +5794,19 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I76">
         <v>3</v>
@@ -5862,37 +5862,37 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O77">
         <v>6</v>
@@ -6013,22 +6013,22 @@
         <v>3</v>
       </c>
       <c r="I79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O79">
         <v>6</v>
@@ -6066,19 +6066,19 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I80">
         <v>7</v>
@@ -6134,37 +6134,37 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L81">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N81">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O81">
         <v>6</v>
@@ -6202,37 +6202,37 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J82">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K82">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O82">
         <v>6</v>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -85,232 +85,232 @@
     <t>A_L13</t>
   </si>
   <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
     <t>A_L19</t>
   </si>
   <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L25</t>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L07</t>
   </si>
   <si>
     <t>B_L23</t>
   </si>
   <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L06</t>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
   </si>
   <si>
     <t>A_L15</t>
   </si>
   <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>A_L05</t>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L01</t>
   </si>
   <si>
     <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
   </si>
   <si>
     <t>C_L05</t>
@@ -768,34 +768,34 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
         <v>5</v>
@@ -804,25 +804,25 @@
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,61 +836,61 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,10 +904,10 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -916,49 +916,49 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -975,58 +975,58 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1040,7 +1040,7 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1061,13 +1061,13 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -1082,16 +1082,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1108,61 +1108,61 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,43 +1244,43 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1289,16 +1289,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,58 +1312,61 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>4</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>43</v>
+      </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,25 +1380,25 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1404,34 +1407,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1448,55 +1451,55 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1513,61 +1516,61 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,7 +1584,7 @@
         <v>104</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1590,52 +1593,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,10 +1652,10 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -1664,46 +1667,43 @@
         <v>4</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>2</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>2</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,10 +1717,10 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1735,40 +1735,40 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1785,7 +1785,7 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1794,49 +1794,49 @@
         <v>3</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1856,40 +1856,40 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>4</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <v>2</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1898,16 +1898,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,7 +1921,7 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1933,25 +1933,25 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1960,19 +1960,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1989,58 +1989,58 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2057,34 +2057,34 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -2093,25 +2093,25 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,58 +2125,58 @@
         <v>103</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,61 +2193,61 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>4</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>4</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2264,25 +2264,25 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2291,7 +2291,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2306,16 +2306,13 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
-      </c>
-      <c r="T24">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2329,34 +2326,34 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N25">
         <v>4</v>
@@ -2365,25 +2362,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2397,10 +2394,10 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2409,10 +2406,10 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -2433,22 +2430,22 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2468,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2480,43 +2477,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2533,61 +2530,61 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2601,273 +2598,273 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M29">
         <v>3</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>4</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31">
         <v>3</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q31">
         <v>2</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>4</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U32">
         <v>16</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
@@ -2888,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -2909,7 +2906,7 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2918,30 +2915,30 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2950,25 +2947,25 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>6</v>
@@ -2977,7 +2974,7 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2986,7 +2983,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -2995,83 +2992,83 @@
         <v>12</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>6</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
@@ -3080,40 +3077,40 @@
         <v>2</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>3</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K36">
         <v>4</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3122,81 +3119,81 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3204,67 +3201,67 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38">
         <v>3</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3272,10 +3269,10 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
@@ -3299,81 +3296,81 @@
         <v>6</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M40">
         <v>4</v>
@@ -3385,107 +3382,107 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>6</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>6</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>6</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -3494,22 +3491,22 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>7</v>
@@ -3521,22 +3518,22 @@
         <v>6</v>
       </c>
       <c r="P42">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V42">
         <v>4</v>
@@ -3544,10 +3541,10 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
@@ -3571,93 +3568,93 @@
         <v>5</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
         <v>5</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3666,10 +3663,10 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>13</v>
@@ -3680,78 +3677,78 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -3760,40 +3757,40 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3802,134 +3799,134 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S47">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
         <v>103</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3938,92 +3935,92 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>10.6</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -4044,75 +4041,75 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51">
         <v>4</v>
@@ -4124,16 +4121,16 @@
         <v>5</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4142,36 +4139,36 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -4180,111 +4177,111 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S53">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T53">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U53">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V53">
         <v>3</v>
@@ -4292,52 +4289,52 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4346,13 +4343,13 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="T54">
         <v>6</v>
       </c>
       <c r="U54">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4360,10 +4357,10 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -4372,31 +4369,31 @@
         <v>2</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>6</v>
       </c>
       <c r="J55">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N55">
         <v>5</v>
@@ -4405,33 +4402,33 @@
         <v>6</v>
       </c>
       <c r="P55">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>7.3</v>
+        <v>10.3</v>
       </c>
       <c r="T55">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U55">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
@@ -4443,22 +4440,22 @@
         <v>4</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I56">
         <v>6</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -4467,28 +4464,28 @@
         <v>6</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U56">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V56">
         <v>3</v>
@@ -4505,58 +4502,58 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="T57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U57">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4573,58 +4570,58 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U58">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4644,13 +4641,13 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -4668,7 +4665,7 @@
         <v>7</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N59">
         <v>7</v>
@@ -4677,25 +4674,25 @@
         <v>6</v>
       </c>
       <c r="P59">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U59">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V59">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4709,58 +4706,58 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T60">
         <v>6</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="V60">
         <v>4</v>
@@ -4780,40 +4777,40 @@
         <v>3</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4821,11 +4818,14 @@
       <c r="R61">
         <v>3</v>
       </c>
+      <c r="S61">
+        <v>3.9</v>
+      </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4845,55 +4845,55 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62">
         <v>2</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62">
         <v>6</v>
       </c>
       <c r="K62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>10.6</v>
+        <v>9.4</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4910,58 +4910,58 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K63">
         <v>4</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M63">
         <v>5</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,13 +4978,13 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -4993,46 +4993,46 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>9.9</v>
+        <v>6.4</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U64">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5049,58 +5049,58 @@
         <v>4</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H65">
         <v>4</v>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K65">
         <v>3</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,7 +5114,7 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <v>2</v>
@@ -5132,43 +5132,40 @@
         <v>6</v>
       </c>
       <c r="J66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
-      <c r="P66">
-        <v>37</v>
-      </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U66">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5203,13 +5200,13 @@
         <v>7</v>
       </c>
       <c r="K67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N67">
         <v>7</v>
@@ -5218,25 +5215,25 @@
         <v>6</v>
       </c>
       <c r="P67">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q67">
         <v>2</v>
       </c>
       <c r="R67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5250,58 +5247,58 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I68">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5321,58 +5318,58 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69">
         <v>5</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T69">
         <v>6</v>
       </c>
       <c r="U69">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5395,49 +5392,49 @@
         <v>3</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5460,37 +5457,37 @@
         <v>2</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5499,16 +5496,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="T71">
         <v>3</v>
       </c>
       <c r="U71">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5522,7 +5519,7 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5537,46 +5534,46 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72">
         <v>6</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S72">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5590,61 +5587,61 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S73">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5658,34 +5655,34 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -5694,7 +5691,7 @@
         <v>6</v>
       </c>
       <c r="P74">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q74">
         <v>2</v>
@@ -5703,16 +5700,16 @@
         <v>3</v>
       </c>
       <c r="S74">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="T74">
         <v>5</v>
       </c>
       <c r="U74">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5726,34 +5723,34 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75">
         <v>2</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N75">
         <v>6</v>
@@ -5762,25 +5759,25 @@
         <v>6</v>
       </c>
       <c r="P75">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U75">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,7 +5791,7 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76">
         <v>2</v>
@@ -5803,49 +5800,49 @@
         <v>1</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="T76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V76">
         <v>4</v>
@@ -5862,61 +5859,61 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S77">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T77">
         <v>5</v>
       </c>
       <c r="U77">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5933,55 +5930,55 @@
         <v>3</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M78">
         <v>3</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T78">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U78">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V78">
         <v>3</v>
@@ -5998,25 +5995,25 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79">
         <v>3</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K79">
         <v>4</v>
@@ -6028,13 +6025,13 @@
         <v>4</v>
       </c>
       <c r="N79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6043,16 +6040,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V79">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6066,34 +6063,34 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>7</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
         <v>7</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N80">
         <v>6</v>
@@ -6102,25 +6099,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U80">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,7 +6131,7 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>2</v>
@@ -6143,52 +6140,52 @@
         <v>2</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="T81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U81">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V81">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6202,49 +6199,52 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K82">
         <v>6</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="S82">
+        <v>5.3</v>
       </c>
       <c r="T82">
         <v>5</v>
@@ -6253,7 +6253,7 @@
         <v>22</v>
       </c>
       <c r="V82">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,244 +82,244 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L18</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
   </si>
   <si>
     <t>A_L07</t>
   </si>
   <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L09</t>
   </si>
   <si>
     <t>C_L12</t>
   </si>
   <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L10</t>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L05</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -768,61 +768,61 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,61 +836,61 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,25 +904,25 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -931,34 +931,34 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,13 +972,13 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -987,46 +987,46 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1040,19 +1040,19 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -1061,13 +1061,13 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -1082,16 +1082,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1120,49 +1120,49 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,43 +1244,43 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1289,16 +1289,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,61 +1312,58 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>4</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
-      <c r="P10">
-        <v>43</v>
-      </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1380,25 +1377,25 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1407,34 +1404,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1448,58 +1445,58 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>6</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>5</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1516,34 +1513,34 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N13">
         <v>5</v>
@@ -1552,25 +1549,25 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,10 +1578,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1593,52 +1590,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1652,58 +1649,61 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>7.4</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,58 +1717,58 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1785,7 +1785,7 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1794,49 +1794,49 @@
         <v>3</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,43 +1853,43 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1898,16 +1898,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,7 +1921,7 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1933,25 +1933,25 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1960,19 +1960,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1989,58 +1989,58 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2057,34 +2057,34 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -2093,25 +2093,25 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,58 +2125,58 @@
         <v>103</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,61 +2193,61 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>5</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2264,34 +2264,34 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2306,13 +2306,16 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="T24">
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2326,61 +2329,61 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2406,46 +2409,46 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>5</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,7 +2468,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2477,43 +2480,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2530,61 +2533,61 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2595,208 +2598,208 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q31">
         <v>2</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
@@ -2808,10 +2811,10 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2820,75 +2823,75 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>6</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>5</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>16</v>
       </c>
       <c r="V32">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>7</v>
@@ -2900,13 +2903,13 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2915,30 +2918,30 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2947,25 +2950,25 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>6</v>
@@ -2974,7 +2977,7 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2983,7 +2986,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -2992,125 +2995,125 @@
         <v>12</v>
       </c>
       <c r="V34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3119,81 +3122,81 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3201,67 +3204,67 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38">
         <v>3</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>6</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38">
         <v>3</v>
       </c>
       <c r="S38">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3269,10 +3272,10 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
@@ -3296,81 +3299,81 @@
         <v>6</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>4</v>
@@ -3382,107 +3385,107 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -3491,22 +3494,22 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>7</v>
@@ -3518,22 +3521,22 @@
         <v>6</v>
       </c>
       <c r="P42">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S42">
-        <v>10.2</v>
+        <v>3.3</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V42">
         <v>4</v>
@@ -3541,10 +3544,10 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
@@ -3562,99 +3565,99 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44">
         <v>5</v>
       </c>
       <c r="N44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3663,10 +3666,10 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
         <v>13</v>
@@ -3677,78 +3680,78 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -3757,40 +3760,40 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3799,101 +3802,101 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="T47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>103</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3908,25 +3911,25 @@
         <v>5</v>
       </c>
       <c r="J48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L48">
         <v>5</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3935,181 +3938,181 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>10.6</v>
+        <v>3.6</v>
       </c>
       <c r="T48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U48">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U49">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S50">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J51">
         <v>4</v>
@@ -4121,16 +4124,16 @@
         <v>5</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4139,36 +4142,36 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U51">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -4177,13 +4180,13 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52">
         <v>4</v>
@@ -4192,96 +4195,96 @@
         <v>4</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U52">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S53">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T53">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V53">
         <v>3</v>
@@ -4289,43 +4292,43 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>6</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N54">
         <v>6</v>
@@ -4334,7 +4337,7 @@
         <v>6</v>
       </c>
       <c r="P54">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4343,13 +4346,13 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="T54">
         <v>6</v>
       </c>
       <c r="U54">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4357,10 +4360,10 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -4369,22 +4372,22 @@
         <v>2</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K55">
         <v>5</v>
@@ -4393,75 +4396,75 @@
         <v>5</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S55">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="T55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U55">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V55">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56">
         <v>3</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N56">
         <v>7</v>
@@ -4470,22 +4473,22 @@
         <v>6</v>
       </c>
       <c r="P56">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="T56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V56">
         <v>3</v>
@@ -4502,10 +4505,10 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57">
         <v>5</v>
@@ -4514,46 +4517,46 @@
         <v>5</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57">
         <v>2</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S57">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="T57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U57">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4570,13 +4573,13 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -4585,43 +4588,43 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M58">
         <v>5</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U58">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4638,61 +4641,61 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S59">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="T59">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4706,58 +4709,58 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T60">
         <v>6</v>
       </c>
       <c r="U60">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>4</v>
@@ -4774,43 +4777,43 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61">
         <v>4</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4818,14 +4821,11 @@
       <c r="R61">
         <v>3</v>
       </c>
-      <c r="S61">
-        <v>3.9</v>
-      </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4842,58 +4842,58 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4910,58 +4910,58 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,61 +4978,61 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64">
         <v>2</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S64">
-        <v>6.4</v>
+        <v>9.9</v>
       </c>
       <c r="T64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V64">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5046,61 +5046,61 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V65">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,58 +5114,61 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J66">
         <v>5</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M66">
         <v>5</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
+      <c r="P66">
+        <v>37</v>
+      </c>
       <c r="Q66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V66">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5179,61 +5182,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q67">
         <v>2</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S67">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U67">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,58 +5250,58 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S68">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5318,58 +5321,58 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>5</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K69">
         <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M69">
         <v>4</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S69">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T69">
         <v>6</v>
       </c>
       <c r="U69">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V69">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5392,49 +5395,49 @@
         <v>3</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S70">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5457,37 +5460,37 @@
         <v>2</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5496,16 +5499,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="T71">
         <v>3</v>
       </c>
       <c r="U71">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,7 +5522,7 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5534,46 +5537,46 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K72">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S72">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U72">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V72">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5596,19 +5599,19 @@
         <v>1</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73">
         <v>5</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L73">
         <v>6</v>
@@ -5623,25 +5626,25 @@
         <v>6</v>
       </c>
       <c r="P73">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,43 +5658,43 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74">
         <v>3</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74">
         <v>7</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K74">
         <v>7</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M74">
         <v>7</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q74">
         <v>2</v>
@@ -5700,16 +5703,16 @@
         <v>3</v>
       </c>
       <c r="S74">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="T74">
         <v>5</v>
       </c>
       <c r="U74">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5729,55 +5732,55 @@
         <v>3</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G75">
         <v>3</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L75">
         <v>5</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S75">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U75">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,55 +5797,55 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U76">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V76">
         <v>4</v>
@@ -5859,61 +5862,61 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>6</v>
       </c>
       <c r="J77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K77">
         <v>4</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M77">
         <v>5</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S77">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T77">
         <v>5</v>
       </c>
       <c r="U77">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5930,19 +5933,19 @@
         <v>3</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J78">
         <v>3</v>
@@ -5954,7 +5957,7 @@
         <v>4</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N78">
         <v>4</v>
@@ -5963,22 +5966,22 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S78">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T78">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V78">
         <v>3</v>
@@ -5995,43 +5998,43 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6040,16 +6043,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U79">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,34 +6066,34 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I80">
         <v>7</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80">
         <v>7</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N80">
         <v>6</v>
@@ -6099,25 +6102,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="T80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U80">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,58 +6137,58 @@
         <v>2</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J81">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K81">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L81">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S81">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="T81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U81">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V81">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6199,52 +6202,49 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L82">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N82">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R82">
-        <v>2</v>
-      </c>
-      <c r="S82">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T82">
         <v>5</v>
@@ -6253,7 +6253,7 @@
         <v>22</v>
       </c>
       <c r="V82">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,244 +82,244 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
-    <t>A_L19</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
   </si>
   <si>
     <t>A_L08</t>
   </si>
   <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L18</t>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
   </si>
   <si>
     <t>C_L26</t>
   </si>
   <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L05</t>
   </si>
   <si>
     <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -768,61 +768,61 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
         <v>4</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,61 +836,61 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,25 +904,25 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -931,34 +931,34 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,13 +972,13 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -987,46 +987,46 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1040,7 +1040,7 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1055,22 +1055,22 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1082,16 +1082,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1108,16 +1108,16 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1126,43 +1126,43 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,43 +1244,43 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1289,16 +1289,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,58 +1312,61 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>5</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>43</v>
+      </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,25 +1380,25 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1404,34 +1407,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,58 +1448,58 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1513,34 +1516,34 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>5</v>
@@ -1549,25 +1552,25 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1578,10 +1581,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1590,52 +1593,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,61 +1652,58 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,10 +1717,10 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -1735,40 +1735,40 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1785,58 +1785,58 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1856,40 +1856,40 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1898,16 +1898,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,7 +1921,7 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1933,22 +1933,22 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1960,19 +1960,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1989,58 +1989,58 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2057,22 +2057,22 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -2081,37 +2081,37 @@
         <v>4</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,55 +2128,55 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,61 +2193,61 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>5</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>5</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2264,34 +2264,34 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2306,16 +2306,13 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
-      </c>
-      <c r="T24">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2329,61 +2326,61 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2397,10 +2394,10 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2409,46 +2406,46 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2468,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2480,43 +2477,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K27">
         <v>3</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2533,10 +2530,10 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2545,49 +2542,49 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2601,137 +2598,137 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I29">
         <v>5</v>
       </c>
       <c r="J29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
@@ -2746,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -2761,7 +2758,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -2773,143 +2770,143 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q31">
         <v>2</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U32">
         <v>16</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2918,24 +2915,24 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
@@ -2956,19 +2953,19 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>6</v>
@@ -2977,7 +2974,7 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2986,7 +2983,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -2995,83 +2992,83 @@
         <v>12</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
@@ -3086,19 +3083,19 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -3113,7 +3110,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3122,81 +3119,81 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3204,10 +3201,10 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
@@ -3219,7 +3216,7 @@
         <v>3</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -3228,10 +3225,10 @@
         <v>3</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>4</v>
@@ -3240,31 +3237,31 @@
         <v>5</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38">
         <v>3</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3272,108 +3269,108 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
         <v>6</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M40">
         <v>4</v>
@@ -3385,107 +3382,107 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I41">
         <v>5</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>5</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -3494,22 +3491,22 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>7</v>
@@ -3521,22 +3518,22 @@
         <v>6</v>
       </c>
       <c r="P42">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V42">
         <v>4</v>
@@ -3544,10 +3541,10 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
@@ -3565,57 +3562,57 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
@@ -3633,31 +3630,31 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>5</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L44">
         <v>6</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3666,10 +3663,10 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>13</v>
@@ -3680,78 +3677,78 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -3760,40 +3757,40 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3802,101 +3799,101 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S47">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
         <v>103</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3911,25 +3908,25 @@
         <v>5</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L48">
         <v>5</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3938,24 +3935,24 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>10.6</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
@@ -3964,7 +3961,7 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -3976,143 +3973,143 @@
         <v>2</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51">
         <v>4</v>
@@ -4124,16 +4121,16 @@
         <v>5</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4142,36 +4139,36 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -4180,111 +4177,111 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S53">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T53">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U53">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V53">
         <v>3</v>
@@ -4292,43 +4289,43 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>6</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N54">
         <v>6</v>
@@ -4337,7 +4334,7 @@
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4346,13 +4343,13 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="T54">
         <v>6</v>
       </c>
       <c r="U54">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4360,10 +4357,10 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -4372,22 +4369,22 @@
         <v>2</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55">
         <v>5</v>
@@ -4396,42 +4393,42 @@
         <v>5</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>7.3</v>
+        <v>10.3</v>
       </c>
       <c r="T55">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U55">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
@@ -4443,28 +4440,28 @@
         <v>3</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N56">
         <v>7</v>
@@ -4473,22 +4470,22 @@
         <v>6</v>
       </c>
       <c r="P56">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U56">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V56">
         <v>3</v>
@@ -4508,55 +4505,55 @@
         <v>4</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H57">
         <v>5</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57">
         <v>2</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="T57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U57">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4576,55 +4573,55 @@
         <v>2</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M58">
         <v>5</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U58">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4644,58 +4641,58 @@
         <v>3</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59">
         <v>6</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U59">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V59">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4712,55 +4709,55 @@
         <v>4</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T60">
         <v>6</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="V60">
         <v>4</v>
@@ -4777,13 +4774,13 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G61">
         <v>3</v>
@@ -4792,28 +4789,28 @@
         <v>3</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4821,11 +4818,14 @@
       <c r="R61">
         <v>3</v>
       </c>
+      <c r="S61">
+        <v>3.9</v>
+      </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4845,55 +4845,55 @@
         <v>3</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62">
         <v>3</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62">
         <v>5</v>
       </c>
       <c r="K62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>10.6</v>
+        <v>9.4</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4910,58 +4910,58 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M63">
         <v>4</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,61 +4978,61 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64">
         <v>2</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>9.9</v>
+        <v>6.4</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U64">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5055,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -5064,43 +5064,43 @@
         <v>6</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M65">
         <v>7</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,7 +5114,7 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66">
         <v>4</v>
@@ -5132,43 +5132,40 @@
         <v>4</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
-      <c r="P66">
-        <v>37</v>
-      </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U66">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5179,64 +5176,64 @@
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K67">
         <v>5</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q67">
         <v>2</v>
       </c>
       <c r="R67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5250,19 +5247,19 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I68">
         <v>6</v>
@@ -5274,34 +5271,34 @@
         <v>5</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5321,58 +5318,58 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
         <v>5</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69">
         <v>5</v>
       </c>
       <c r="L69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M69">
         <v>4</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T69">
         <v>6</v>
       </c>
       <c r="U69">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5395,49 +5392,49 @@
         <v>3</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5460,37 +5457,37 @@
         <v>2</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K71">
         <v>5</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5499,16 +5496,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="T71">
         <v>3</v>
       </c>
       <c r="U71">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5534,49 +5531,49 @@
         <v>1</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72">
         <v>5</v>
       </c>
       <c r="N72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S72">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5590,61 +5587,61 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S73">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5658,43 +5655,43 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74">
         <v>3</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74">
         <v>7</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K74">
         <v>7</v>
       </c>
       <c r="L74">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M74">
         <v>7</v>
       </c>
       <c r="N74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q74">
         <v>2</v>
@@ -5703,16 +5700,16 @@
         <v>3</v>
       </c>
       <c r="S74">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="T74">
         <v>5</v>
       </c>
       <c r="U74">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5732,55 +5729,55 @@
         <v>3</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G75">
         <v>3</v>
       </c>
       <c r="H75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L75">
         <v>5</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U75">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,10 +5791,10 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -5809,43 +5806,43 @@
         <v>3</v>
       </c>
       <c r="I76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="T76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V76">
         <v>4</v>
@@ -5862,61 +5859,61 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J77">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S77">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T77">
         <v>5</v>
       </c>
       <c r="U77">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5933,19 +5930,19 @@
         <v>3</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J78">
         <v>3</v>
@@ -5957,7 +5954,7 @@
         <v>4</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N78">
         <v>4</v>
@@ -5966,22 +5963,22 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T78">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U78">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V78">
         <v>3</v>
@@ -5998,43 +5995,43 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6043,16 +6040,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V79">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6066,34 +6063,34 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>7</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
         <v>7</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N80">
         <v>6</v>
@@ -6102,25 +6099,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U80">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,7 +6131,7 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -6143,52 +6140,52 @@
         <v>3</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H81">
         <v>2</v>
       </c>
       <c r="I81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K81">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L81">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="T81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U81">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V81">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6202,49 +6199,52 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L82">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N82">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="S82">
+        <v>5.3</v>
       </c>
       <c r="T82">
         <v>5</v>
@@ -6253,7 +6253,7 @@
         <v>22</v>
       </c>
       <c r="V82">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,244 +82,244 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>B_L07</t>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L05</t>
   </si>
   <si>
     <t>A_L05</t>
   </si>
   <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
     <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -768,61 +768,61 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>4</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,61 +836,61 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,10 +904,10 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -916,49 +916,49 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -975,58 +975,58 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1040,37 +1040,37 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1082,16 +1082,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1120,49 +1120,49 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1179,19 +1179,19 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>4</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1212,25 +1212,25 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,43 +1244,43 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1289,16 +1289,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,58 +1312,61 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>5</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>43</v>
+      </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,25 +1380,25 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1404,34 +1407,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,7 +1448,7 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1454,49 +1457,49 @@
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1513,61 +1516,61 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,7 +1584,7 @@
         <v>104</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1590,52 +1593,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,61 +1652,58 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>2</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>2</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,58 +1717,58 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1785,58 +1785,58 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,34 +1853,34 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18">
         <v>4</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1889,7 +1889,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1898,16 +1898,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,7 +1921,7 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1933,22 +1933,22 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1960,19 +1960,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1989,58 +1989,58 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2057,22 +2057,22 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -2081,37 +2081,37 @@
         <v>4</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,55 +2128,55 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,61 +2193,61 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>4</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>4</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2264,25 +2264,25 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2291,7 +2291,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2306,16 +2306,13 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
-      </c>
-      <c r="T24">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2329,61 +2326,61 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2409,46 +2406,46 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2468,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2480,43 +2477,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K27">
         <v>3</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2533,10 +2530,10 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2545,49 +2542,49 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2598,37 +2595,37 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2637,169 +2634,169 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>4</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>7</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>6</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q31">
         <v>2</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
@@ -2811,105 +2808,105 @@
         <v>4</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32">
         <v>3</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U32">
         <v>16</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2918,24 +2915,24 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
@@ -2956,19 +2953,19 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>6</v>
@@ -2977,7 +2974,7 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2986,7 +2983,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -2995,89 +2992,89 @@
         <v>12</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>6</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3086,34 +3083,34 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>5</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3122,81 +3119,81 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3204,67 +3201,67 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38">
         <v>4</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38">
         <v>3</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>4</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38">
         <v>3</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3272,108 +3269,108 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
         <v>6</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M40">
         <v>4</v>
@@ -3385,66 +3382,66 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J41">
         <v>5</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>5</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N41">
         <v>5</v>
@@ -3453,39 +3450,39 @@
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -3494,22 +3491,22 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>7</v>
@@ -3521,22 +3518,22 @@
         <v>6</v>
       </c>
       <c r="P42">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V42">
         <v>4</v>
@@ -3544,10 +3541,10 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
@@ -3571,51 +3568,51 @@
         <v>5</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
@@ -3633,31 +3630,31 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>5</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L44">
         <v>6</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3666,10 +3663,10 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>13</v>
@@ -3680,78 +3677,78 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -3760,40 +3757,40 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3802,134 +3799,134 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S47">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
         <v>103</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3938,24 +3935,24 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>10.6</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
@@ -3964,7 +3961,7 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -3976,54 +3973,54 @@
         <v>2</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -4044,75 +4041,75 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51">
         <v>4</v>
@@ -4124,16 +4121,16 @@
         <v>5</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4142,36 +4139,36 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -4180,111 +4177,111 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S53">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T53">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U53">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V53">
         <v>3</v>
@@ -4292,52 +4289,52 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4346,13 +4343,13 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="T54">
         <v>6</v>
       </c>
       <c r="U54">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4360,10 +4357,10 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -4372,31 +4369,31 @@
         <v>2</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>6</v>
       </c>
       <c r="J55">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N55">
         <v>5</v>
@@ -4405,60 +4402,60 @@
         <v>6</v>
       </c>
       <c r="P55">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>7.3</v>
+        <v>10.3</v>
       </c>
       <c r="T55">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U55">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>6</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -4467,28 +4464,28 @@
         <v>6</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U56">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V56">
         <v>3</v>
@@ -4505,58 +4502,58 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="T57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U57">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4573,58 +4570,58 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U58">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4641,61 +4638,61 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59">
         <v>7</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M59">
         <v>6</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U59">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V59">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4712,55 +4709,55 @@
         <v>4</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T60">
         <v>6</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="V60">
         <v>4</v>
@@ -4777,43 +4774,43 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61">
         <v>3</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4821,11 +4818,14 @@
       <c r="R61">
         <v>3</v>
       </c>
+      <c r="S61">
+        <v>3.9</v>
+      </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4842,7 +4842,7 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -4851,7 +4851,7 @@
         <v>2</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62">
         <v>2</v>
@@ -4860,7 +4860,7 @@
         <v>5</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62">
         <v>4</v>
@@ -4869,31 +4869,31 @@
         <v>4</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>10.6</v>
+        <v>9.4</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4916,7 +4916,7 @@
         <v>3</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G63">
         <v>3</v>
@@ -4928,40 +4928,40 @@
         <v>4</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L63">
         <v>4</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,13 +4978,13 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -4993,46 +4993,46 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>9.9</v>
+        <v>6.4</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U64">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5046,61 +5046,61 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,61 +5114,58 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
-      <c r="P66">
-        <v>37</v>
-      </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U66">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5179,10 +5176,10 @@
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -5194,49 +5191,49 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J67">
         <v>7</v>
       </c>
       <c r="K67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M67">
         <v>6</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q67">
         <v>2</v>
       </c>
       <c r="R67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5250,58 +5247,58 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5321,58 +5318,58 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69">
         <v>5</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T69">
         <v>6</v>
       </c>
       <c r="U69">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5395,49 +5392,49 @@
         <v>3</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5460,37 +5457,37 @@
         <v>2</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K71">
         <v>5</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5499,16 +5496,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="T71">
         <v>3</v>
       </c>
       <c r="U71">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5534,22 +5531,22 @@
         <v>1</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72">
         <v>5</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L72">
         <v>5</v>
       </c>
       <c r="M72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N72">
         <v>5</v>
@@ -5558,25 +5555,25 @@
         <v>6</v>
       </c>
       <c r="P72">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S72">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5590,28 +5587,28 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73">
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73">
         <v>2</v>
@@ -5626,25 +5623,25 @@
         <v>6</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S73">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5658,34 +5655,34 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -5694,7 +5691,7 @@
         <v>6</v>
       </c>
       <c r="P74">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q74">
         <v>2</v>
@@ -5703,16 +5700,16 @@
         <v>3</v>
       </c>
       <c r="S74">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="T74">
         <v>5</v>
       </c>
       <c r="U74">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5726,34 +5723,34 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75">
         <v>2</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N75">
         <v>6</v>
@@ -5762,25 +5759,25 @@
         <v>6</v>
       </c>
       <c r="P75">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U75">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,19 +5791,19 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I76">
         <v>3</v>
@@ -5818,34 +5815,34 @@
         <v>3</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="T76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V76">
         <v>4</v>
@@ -5871,52 +5868,52 @@
         <v>2</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77">
         <v>2</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S77">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T77">
         <v>5</v>
       </c>
       <c r="U77">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5933,55 +5930,55 @@
         <v>3</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M78">
         <v>3</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T78">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U78">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V78">
         <v>3</v>
@@ -6010,31 +6007,31 @@
         <v>2</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79">
         <v>5</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6043,16 +6040,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V79">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6066,34 +6063,34 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>7</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
         <v>7</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N80">
         <v>6</v>
@@ -6102,25 +6099,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U80">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,31 +6131,31 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81">
         <v>5</v>
       </c>
       <c r="J81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M81">
         <v>6</v>
@@ -6170,25 +6167,25 @@
         <v>6</v>
       </c>
       <c r="P81">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="T81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U81">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V81">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6202,49 +6199,52 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K82">
         <v>6</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="S82">
+        <v>5.3</v>
       </c>
       <c r="T82">
         <v>5</v>
@@ -6253,7 +6253,7 @@
         <v>22</v>
       </c>
       <c r="V82">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -88,238 +88,238 @@
     <t>A_L20</t>
   </si>
   <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
     <t>A_L09</t>
   </si>
   <si>
-    <t>B_L11</t>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
   </si>
   <si>
     <t>B_L07</t>
   </si>
   <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
   </si>
   <si>
     <t>A_L29</t>
   </si>
   <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L20</t>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
   </si>
   <si>
     <t>B_L12</t>
   </si>
   <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L23</t>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L13</t>
   </si>
   <si>
     <t>B_L16</t>
   </si>
   <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L13</t>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L05</t>
   </si>
   <si>
     <t>A_L04</t>
   </si>
   <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>A_L28</t>
+    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -771,13 +771,13 @@
         <v>4</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -792,13 +792,13 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -836,7 +836,7 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -845,16 +845,16 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -866,7 +866,7 @@
         <v>7</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -907,34 +907,34 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -972,13 +972,13 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -990,13 +990,13 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -1049,25 +1049,25 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>6</v>
@@ -1123,10 +1123,10 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1135,7 +1135,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -1176,37 +1176,37 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1244,37 +1244,37 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1315,7 +1315,7 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -1324,25 +1324,25 @@
         <v>3</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1386,31 +1386,31 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>3</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1448,34 +1448,34 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>7</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>6</v>
@@ -1516,37 +1516,37 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1593,19 +1593,19 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1652,7 +1652,7 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1670,10 +1670,10 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1682,7 +1682,7 @@
         <v>2</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1717,37 +1717,37 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16">
         <v>5</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -1785,10 +1785,10 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <v>4</v>
@@ -1800,22 +1800,22 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1859,25 +1859,25 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -1936,22 +1936,22 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -2001,25 +2001,25 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>7</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2057,19 +2057,19 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2081,13 +2081,13 @@
         <v>4</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2131,7 +2131,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2140,22 +2140,22 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>3</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2193,34 +2193,34 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>4</v>
@@ -2261,37 +2261,37 @@
         <v>104</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>3</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M24">
         <v>4</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2326,37 +2326,37 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2394,34 +2394,34 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N26">
         <v>4</v>
@@ -2462,19 +2462,19 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27">
         <v>3</v>
@@ -2483,16 +2483,16 @@
         <v>2</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M27">
         <v>3</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2530,7 +2530,7 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2542,25 +2542,25 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>4</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2604,31 +2604,31 @@
         <v>4</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2675,19 +2675,19 @@
         <v>2</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>4</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -2743,25 +2743,25 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>7</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>7</v>
@@ -2802,37 +2802,37 @@
         <v>104</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>3</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32">
         <v>2</v>
       </c>
       <c r="K32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2873,31 +2873,31 @@
         <v>4</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>5</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -2938,37 +2938,37 @@
         <v>104</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>6</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3006,37 +3006,37 @@
         <v>103</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35">
         <v>7</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>6</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>6</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3077,34 +3077,34 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>5</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M36">
         <v>5</v>
       </c>
       <c r="N36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3145,7 +3145,7 @@
         <v>2</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -3154,7 +3154,7 @@
         <v>3</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37">
         <v>3</v>
@@ -3163,16 +3163,16 @@
         <v>2</v>
       </c>
       <c r="K37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -3210,37 +3210,37 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3281,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -3290,19 +3290,19 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>6</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>7</v>
@@ -3352,31 +3352,31 @@
         <v>2</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40">
         <v>2</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L40">
         <v>3</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3414,37 +3414,37 @@
         <v>104</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M41">
         <v>5</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3482,13 +3482,13 @@
         <v>104</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42">
         <v>2</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -3497,13 +3497,13 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42">
         <v>7</v>
@@ -3512,7 +3512,7 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3556,31 +3556,31 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K43">
         <v>3</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3621,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3630,25 +3630,25 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J44">
         <v>7</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44">
         <v>6</v>
       </c>
       <c r="M44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O44">
         <v>6</v>
@@ -3686,13 +3686,13 @@
         <v>104</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -3701,7 +3701,7 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J45">
         <v>5</v>
@@ -3710,10 +3710,10 @@
         <v>4</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N45">
         <v>4</v>
@@ -3754,7 +3754,7 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -3763,22 +3763,22 @@
         <v>3</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K46">
         <v>6</v>
       </c>
       <c r="L46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M46">
         <v>6</v>
@@ -3822,37 +3822,37 @@
         <v>104</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47">
         <v>3</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47">
         <v>4</v>
       </c>
       <c r="K47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -3893,22 +3893,22 @@
         <v>2</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48">
         <v>7</v>
@@ -3961,16 +3961,16 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49">
         <v>2</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>7</v>
@@ -4044,19 +4044,19 @@
         <v>5</v>
       </c>
       <c r="J50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M50">
         <v>5</v>
       </c>
       <c r="N50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -4103,28 +4103,28 @@
         <v>2</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L51">
         <v>5</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O51">
         <v>6</v>
@@ -4168,10 +4168,10 @@
         <v>2</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -4183,13 +4183,13 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L52">
         <v>2</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N52">
         <v>3</v>
@@ -4298,34 +4298,34 @@
         <v>103</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N54">
         <v>6</v>
@@ -4366,28 +4366,28 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -4434,34 +4434,34 @@
         <v>103</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56">
         <v>6</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N56">
         <v>7</v>
@@ -4502,19 +4502,19 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57">
         <v>5</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I57">
         <v>1</v>
@@ -4526,10 +4526,10 @@
         <v>2</v>
       </c>
       <c r="L57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N57">
         <v>2</v>
@@ -4570,10 +4570,10 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4585,16 +4585,16 @@
         <v>2</v>
       </c>
       <c r="I58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M58">
         <v>5</v>
@@ -4638,10 +4638,10 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -4650,25 +4650,25 @@
         <v>3</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K59">
         <v>6</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4706,7 +4706,7 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -4715,22 +4715,22 @@
         <v>3</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60">
         <v>4</v>
       </c>
       <c r="J60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M60">
         <v>5</v>
@@ -4774,25 +4774,25 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61">
         <v>6</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K61">
         <v>6</v>
@@ -4801,10 +4801,10 @@
         <v>6</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -4842,37 +4842,37 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M62">
         <v>6</v>
       </c>
       <c r="N62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4910,37 +4910,37 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4978,7 +4978,7 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -4990,25 +4990,25 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O64">
         <v>6</v>
@@ -5046,37 +5046,37 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5114,34 +5114,34 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F66">
         <v>4</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I66">
         <v>4</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66">
         <v>4</v>
@@ -5176,40 +5176,40 @@
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -5250,34 +5250,34 @@
         <v>5</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68">
         <v>6</v>
       </c>
       <c r="J68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L68">
         <v>5</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O68">
         <v>6</v>
@@ -5318,34 +5318,34 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K69">
         <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
         <v>4</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5386,31 +5386,31 @@
         <v>3</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70">
         <v>4</v>
@@ -5454,34 +5454,34 @@
         <v>2</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71">
         <v>2</v>
       </c>
       <c r="I71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L71">
         <v>4</v>
       </c>
       <c r="M71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O71">
         <v>6</v>
@@ -5531,22 +5531,22 @@
         <v>1</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>5</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L72">
         <v>5</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N72">
         <v>5</v>
@@ -5587,37 +5587,37 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O73">
         <v>6</v>
@@ -5655,31 +5655,31 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74">
         <v>7</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K74">
         <v>7</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M74">
         <v>7</v>
@@ -5726,34 +5726,34 @@
         <v>4</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5791,10 +5791,10 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -5803,25 +5803,25 @@
         <v>3</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76">
         <v>4</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O76">
         <v>6</v>
@@ -5859,7 +5859,7 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -5868,7 +5868,7 @@
         <v>2</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H77">
         <v>2</v>
@@ -5927,37 +5927,37 @@
         <v>102</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78">
         <v>3</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K78">
         <v>3</v>
       </c>
       <c r="L78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M78">
         <v>3</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O78">
         <v>6</v>
@@ -5995,28 +5995,28 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79">
         <v>3</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J79">
         <v>6</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L79">
         <v>6</v>
@@ -6025,7 +6025,7 @@
         <v>5</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79">
         <v>6</v>
@@ -6069,10 +6069,10 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -6081,19 +6081,19 @@
         <v>7</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K80">
         <v>7</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>6</v>
@@ -6131,37 +6131,37 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81">
         <v>4</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81">
         <v>5</v>
       </c>
       <c r="J81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O81">
         <v>6</v>
@@ -6199,37 +6199,37 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N82">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O82">
         <v>6</v>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,238 +82,238 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
     <t>A_L15</t>
   </si>
   <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L26</t>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
   </si>
   <si>
     <t>A_L11</t>
   </si>
   <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L29</t>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
   </si>
   <si>
     <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L05</t>
   </si>
   <si>
     <t>A_L04</t>
@@ -768,37 +768,37 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -807,19 +807,19 @@
         <v>37</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="V2">
         <v>4</v>
@@ -836,34 +836,34 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>7</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>7</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3">
         <v>7</v>
@@ -872,25 +872,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,34 +904,34 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -940,22 +940,22 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="V4">
         <v>4</v>
@@ -975,19 +975,19 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -996,34 +996,34 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1040,28 +1040,28 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1070,28 +1070,28 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1108,43 +1108,43 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -1153,16 +1153,16 @@
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="T7">
         <v>5</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,16 +1244,16 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -1265,40 +1265,40 @@
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,58 +1312,58 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>4</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
       <c r="T10">
         <v>4</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V10">
         <v>3</v>
@@ -1380,34 +1380,34 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -1416,22 +1416,22 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="T11">
         <v>5</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V11">
         <v>4</v>
@@ -1448,58 +1448,58 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1519,31 +1519,31 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -1552,22 +1552,22 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>3</v>
@@ -1581,46 +1581,46 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1629,16 +1629,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1652,55 +1652,55 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
-      </c>
-      <c r="S15">
-        <v>2.6</v>
+        <v>5</v>
+      </c>
+      <c r="T15">
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V15">
         <v>2</v>
@@ -1717,28 +1717,28 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>4</v>
@@ -1747,31 +1747,31 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>2.1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1785,37 +1785,37 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1827,16 +1827,16 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,10 +1853,10 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -1865,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -1883,31 +1883,31 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,16 +1921,16 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1939,10 +1939,10 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -1957,25 +1957,25 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1989,58 +1989,58 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>2</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2057,61 +2057,61 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <v>4</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,13 +2128,13 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>2</v>
@@ -2146,22 +2146,22 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -2170,13 +2170,13 @@
         <v>4</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,43 +2193,43 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -2238,13 +2238,13 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V23">
         <v>2</v>
@@ -2261,58 +2261,61 @@
         <v>104</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>6.4</v>
+      </c>
+      <c r="T24">
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2326,10 +2329,10 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2344,43 +2347,43 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q25">
         <v>2</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2400,37 +2403,37 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -2439,13 +2442,13 @@
         <v>4</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2462,22 +2465,22 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -2489,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27">
         <v>3</v>
@@ -2498,25 +2501,25 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2530,10 +2533,10 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2545,43 +2548,43 @@
         <v>2</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V28">
         <v>4</v>
@@ -2598,137 +2601,137 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>4</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
         <v>104</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30">
         <v>2</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <v>2</v>
       </c>
       <c r="K30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
@@ -2743,155 +2746,155 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>2</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>4</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V32">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -2900,28 +2903,28 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Q33">
         <v>1</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -2929,46 +2932,46 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>6</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -2983,48 +2986,48 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>6</v>
@@ -3033,10 +3036,10 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3045,45 +3048,45 @@
         <v>47</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>2</v>
@@ -3092,16 +3095,16 @@
         <v>5</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>5</v>
@@ -3110,7 +3113,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3119,57 +3122,57 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N37">
         <v>4</v>
@@ -3178,22 +3181,22 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3201,52 +3204,52 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38">
         <v>5</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -3255,36 +3258,36 @@
         <v>3</v>
       </c>
       <c r="S38">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V38">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3293,10 +3296,10 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>7</v>
@@ -3314,22 +3317,22 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V39">
         <v>4</v>
@@ -3337,78 +3340,78 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F40">
         <v>4</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J40">
         <v>5</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>3</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
@@ -3417,143 +3420,143 @@
         <v>3</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S41">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S42">
-        <v>10.2</v>
+        <v>2.8</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U42">
         <v>13</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -3562,57 +3565,57 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
@@ -3624,52 +3627,52 @@
         <v>2</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44">
         <v>6</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M44">
         <v>5</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="Q44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U44">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V44">
         <v>3</v>
@@ -3677,67 +3680,67 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H45">
         <v>3</v>
       </c>
       <c r="I45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S45">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="V45">
         <v>4</v>
@@ -3745,61 +3748,61 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46">
         <v>3</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <v>3</v>
       </c>
       <c r="S46">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="T46">
         <v>4</v>
@@ -3808,15 +3811,15 @@
         <v>21</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -3825,55 +3828,55 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M47">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>12</v>
+        <v>7.3</v>
       </c>
       <c r="T47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3890,10 +3893,10 @@
         <v>103</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48">
         <v>2</v>
@@ -3902,46 +3905,46 @@
         <v>3</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S48">
-        <v>10.6</v>
+        <v>4.2</v>
       </c>
       <c r="T48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V48">
         <v>3</v>
@@ -3958,16 +3961,16 @@
         <v>102</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -3976,10 +3979,10 @@
         <v>7</v>
       </c>
       <c r="J49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L49">
         <v>7</v>
@@ -3988,28 +3991,25 @@
         <v>7</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>6.7</v>
-      </c>
-      <c r="T49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U49">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V49">
         <v>3</v>
@@ -4026,34 +4026,34 @@
         <v>104</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50">
         <v>5</v>
@@ -4062,25 +4062,25 @@
         <v>6</v>
       </c>
       <c r="P50">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S50">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4094,10 +4094,10 @@
         <v>103</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51">
         <v>2</v>
@@ -4109,46 +4109,46 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4162,55 +4162,55 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U52">
         <v>9</v>
@@ -4230,34 +4230,34 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>4</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L53">
         <v>5</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -4266,22 +4266,22 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S53">
-        <v>5.1</v>
+        <v>8.5</v>
       </c>
       <c r="T53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U53">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V53">
         <v>3</v>
@@ -4298,43 +4298,43 @@
         <v>103</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L54">
         <v>5</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4343,13 +4343,13 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="T54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U54">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4366,61 +4366,61 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55">
         <v>4</v>
       </c>
       <c r="K55">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L55">
         <v>5</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R55">
         <v>3</v>
       </c>
       <c r="S55">
-        <v>10.3</v>
+        <v>7.9</v>
       </c>
       <c r="T55">
+        <v>6</v>
+      </c>
+      <c r="U55">
         <v>8</v>
       </c>
-      <c r="U55">
-        <v>17</v>
-      </c>
       <c r="V55">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:22">
@@ -4434,61 +4434,61 @@
         <v>103</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M56">
         <v>5</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S56">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="T56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U56">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V56">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4502,43 +4502,43 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q57">
         <v>1</v>
@@ -4547,13 +4547,10 @@
         <v>3</v>
       </c>
       <c r="S57">
-        <v>3.3</v>
-      </c>
-      <c r="T57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U57">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4570,34 +4567,34 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L58">
         <v>6</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58">
         <v>7</v>
@@ -4606,25 +4603,25 @@
         <v>6</v>
       </c>
       <c r="P58">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="Q58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R58">
         <v>3</v>
       </c>
       <c r="S58">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U58">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="V58">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4638,61 +4635,61 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S59">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="T59">
         <v>8</v>
       </c>
       <c r="U59">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4706,61 +4703,61 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L60">
         <v>3</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>3</v>
+        <v>11.9</v>
       </c>
       <c r="T60">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U60">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V60">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4774,43 +4771,43 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4819,16 +4816,16 @@
         <v>3</v>
       </c>
       <c r="S61">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V61">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -4842,31 +4839,31 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M62">
         <v>6</v>
@@ -4878,7 +4875,7 @@
         <v>6</v>
       </c>
       <c r="P62">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q62">
         <v>2</v>
@@ -4887,16 +4884,16 @@
         <v>3</v>
       </c>
       <c r="S62">
-        <v>9.4</v>
+        <v>3.2</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U62">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4910,58 +4907,58 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,22 +4975,22 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J64">
         <v>7</v>
@@ -5002,7 +4999,7 @@
         <v>7</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M64">
         <v>7</v>
@@ -5014,25 +5011,25 @@
         <v>6</v>
       </c>
       <c r="P64">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S64">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="T64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="V64">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5049,31 +5046,31 @@
         <v>3</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K65">
         <v>4</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N65">
         <v>2</v>
@@ -5088,19 +5085,19 @@
         <v>1</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>3.6</v>
+        <v>9.1</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="V65">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5117,55 +5114,58 @@
         <v>4</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
+      <c r="P66">
+        <v>33</v>
+      </c>
       <c r="Q66">
         <v>2</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="T66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V66">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5179,61 +5179,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>3</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M67">
         <v>4</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
         <v>3</v>
       </c>
       <c r="S67">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="T67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U67">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,58 +5247,58 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M68">
         <v>4</v>
       </c>
       <c r="N68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
         <v>4</v>
       </c>
       <c r="S68">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U68">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5315,7 +5315,7 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -5324,49 +5324,49 @@
         <v>2</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q69">
         <v>1</v>
       </c>
       <c r="R69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S69">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="T69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U69">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V69">
         <v>4</v>
@@ -5383,34 +5383,34 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G70">
         <v>3</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70">
         <v>4</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N70">
         <v>4</v>
@@ -5419,22 +5419,22 @@
         <v>6</v>
       </c>
       <c r="P70">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S70">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5454,31 +5454,31 @@
         <v>2</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71">
         <v>5</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L71">
         <v>4</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N71">
         <v>4</v>
@@ -5487,22 +5487,22 @@
         <v>6</v>
       </c>
       <c r="P71">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q71">
         <v>1</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="T71">
         <v>3</v>
       </c>
       <c r="U71">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V71">
         <v>3</v>
@@ -5519,61 +5519,61 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72">
         <v>5</v>
       </c>
       <c r="S72">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U72">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V72">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,7 +5587,7 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -5599,22 +5599,22 @@
         <v>1</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K73">
         <v>6</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N73">
         <v>5</v>
@@ -5623,22 +5623,22 @@
         <v>6</v>
       </c>
       <c r="P73">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73">
         <v>4</v>
       </c>
       <c r="S73">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V73">
         <v>3</v>
@@ -5661,31 +5661,31 @@
         <v>3</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5694,22 +5694,22 @@
         <v>44</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S74">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="T74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U74">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5723,58 +5723,58 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M75">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75">
         <v>3</v>
       </c>
       <c r="S75">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U75">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V75">
         <v>3</v>
@@ -5791,58 +5791,58 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="T76">
         <v>3</v>
       </c>
       <c r="U76">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="V76">
         <v>4</v>
@@ -5859,61 +5859,61 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J77">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L77">
         <v>7</v>
       </c>
       <c r="M77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U77">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5927,58 +5927,58 @@
         <v>102</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>3</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K78">
         <v>3</v>
       </c>
       <c r="L78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N78">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
-        <v>5.1</v>
+        <v>8.5</v>
       </c>
       <c r="T78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V78">
         <v>3</v>
@@ -5995,58 +5995,58 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I79">
         <v>4</v>
       </c>
       <c r="J79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="T79">
         <v>5</v>
       </c>
       <c r="U79">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="V79">
         <v>4</v>
@@ -6069,25 +6069,25 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80">
         <v>3</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K80">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M80">
         <v>6</v>
@@ -6099,25 +6099,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
         <v>4</v>
       </c>
       <c r="S80">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U80">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6131,52 +6131,52 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J81">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S81">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="T81">
         <v>7</v>
@@ -6185,7 +6185,7 @@
         <v>10</v>
       </c>
       <c r="V81">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6199,22 +6199,22 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J82">
         <v>5</v>
@@ -6223,37 +6223,37 @@
         <v>4</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q82">
         <v>1</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S82">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T82">
         <v>5</v>
       </c>
       <c r="U82">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V82">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,244 +82,244 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
     <t>A_L18</t>
   </si>
   <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
     <t>A_L07</t>
   </si>
   <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
   </si>
   <si>
     <t>C_L11</t>
   </si>
   <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -768,43 +768,43 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -813,16 +813,16 @@
         <v>3</v>
       </c>
       <c r="S2">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,7 +836,7 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -845,25 +845,25 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>7</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>7</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3">
         <v>7</v>
@@ -872,7 +872,7 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -881,16 +881,16 @@
         <v>3</v>
       </c>
       <c r="S3">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="T3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,13 +904,13 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -919,19 +919,19 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -940,7 +940,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -949,16 +949,16 @@
         <v>4</v>
       </c>
       <c r="S4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -975,55 +975,55 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1043,58 +1043,58 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1108,49 +1108,49 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S7">
         <v>4</v>
@@ -1159,10 +1159,10 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,34 +1244,34 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>4</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9">
         <v>4</v>
@@ -1280,22 +1280,22 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S9">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>6</v>
       </c>
       <c r="U9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V9">
         <v>3</v>
@@ -1315,55 +1315,55 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
         <v>3</v>
       </c>
       <c r="S10">
-        <v>6.9</v>
+        <v>12.9</v>
       </c>
       <c r="T10">
         <v>4</v>
       </c>
       <c r="U10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="V10">
         <v>3</v>
@@ -1380,28 +1380,28 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>4</v>
@@ -1410,31 +1410,31 @@
         <v>4</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U11">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1448,37 +1448,37 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1490,13 +1490,13 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>2.3</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U12">
         <v>14</v>
@@ -1519,40 +1519,40 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>2</v>
@@ -1561,16 +1561,16 @@
         <v>3</v>
       </c>
       <c r="S13">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,37 +1581,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -1620,7 +1620,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1629,16 +1629,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1658,52 +1658,55 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="S15">
+        <v>4.2</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,31 +1720,31 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1753,25 +1756,25 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1785,61 +1788,61 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1853,34 +1856,34 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>7</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -1889,7 +1892,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -1898,10 +1901,10 @@
         <v>3</v>
       </c>
       <c r="S18">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U18">
         <v>19</v>
@@ -1921,7 +1924,7 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1930,34 +1933,34 @@
         <v>2</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>7</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
       <c r="P19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -1966,13 +1969,13 @@
         <v>4</v>
       </c>
       <c r="S19">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="T19">
         <v>4</v>
       </c>
       <c r="U19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="V19">
         <v>3</v>
@@ -1989,22 +1992,22 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2013,28 +2016,28 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2063,55 +2066,55 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S21">
-        <v>2.6</v>
+        <v>15.1</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,55 +2131,55 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>5</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,31 +2196,31 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>7</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2229,25 +2232,25 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23">
         <v>3</v>
       </c>
       <c r="S23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>14</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,37 +2264,37 @@
         <v>104</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
         <v>2</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
       <c r="M24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2300,22 +2303,22 @@
         <v>37</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="V24">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2335,52 +2338,52 @@
         <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q25">
         <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V25">
         <v>3</v>
@@ -2400,31 +2403,31 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -2433,25 +2436,25 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U26">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2465,43 +2468,43 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>4</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q27">
         <v>1</v>
@@ -2510,16 +2513,16 @@
         <v>2</v>
       </c>
       <c r="S27">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2533,7 +2536,7 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -2542,13 +2545,13 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2557,34 +2560,34 @@
         <v>4</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V28">
         <v>4</v>
@@ -2601,37 +2604,37 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2640,140 +2643,140 @@
         <v>45</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="T29">
         <v>4</v>
       </c>
       <c r="U29">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30">
         <v>5</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
         <v>4</v>
       </c>
       <c r="S30">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="Q31">
         <v>1</v>
@@ -2782,24 +2785,24 @@
         <v>3</v>
       </c>
       <c r="S31">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
@@ -2808,66 +2811,66 @@
         <v>2</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>7</v>
       </c>
       <c r="M32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q32">
         <v>2</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>21</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
@@ -2879,52 +2882,52 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q33">
         <v>1</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -2932,19 +2935,19 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -2953,16 +2956,16 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>6</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2971,28 +2974,28 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q34">
         <v>2</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="T34">
         <v>6</v>
       </c>
       <c r="U34">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3000,52 +3003,52 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L35">
         <v>5</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -3054,13 +3057,13 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="T35">
         <v>8</v>
       </c>
       <c r="U35">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="V35">
         <v>4</v>
@@ -3068,135 +3071,135 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>2</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Q36">
         <v>1</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="T36">
         <v>5</v>
       </c>
       <c r="U36">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V36">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>3</v>
       </c>
       <c r="S37">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3204,52 +3207,52 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38">
         <v>2</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -3258,24 +3261,24 @@
         <v>3</v>
       </c>
       <c r="S38">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
@@ -3296,43 +3299,43 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>7</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V39">
         <v>4</v>
@@ -3340,67 +3343,67 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
       <c r="R40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="T40">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3408,67 +3411,67 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H41">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <v>4</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S41">
-        <v>4.6</v>
+        <v>13.7</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V41">
         <v>4</v>
@@ -3476,10 +3479,10 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
@@ -3491,120 +3494,120 @@
         <v>3</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>7</v>
       </c>
       <c r="L42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>5</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S42">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43">
         <v>2</v>
       </c>
       <c r="I43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S43">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V43">
         <v>4</v>
@@ -3612,247 +3615,247 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>3</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>7</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q44">
         <v>2</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="T44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U44">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H45">
         <v>3</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L45">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N45">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>2</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L46">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="Q46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46">
         <v>3</v>
       </c>
       <c r="S46">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K47">
         <v>5</v>
       </c>
       <c r="L47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3861,22 +3864,19 @@
         <v>6</v>
       </c>
       <c r="P47">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47">
         <v>4</v>
       </c>
       <c r="S47">
-        <v>7.3</v>
-      </c>
-      <c r="T47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U47">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3896,55 +3896,55 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J48">
         <v>6</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <v>3</v>
       </c>
       <c r="S48">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U48">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V48">
         <v>3</v>
@@ -3961,34 +3961,34 @@
         <v>102</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J49">
         <v>6</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N49">
         <v>5</v>
@@ -3997,22 +3997,25 @@
         <v>6</v>
       </c>
       <c r="P49">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>6</v>
+        <v>2.9</v>
+      </c>
+      <c r="T49">
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4029,58 +4032,58 @@
         <v>3</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50">
         <v>4</v>
       </c>
       <c r="L50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S50">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4094,19 +4097,19 @@
         <v>103</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>2</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51">
         <v>7</v>
@@ -4115,22 +4118,22 @@
         <v>7</v>
       </c>
       <c r="K51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L51">
         <v>7</v>
       </c>
       <c r="M51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q51">
         <v>1</v>
@@ -4139,13 +4142,13 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="T51">
         <v>4</v>
       </c>
       <c r="U51">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="V51">
         <v>3</v>
@@ -4162,34 +4165,34 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J52">
         <v>6</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N52">
         <v>7</v>
@@ -4198,25 +4201,25 @@
         <v>6</v>
       </c>
       <c r="P52">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q52">
         <v>1</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="T52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4230,34 +4233,34 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53">
         <v>5</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -4266,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S53">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
       <c r="T53">
         <v>6</v>
@@ -4298,28 +4301,28 @@
         <v>103</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J54">
         <v>5</v>
       </c>
       <c r="K54">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -4328,13 +4331,13 @@
         <v>5</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4343,16 +4346,16 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U54">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V54">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4366,31 +4369,31 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I55">
         <v>5</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55">
         <v>5</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55">
         <v>4</v>
@@ -4402,25 +4405,25 @@
         <v>6</v>
       </c>
       <c r="P55">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Q55">
         <v>2</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S55">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="T55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U55">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:22">
@@ -4434,61 +4437,61 @@
         <v>103</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56">
         <v>6</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U56">
         <v>19</v>
       </c>
       <c r="V56">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4502,55 +4505,58 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>3</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M57">
         <v>3</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S57">
-        <v>2</v>
+        <v>8.5</v>
+      </c>
+      <c r="T57">
+        <v>6</v>
       </c>
       <c r="U57">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4567,13 +4573,13 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -4582,46 +4588,43 @@
         <v>3</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58">
         <v>6</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
-      <c r="P58">
-        <v>41</v>
-      </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="T58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U58">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="V58">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4635,61 +4638,61 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="T59">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="V59">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4703,61 +4706,61 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K60">
         <v>5</v>
       </c>
       <c r="L60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="T60">
         <v>8</v>
       </c>
       <c r="U60">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V60">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4768,46 +4771,46 @@
         <v>80</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4816,16 +4819,16 @@
         <v>3</v>
       </c>
       <c r="S61">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U61">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V61">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -4842,31 +4845,31 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
         <v>4</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N62">
         <v>7</v>
@@ -4878,22 +4881,22 @@
         <v>36</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="T62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V62">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4907,61 +4910,61 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K63">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U63">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="V63">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,58 +4978,58 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L64">
         <v>4</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S64">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U64">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V64">
         <v>4</v>
@@ -5043,31 +5046,31 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65">
         <v>4</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65">
         <v>3</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K65">
         <v>4</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M65">
         <v>3</v>
@@ -5079,25 +5082,25 @@
         <v>6</v>
       </c>
       <c r="P65">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5111,61 +5114,61 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G66">
         <v>4</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q66">
         <v>2</v>
       </c>
       <c r="R66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S66">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U66">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5176,37 +5179,37 @@
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67">
         <v>3</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N67">
         <v>5</v>
@@ -5215,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="P67">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q67">
         <v>1</v>
@@ -5224,16 +5227,16 @@
         <v>3</v>
       </c>
       <c r="S67">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="T67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U67">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,34 +5250,34 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N68">
         <v>3</v>
@@ -5283,22 +5286,22 @@
         <v>6</v>
       </c>
       <c r="P68">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q68">
         <v>2</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>8.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="T68">
         <v>7</v>
       </c>
       <c r="U68">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5315,61 +5318,61 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J69">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69">
         <v>3</v>
       </c>
       <c r="S69">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="T69">
         <v>7</v>
       </c>
       <c r="U69">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V69">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5383,61 +5386,61 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="Q70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70">
         <v>4</v>
       </c>
       <c r="S70">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U70">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5451,61 +5454,61 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q71">
         <v>1</v>
       </c>
       <c r="R71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S71">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="T71">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U71">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,31 +5522,31 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72">
         <v>6</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M72">
         <v>5</v>
@@ -5555,25 +5558,25 @@
         <v>6</v>
       </c>
       <c r="P72">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72">
         <v>5</v>
       </c>
       <c r="S72">
-        <v>2.1</v>
+        <v>13.9</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U72">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5590,7 +5593,7 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5599,46 +5602,46 @@
         <v>1</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J73">
         <v>7</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="T73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U73">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V73">
         <v>3</v>
@@ -5658,58 +5661,58 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="T74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U74">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V74">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5726,58 +5729,55 @@
         <v>5</v>
       </c>
       <c r="E75">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75">
         <v>3</v>
       </c>
-      <c r="S75">
-        <v>10.6</v>
-      </c>
       <c r="T75">
         <v>4</v>
       </c>
       <c r="U75">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,58 +5794,58 @@
         <v>2</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76">
         <v>4</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S76">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="T76">
         <v>3</v>
       </c>
       <c r="U76">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V76">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5859,10 +5859,10 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -5880,22 +5880,22 @@
         <v>6</v>
       </c>
       <c r="K77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M77">
         <v>4</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5904,16 +5904,16 @@
         <v>3</v>
       </c>
       <c r="S77">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="T77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U77">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5927,52 +5927,52 @@
         <v>102</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M78">
         <v>5</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S78">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
       <c r="T78">
         <v>6</v>
@@ -5995,43 +5995,43 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J79">
         <v>3</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6040,13 +6040,13 @@
         <v>2</v>
       </c>
       <c r="S79">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V79">
         <v>4</v>
@@ -6063,25 +6063,25 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K80">
         <v>3</v>
@@ -6090,34 +6090,34 @@
         <v>7</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="T80">
         <v>5</v>
       </c>
       <c r="U80">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6131,22 +6131,22 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J81">
         <v>4</v>
@@ -6155,37 +6155,37 @@
         <v>5</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M81">
         <v>5</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S81">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="T81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U81">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V81">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6199,34 +6199,34 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J82">
         <v>5</v>
       </c>
       <c r="K82">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N82">
         <v>7</v>
@@ -6235,25 +6235,25 @@
         <v>6</v>
       </c>
       <c r="P82">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q82">
         <v>1</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S82">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="T82">
         <v>5</v>
       </c>
       <c r="U82">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V82">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,244 +82,244 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
     <t>A_L20</t>
   </si>
   <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L28</t>
   </si>
   <si>
     <t>A</t>
@@ -774,31 +774,31 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -807,19 +807,19 @@
         <v>52</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <v>3</v>
       </c>
       <c r="S2">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="T2">
         <v>5</v>
       </c>
       <c r="U2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V2">
         <v>3</v>
@@ -845,22 +845,22 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -872,25 +872,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
         <v>3</v>
       </c>
       <c r="S3">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,61 +904,61 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
         <v>5</v>
       </c>
       <c r="U4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,55 +972,55 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5">
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>11</v>
@@ -1040,58 +1040,58 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>7.9</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V6">
         <v>4</v>
@@ -1117,52 +1117,52 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1179,31 +1179,31 @@
         <v>6</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -1212,25 +1212,25 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>4</v>
       </c>
       <c r="S8">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,58 +1244,58 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>3</v>
@@ -1315,7 +1315,7 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1324,22 +1324,22 @@
         <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1348,7 +1348,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="Q10">
         <v>2</v>
@@ -1357,16 +1357,16 @@
         <v>3</v>
       </c>
       <c r="S10">
-        <v>12.9</v>
+        <v>5.9</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1380,46 +1380,46 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>4</v>
@@ -1428,10 +1428,10 @@
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V11">
         <v>3</v>
@@ -1448,34 +1448,34 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -1484,25 +1484,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1516,55 +1516,55 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>6</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13">
         <v>3</v>
       </c>
       <c r="S13">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1584,43 +1584,43 @@
         <v>104</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>3</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1629,13 +1629,13 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>3</v>
@@ -1658,13 +1658,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -1676,34 +1676,31 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M15">
         <v>6</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>4.2</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U15">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="V15">
         <v>3</v>
@@ -1720,61 +1717,61 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>3</v>
       </c>
       <c r="S16">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="T16">
         <v>3</v>
       </c>
       <c r="U16">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1788,61 +1785,61 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1856,25 +1853,25 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>6</v>
@@ -1883,31 +1880,31 @@
         <v>4</v>
       </c>
       <c r="M18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q18">
         <v>2</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>12.7</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="V18">
         <v>4</v>
@@ -1927,22 +1924,22 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -1951,7 +1948,7 @@
         <v>3</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1960,22 +1957,22 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>4</v>
       </c>
       <c r="S19">
-        <v>8.9</v>
+        <v>5.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>3</v>
@@ -1992,43 +1989,43 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q20">
         <v>1</v>
@@ -2037,16 +2034,16 @@
         <v>4</v>
       </c>
       <c r="S20">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2063,58 +2060,58 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>6</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>15.1</v>
+        <v>4.9</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2131,25 +2128,25 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L22">
         <v>3</v>
@@ -2158,31 +2155,31 @@
         <v>4</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T22">
+        <v>5</v>
+      </c>
+      <c r="U22">
         <v>8</v>
       </c>
-      <c r="U22">
-        <v>17</v>
-      </c>
       <c r="V22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2196,25 +2193,25 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>4</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2223,34 +2220,34 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <v>3</v>
       </c>
       <c r="S23">
-        <v>4</v>
+        <v>12.9</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V23">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2264,61 +2261,61 @@
         <v>104</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2332,58 +2329,58 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V25">
         <v>3</v>
@@ -2403,10 +2400,10 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2415,46 +2412,46 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M26">
         <v>4</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2468,22 +2465,22 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2492,7 +2489,7 @@
         <v>4</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M27">
         <v>4</v>
@@ -2504,25 +2501,25 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2536,19 +2533,19 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2557,40 +2554,40 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M28">
         <v>4</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2604,34 +2601,34 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -2640,93 +2637,93 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
         <v>103</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>3</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q30">
         <v>2</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="V30">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2740,43 +2737,43 @@
         <v>102</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31">
         <v>4</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q31">
         <v>1</v>
@@ -2785,16 +2782,16 @@
         <v>3</v>
       </c>
       <c r="S31">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2808,61 +2805,61 @@
         <v>104</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M32">
         <v>7</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q32">
         <v>2</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>2.2</v>
+        <v>7.9</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V32">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -2879,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -2888,46 +2885,46 @@
         <v>1</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>7</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -2947,25 +2944,25 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2974,28 +2971,28 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
         <v>4</v>
       </c>
       <c r="S34">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3015,55 +3012,55 @@
         <v>2</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35">
         <v>3</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35">
-        <v>1.7</v>
+        <v>16</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>4</v>
@@ -3080,61 +3077,61 @@
         <v>104</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>3</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36">
         <v>4</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Q36">
         <v>1</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U36">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3148,58 +3145,58 @@
         <v>103</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S37">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="T37">
         <v>5</v>
       </c>
       <c r="U37">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3216,61 +3213,61 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q38">
         <v>2</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V38">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3284,34 +3281,34 @@
         <v>104</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -3320,22 +3317,22 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U39">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V39">
         <v>4</v>
@@ -3352,16 +3349,16 @@
         <v>102</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40">
         <v>2</v>
@@ -3373,16 +3370,16 @@
         <v>6</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M40">
         <v>5</v>
       </c>
       <c r="N40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3391,19 +3388,19 @@
         <v>38</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
         <v>3</v>
       </c>
       <c r="S40">
-        <v>2.4</v>
+        <v>8.1</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U40">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3420,61 +3417,61 @@
         <v>104</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>13.7</v>
+        <v>6.8</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3491,13 +3488,13 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -3506,10 +3503,10 @@
         <v>5</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -3518,31 +3515,31 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R42">
         <v>3</v>
       </c>
       <c r="S42">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3556,10 +3553,10 @@
         <v>103</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>3</v>
@@ -3571,46 +3568,46 @@
         <v>2</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U43">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3627,19 +3624,19 @@
         <v>2</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J44">
         <v>7</v>
@@ -3648,37 +3645,37 @@
         <v>7</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44">
         <v>3</v>
       </c>
       <c r="S44">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V44">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3692,16 +3689,16 @@
         <v>104</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -3710,43 +3707,40 @@
         <v>5</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L45">
         <v>6</v>
       </c>
       <c r="M45">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
-      <c r="P45">
-        <v>32</v>
-      </c>
       <c r="Q45">
         <v>1</v>
       </c>
       <c r="R45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S45">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3760,25 +3754,25 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I46">
         <v>5</v>
       </c>
       <c r="J46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K46">
         <v>7</v>
@@ -3790,31 +3784,31 @@
         <v>7</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S46">
-        <v>5.3</v>
+        <v>10.2</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3828,34 +3822,34 @@
         <v>104</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K47">
         <v>5</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3864,19 +3858,19 @@
         <v>6</v>
       </c>
       <c r="P47">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
         <v>4</v>
       </c>
-      <c r="S47">
-        <v>7</v>
+      <c r="T47">
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3893,37 +3887,37 @@
         <v>103</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M48">
         <v>4</v>
       </c>
       <c r="N48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -3938,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="S48">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V48">
         <v>3</v>
@@ -3964,55 +3958,55 @@
         <v>1</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>5</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K49">
         <v>7</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4029,58 +4023,58 @@
         <v>104</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S50">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="T50">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V50">
         <v>4</v>
@@ -4097,43 +4091,43 @@
         <v>103</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>2</v>
       </c>
       <c r="I51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Q51">
         <v>1</v>
@@ -4142,16 +4136,16 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="T51">
         <v>4</v>
       </c>
       <c r="U51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4165,58 +4159,58 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>2</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q52">
         <v>1</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V52">
         <v>4</v>
@@ -4233,19 +4227,19 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>5</v>
@@ -4257,19 +4251,19 @@
         <v>5</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4278,16 +4272,16 @@
         <v>2</v>
       </c>
       <c r="S53">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4301,28 +4295,28 @@
         <v>103</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J54">
         <v>5</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -4331,31 +4325,31 @@
         <v>5</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="T54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U54">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="V54">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4369,58 +4363,58 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L55">
         <v>4</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T55">
         <v>4</v>
       </c>
       <c r="U55">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4437,61 +4431,61 @@
         <v>103</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56">
         <v>6</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K56">
         <v>6</v>
       </c>
       <c r="L56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Q56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="T56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U56">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V56">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4508,55 +4502,55 @@
         <v>1</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I57">
         <v>4</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Q57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="T57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U57">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4576,55 +4570,58 @@
         <v>1</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
+      <c r="P58">
+        <v>41</v>
+      </c>
       <c r="Q58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S58">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U58">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V58">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4638,61 +4635,61 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59">
         <v>4</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U59">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4706,61 +4703,61 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I60">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J60">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L60">
         <v>6</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q60">
         <v>1</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S60">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="T60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U60">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="V60">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4774,58 +4771,58 @@
         <v>104</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K61">
         <v>5</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="Q61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S61">
-        <v>2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U61">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4845,55 +4842,55 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62">
         <v>4</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U62">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4910,61 +4907,61 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="T63">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="V63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4978,34 +4975,34 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K64">
         <v>6</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N64">
         <v>4</v>
@@ -5023,16 +5020,16 @@
         <v>4</v>
       </c>
       <c r="S64">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="T64">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U64">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="V64">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5046,16 +5043,16 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65">
         <v>3</v>
@@ -5064,43 +5061,43 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L65">
         <v>2</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,58 +5111,58 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L66">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V66">
         <v>4</v>
@@ -5179,37 +5176,37 @@
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G67">
         <v>3</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N67">
         <v>5</v>
@@ -5218,25 +5215,25 @@
         <v>6</v>
       </c>
       <c r="P67">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q67">
         <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S67">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="T67">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U67">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5250,61 +5247,61 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68">
         <v>3</v>
       </c>
       <c r="S68">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="T68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V68">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5318,43 +5315,43 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69">
         <v>4</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I69">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K69">
         <v>4</v>
       </c>
       <c r="L69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -5363,16 +5360,16 @@
         <v>3</v>
       </c>
       <c r="S69">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="T69">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U69">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V69">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5386,61 +5383,61 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="T70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5454,16 +5451,16 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -5472,25 +5469,25 @@
         <v>6</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M71">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5499,16 +5496,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="T71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U71">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="V71">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5522,37 +5519,37 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O72">
         <v>6</v>
@@ -5564,16 +5561,16 @@
         <v>1</v>
       </c>
       <c r="R72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S72">
-        <v>13.9</v>
+        <v>10.3</v>
       </c>
       <c r="T72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U72">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="V72">
         <v>4</v>
@@ -5593,10 +5590,10 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -5605,46 +5602,46 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J73">
         <v>7</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L73">
         <v>7</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R73">
         <v>3</v>
       </c>
       <c r="S73">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5661,58 +5658,58 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R74">
         <v>3</v>
       </c>
       <c r="S74">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="T74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U74">
         <v>10</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5726,58 +5723,61 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N75">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="S75">
+        <v>1.1</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U75">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5791,28 +5791,28 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L76">
         <v>5</v>
@@ -5821,31 +5821,31 @@
         <v>5</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U76">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V76">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5862,55 +5862,55 @@
         <v>2</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>3</v>
       </c>
       <c r="I77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L77">
         <v>5</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="T77">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U77">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5927,7 +5927,7 @@
         <v>102</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78">
         <v>2</v>
@@ -5939,31 +5939,31 @@
         <v>4</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I78">
         <v>1</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L78">
         <v>5</v>
       </c>
       <c r="M78">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q78">
         <v>1</v>
@@ -5972,16 +5972,16 @@
         <v>2</v>
       </c>
       <c r="S78">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U78">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V78">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,58 +5995,58 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79">
         <v>4</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J79">
         <v>3</v>
       </c>
       <c r="K79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="T79">
         <v>6</v>
       </c>
       <c r="U79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V79">
         <v>4</v>
@@ -6063,13 +6063,13 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80">
         <v>2</v>
@@ -6078,28 +6078,28 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J80">
         <v>4</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q80">
         <v>2</v>
@@ -6108,16 +6108,16 @@
         <v>3</v>
       </c>
       <c r="S80">
-        <v>4.7</v>
+        <v>15.7</v>
       </c>
       <c r="T80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U80">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,31 +6134,31 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L81">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N81">
         <v>7</v>
@@ -6167,7 +6167,7 @@
         <v>6</v>
       </c>
       <c r="P81">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="Q81">
         <v>1</v>
@@ -6176,16 +6176,16 @@
         <v>3</v>
       </c>
       <c r="S81">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="T81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U81">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V81">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6202,7 +6202,7 @@
         <v>1</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -6214,43 +6214,43 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M82">
         <v>7</v>
       </c>
       <c r="N82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q82">
         <v>1</v>
       </c>
       <c r="R82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S82">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U82">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="V82">
         <v>3</v>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,235 +82,235 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L07</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L21</t>
   </si>
   <si>
     <t>B_L11</t>
   </si>
   <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
     <t>B_L07</t>
   </si>
   <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
   </si>
   <si>
     <t>A_L12</t>
   </si>
   <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
     <t>B_L19</t>
   </si>
   <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
+    <t>A_L22</t>
   </si>
   <si>
     <t>A_L24</t>
   </si>
   <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
     <t>A_L01</t>
   </si>
   <si>
-    <t>C_L23</t>
+    <t>C_L24</t>
   </si>
   <si>
     <t>C_L06</t>
@@ -319,7 +319,7 @@
     <t>A_L04</t>
   </si>
   <si>
-    <t>A_L26</t>
+    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -768,61 +768,61 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>5</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>5</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,13 +836,13 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -851,16 +851,16 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -872,25 +872,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,58 +904,58 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
         <v>4</v>
@@ -972,58 +972,58 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1040,61 +1040,61 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1117,34 +1117,34 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -1153,16 +1153,16 @@
         <v>3</v>
       </c>
       <c r="S7">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,37 +1244,37 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1283,22 +1283,22 @@
         <v>31</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
         <v>5</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,16 +1312,16 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>4</v>
@@ -1330,43 +1330,43 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1380,7 +1380,7 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1389,52 +1389,52 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1448,34 +1448,34 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>4</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -1484,25 +1484,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1516,61 +1516,61 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1584,25 +1584,25 @@
         <v>104</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>4</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1614,13 +1614,13 @@
         <v>2</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1629,16 +1629,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1652,34 +1652,34 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -1688,22 +1688,22 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,19 +1717,19 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1738,22 +1738,22 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1762,16 +1762,16 @@
         <v>3</v>
       </c>
       <c r="S16">
-        <v>5.6</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1785,58 +1785,58 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,34 +1853,34 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1889,25 +1889,25 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18">
-        <v>12.7</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,34 +1921,34 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1957,25 +1957,25 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1992,58 +1992,58 @@
         <v>3</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2057,61 +2057,61 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,10 +2128,10 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2140,46 +2140,46 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>4</v>
       </c>
       <c r="S22">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V22">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2193,22 +2193,22 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>4</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2217,19 +2217,19 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23">
         <v>5</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -2238,16 +2238,16 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>12.9</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,22 +2261,22 @@
         <v>104</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2285,37 +2285,34 @@
         <v>4</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S24">
-        <v>1.9</v>
-      </c>
-      <c r="T24">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2338,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -2347,13 +2344,13 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>7</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2365,25 +2362,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2400,55 +2397,55 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>4</v>
       </c>
       <c r="S26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2468,28 +2465,28 @@
         <v>2</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27">
         <v>4</v>
@@ -2501,25 +2498,25 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>3</v>
       </c>
       <c r="S27">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V27">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2533,19 +2530,19 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2554,40 +2551,40 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2601,31 +2598,31 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2637,93 +2634,93 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
         <v>6</v>
       </c>
       <c r="U29">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>7</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>6</v>
+      </c>
+      <c r="P30">
         <v>49</v>
       </c>
-      <c r="B30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>3</v>
-      </c>
-      <c r="J30">
-        <v>4</v>
-      </c>
-      <c r="K30">
-        <v>6</v>
-      </c>
-      <c r="L30">
-        <v>7</v>
-      </c>
-      <c r="M30">
-        <v>6</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30">
-        <v>6</v>
-      </c>
-      <c r="P30">
-        <v>55</v>
-      </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <v>3</v>
       </c>
       <c r="S30">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2740,55 +2737,55 @@
         <v>3</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31">
         <v>3</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="V31">
         <v>4</v>
@@ -2808,34 +2805,34 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2844,19 +2841,19 @@
         <v>37</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="T32">
         <v>4</v>
       </c>
       <c r="U32">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V32">
         <v>4</v>
@@ -2873,58 +2870,58 @@
         <v>102</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>7</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S33">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -2944,31 +2941,31 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>5</v>
@@ -2977,25 +2974,25 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3015,37 +3012,37 @@
         <v>5</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -3054,16 +3051,16 @@
         <v>4</v>
       </c>
       <c r="S35">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3077,43 +3074,43 @@
         <v>104</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36">
         <v>4</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3122,13 +3119,13 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V36">
         <v>3</v>
@@ -3145,58 +3142,58 @@
         <v>103</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37">
         <v>3</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S37">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3213,61 +3210,61 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>4</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q38">
         <v>2</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3281,58 +3278,58 @@
         <v>104</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>7</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>4</v>
@@ -3349,43 +3346,43 @@
         <v>102</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40">
         <v>2</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q40">
         <v>2</v>
@@ -3394,16 +3391,16 @@
         <v>3</v>
       </c>
       <c r="S40">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3420,55 +3417,55 @@
         <v>3</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>4</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>4</v>
       </c>
       <c r="M41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V41">
         <v>3</v>
@@ -3485,61 +3482,61 @@
         <v>104</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42">
         <v>5</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S42">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="T42">
         <v>7</v>
       </c>
       <c r="U42">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3559,55 +3556,55 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43">
         <v>6</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S43">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3621,19 +3618,19 @@
         <v>104</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I44">
         <v>6</v>
@@ -3642,22 +3639,22 @@
         <v>7</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3666,13 +3663,13 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V44">
         <v>3</v>
@@ -3692,55 +3689,58 @@
         <v>2</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
+      <c r="P45">
+        <v>55</v>
+      </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
         <v>5</v>
       </c>
       <c r="S45">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V45">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3754,61 +3754,61 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>10.2</v>
+        <v>5.7</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3825,34 +3825,34 @@
         <v>2</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47">
         <v>5</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -3861,16 +3861,19 @@
         <v>34</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="S47">
+        <v>12</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U47">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3887,19 +3890,19 @@
         <v>103</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
         <v>4</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I48">
         <v>4</v>
@@ -3908,13 +3911,13 @@
         <v>4</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -3923,22 +3926,22 @@
         <v>6</v>
       </c>
       <c r="P48">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q48">
         <v>1</v>
       </c>
       <c r="R48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S48">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U48">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V48">
         <v>3</v>
@@ -3955,37 +3958,37 @@
         <v>102</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -4000,16 +4003,16 @@
         <v>4</v>
       </c>
       <c r="S49">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="T49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4023,58 +4026,58 @@
         <v>104</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I50">
         <v>5</v>
       </c>
       <c r="J50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
         <v>4</v>
       </c>
       <c r="S50">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="V50">
         <v>4</v>
@@ -4091,61 +4094,61 @@
         <v>103</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M51">
         <v>4</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V51">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4165,55 +4168,55 @@
         <v>2</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
         <v>2</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4227,28 +4230,28 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -4257,31 +4260,31 @@
         <v>4</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S53">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T53">
         <v>5</v>
       </c>
       <c r="U53">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V53">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4295,58 +4298,58 @@
         <v>103</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J54">
         <v>5</v>
       </c>
       <c r="K54">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L54">
         <v>5</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U54">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4363,34 +4366,34 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55">
         <v>4</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N55">
         <v>5</v>
@@ -4399,7 +4402,7 @@
         <v>6</v>
       </c>
       <c r="P55">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4408,13 +4411,13 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>3</v>
+        <v>10.3</v>
       </c>
       <c r="T55">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U55">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4431,61 +4434,61 @@
         <v>103</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E56">
         <v>4</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L56">
         <v>7</v>
       </c>
       <c r="M56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U56">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V56">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4499,43 +4502,43 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G57">
         <v>4</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J57">
         <v>4</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Q57">
         <v>1</v>
@@ -4544,13 +4547,13 @@
         <v>3</v>
       </c>
       <c r="S57">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U57">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4567,61 +4570,61 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="T58">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U58">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V58">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4635,22 +4638,22 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J59">
         <v>7</v>
@@ -4659,37 +4662,37 @@
         <v>7</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="T59">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U59">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V59">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4706,58 +4709,58 @@
         <v>3</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U60">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V60">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4774,31 +4777,31 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N61">
         <v>5</v>
@@ -4807,22 +4810,22 @@
         <v>6</v>
       </c>
       <c r="P61">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="T61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,58 +4842,58 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N62">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62">
         <v>3</v>
       </c>
       <c r="S62">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="T62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4910,55 +4913,55 @@
         <v>1</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63">
         <v>2</v>
       </c>
       <c r="I63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="T63">
         <v>4</v>
       </c>
       <c r="U63">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4975,61 +4978,61 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>5</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="T64">
         <v>6</v>
       </c>
       <c r="U64">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5043,61 +5046,61 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65">
         <v>3</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S65">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="V65">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5111,58 +5114,55 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
-      <c r="P66">
-        <v>32</v>
-      </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U66">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V66">
         <v>4</v>
@@ -5179,61 +5179,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="T67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,61 +5247,61 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L68">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V68">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5315,61 +5315,61 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="T69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U69">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5383,58 +5383,58 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70">
         <v>4</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <v>5</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L70">
         <v>5</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70">
         <v>3</v>
       </c>
       <c r="S70">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U70">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5451,43 +5451,43 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5496,16 +5496,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="T71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U71">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,61 +5519,61 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>5</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S72">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="T72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,25 +5587,25 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K73">
         <v>6</v>
@@ -5614,34 +5614,34 @@
         <v>7</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q73">
         <v>2</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S73">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5658,58 +5658,58 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R74">
         <v>3</v>
       </c>
       <c r="S74">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="T74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U74">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5723,58 +5723,58 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75">
         <v>5</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V75">
         <v>3</v>
@@ -5791,13 +5791,13 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76">
         <v>2</v>
@@ -5809,13 +5809,13 @@
         <v>4</v>
       </c>
       <c r="J76">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M76">
         <v>5</v>
@@ -5827,25 +5827,25 @@
         <v>6</v>
       </c>
       <c r="P76">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5859,58 +5859,58 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q77">
         <v>2</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S77">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="T77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5927,61 +5927,61 @@
         <v>102</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78">
         <v>3</v>
       </c>
       <c r="G78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L78">
         <v>5</v>
       </c>
       <c r="M78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T78">
         <v>5</v>
       </c>
       <c r="U78">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,7 +5995,7 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E79">
         <v>4</v>
@@ -6004,49 +6004,49 @@
         <v>4</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>2</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L79">
         <v>5</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Q79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R79">
         <v>3</v>
       </c>
       <c r="S79">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="T79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V79">
         <v>4</v>
@@ -6072,13 +6072,13 @@
         <v>1</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J80">
         <v>4</v>
@@ -6099,25 +6099,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Q80">
         <v>2</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U80">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,19 +6134,19 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J81">
         <v>7</v>
@@ -6167,25 +6167,25 @@
         <v>6</v>
       </c>
       <c r="P81">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="T81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U81">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V81">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6199,58 +6199,58 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q82">
         <v>1</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S82">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U82">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="V82">
         <v>3</v>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -82,244 +82,244 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
     <t>A_L20</t>
   </si>
   <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -768,61 +768,61 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>5</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
         <v>5</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,61 +836,61 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,61 +904,61 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -975,58 +975,58 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1040,37 +1040,37 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1082,16 +1082,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1108,61 +1108,61 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,7 +1176,7 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1185,25 +1185,25 @@
         <v>4</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -1212,25 +1212,25 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,31 +1244,31 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M9">
         <v>4</v>
@@ -1280,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1289,16 +1289,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1315,58 +1315,55 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
-      <c r="P10">
-        <v>43</v>
-      </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1386,55 +1383,55 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1448,31 +1445,31 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>4</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -1484,22 +1481,22 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1528,49 +1525,49 @@
         <v>2</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,64 +1578,64 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>3</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1652,28 +1649,28 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1682,28 +1679,31 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>7.4</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,25 +1717,25 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -1744,31 +1744,31 @@
         <v>4</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1788,55 +1788,55 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,34 +1853,34 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>5</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1889,7 +1889,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1898,16 +1898,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,7 +1921,7 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -1930,25 +1930,25 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>5</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1960,19 +1960,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1989,58 +1989,58 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2066,52 +2066,52 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>2</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,34 +2125,34 @@
         <v>103</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2161,22 +2161,22 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2193,61 +2193,61 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>4</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,22 +2261,22 @@
         <v>104</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2285,13 +2285,13 @@
         <v>4</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2306,13 +2306,16 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="T24">
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2329,10 +2332,10 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2341,46 +2344,46 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2394,7 +2397,7 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2406,22 +2409,22 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>5</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>6</v>
@@ -2430,22 +2433,22 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2462,58 +2465,58 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M27">
         <v>4</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2530,61 +2533,61 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2595,303 +2598,303 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29">
         <v>3</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K29">
         <v>5</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>4</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q31">
         <v>2</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>4</v>
       </c>
       <c r="M32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>16</v>
       </c>
       <c r="V32">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -2900,13 +2903,13 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2915,30 +2918,30 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2947,34 +2950,34 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2983,7 +2986,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -2992,125 +2995,125 @@
         <v>12</v>
       </c>
       <c r="V34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>5</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3119,81 +3122,81 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3201,67 +3204,67 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <v>4</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38">
         <v>3</v>
       </c>
       <c r="S38">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3269,22 +3272,22 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3296,51 +3299,51 @@
         <v>6</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
@@ -3349,191 +3352,191 @@
         <v>2</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>4</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>7</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S42">
-        <v>10.2</v>
+        <v>3.3</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V42">
         <v>4</v>
@@ -3541,78 +3544,78 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>6</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
@@ -3630,31 +3633,31 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3663,10 +3666,10 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
         <v>13</v>
@@ -3677,28 +3680,28 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>6</v>
@@ -3707,90 +3710,90 @@
         <v>4</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N45">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3799,134 +3802,134 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47">
         <v>4</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M47">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="T47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>103</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I48">
         <v>4</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -3935,92 +3938,92 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>10.6</v>
+        <v>3.6</v>
       </c>
       <c r="T48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U48">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>4</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U49">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -4035,78 +4038,78 @@
         <v>1</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>5</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M50">
         <v>4</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S50">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I51">
         <v>3</v>
@@ -4115,22 +4118,22 @@
         <v>3</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4139,149 +4142,149 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U51">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U52">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S53">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T53">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V53">
         <v>3</v>
@@ -4289,10 +4292,10 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
@@ -4301,7 +4304,7 @@
         <v>2</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -4322,19 +4325,19 @@
         <v>6</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4343,13 +4346,13 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="T54">
         <v>6</v>
       </c>
       <c r="U54">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4357,10 +4360,10 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -4372,120 +4375,120 @@
         <v>1</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S55">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="T55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U55">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V55">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E56">
         <v>4</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G56">
         <v>5</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="T56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V56">
         <v>3</v>
@@ -4502,58 +4505,58 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S57">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="T57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U57">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4570,58 +4573,58 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U58">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4641,19 +4644,19 @@
         <v>2</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J59">
         <v>7</v>
@@ -4674,25 +4677,25 @@
         <v>6</v>
       </c>
       <c r="P59">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S59">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="T59">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4709,10 +4712,10 @@
         <v>3</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -4721,43 +4724,43 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L60">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T60">
         <v>6</v>
       </c>
       <c r="U60">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>4</v>
@@ -4771,46 +4774,46 @@
         <v>80</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4818,14 +4821,11 @@
       <c r="R61">
         <v>3</v>
       </c>
-      <c r="S61">
-        <v>3.9</v>
-      </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4842,58 +4842,58 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4910,58 +4910,58 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,34 +4978,34 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J64">
         <v>7</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N64">
         <v>7</v>
@@ -5014,25 +5014,25 @@
         <v>6</v>
       </c>
       <c r="P64">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S64">
-        <v>6.4</v>
+        <v>9.9</v>
       </c>
       <c r="T64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V64">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5046,61 +5046,61 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H65">
         <v>3</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M65">
         <v>4</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V65">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,58 +5114,61 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
+      <c r="P66">
+        <v>37</v>
+      </c>
       <c r="Q66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V66">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5179,61 +5182,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q67">
         <v>2</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S67">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U67">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,58 +5250,58 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J68">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S68">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5318,22 +5321,22 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69">
         <v>3</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K69">
         <v>5</v>
@@ -5345,31 +5348,31 @@
         <v>3</v>
       </c>
       <c r="N69">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S69">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T69">
         <v>6</v>
       </c>
       <c r="U69">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V69">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5386,31 +5389,31 @@
         <v>2</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K70">
         <v>6</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N70">
         <v>5</v>
@@ -5419,22 +5422,22 @@
         <v>6</v>
       </c>
       <c r="P70">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S70">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5451,43 +5454,43 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5496,16 +5499,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="T71">
         <v>3</v>
       </c>
       <c r="U71">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5522,25 +5525,25 @@
         <v>2</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L72">
         <v>5</v>
@@ -5549,31 +5552,31 @@
         <v>5</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S72">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U72">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V72">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,10 +5590,10 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5599,49 +5602,49 @@
         <v>1</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,34 +5658,34 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I74">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N74">
         <v>7</v>
@@ -5691,7 +5694,7 @@
         <v>6</v>
       </c>
       <c r="P74">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q74">
         <v>2</v>
@@ -5700,16 +5703,16 @@
         <v>3</v>
       </c>
       <c r="S74">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="T74">
         <v>5</v>
       </c>
       <c r="U74">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5723,61 +5726,61 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G75">
         <v>2</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M75">
         <v>7</v>
       </c>
       <c r="N75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S75">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U75">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5791,58 +5794,58 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76">
         <v>2</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U76">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V76">
         <v>4</v>
@@ -5859,61 +5862,61 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S77">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T77">
         <v>5</v>
       </c>
       <c r="U77">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5930,55 +5933,55 @@
         <v>4</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I78">
         <v>4</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K78">
         <v>3</v>
       </c>
       <c r="L78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M78">
         <v>3</v>
       </c>
       <c r="N78">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S78">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T78">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V78">
         <v>3</v>
@@ -5995,34 +5998,34 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I79">
         <v>3</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N79">
         <v>3</v>
@@ -6031,7 +6034,7 @@
         <v>6</v>
       </c>
       <c r="P79">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6040,16 +6043,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U79">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,28 +6066,28 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G80">
         <v>3</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L80">
         <v>6</v>
@@ -6093,31 +6096,31 @@
         <v>6</v>
       </c>
       <c r="N80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="T80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U80">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6131,16 +6134,16 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -6149,43 +6152,43 @@
         <v>5</v>
       </c>
       <c r="J81">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S81">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="T81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U81">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V81">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6199,52 +6202,49 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H82">
         <v>2</v>
       </c>
       <c r="I82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J82">
         <v>5</v>
       </c>
       <c r="K82">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R82">
-        <v>2</v>
-      </c>
-      <c r="S82">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T82">
         <v>5</v>
@@ -6253,7 +6253,7 @@
         <v>22</v>
       </c>
       <c r="V82">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -85,241 +85,241 @@
     <t>A_L13</t>
   </si>
   <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
     <t>A_L18</t>
   </si>
   <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
   </si>
   <si>
     <t>C_L20</t>
   </si>
   <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
     <t>C_L26</t>
   </si>
   <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -768,58 +768,58 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <v>5</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>8.9</v>
       </c>
       <c r="T2">
         <v>5</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V2">
         <v>3</v>
@@ -839,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -848,49 +848,49 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,34 +904,34 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -940,7 +940,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -949,16 +949,16 @@
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>20</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,61 +972,61 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1040,61 +1040,61 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
         <v>8</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1108,16 +1108,16 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1129,37 +1129,37 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="V7">
         <v>4</v>
@@ -1176,58 +1176,58 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q8">
         <v>2</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>4</v>
@@ -1244,61 +1244,61 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>3</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,28 +1312,28 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>6</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>4</v>
@@ -1342,25 +1342,28 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>49</v>
+      </c>
       <c r="Q10">
         <v>2</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V10">
         <v>4</v>
@@ -1377,34 +1380,34 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>4</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>4</v>
@@ -1413,25 +1416,25 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>21</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,46 +1448,46 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -1493,13 +1496,13 @@
         <v>2.9</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1513,61 +1516,61 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,19 +1584,19 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>3</v>
@@ -1602,10 +1605,10 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M14">
         <v>3</v>
@@ -1620,22 +1623,22 @@
         <v>47</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,43 +1652,43 @@
         <v>104</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -1694,16 +1697,13 @@
         <v>3</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,31 +1717,31 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -1753,25 +1753,25 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="T16">
         <v>3</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1788,55 +1788,55 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
         <v>3</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,58 +1853,58 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>12.7</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V18">
         <v>4</v>
@@ -1927,13 +1927,13 @@
         <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -1948,16 +1948,16 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
       <c r="P19">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -1966,16 +1966,16 @@
         <v>4</v>
       </c>
       <c r="S19">
+        <v>5.9</v>
+      </c>
+      <c r="T19">
         <v>8</v>
       </c>
-      <c r="T19">
-        <v>4</v>
-      </c>
       <c r="U19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1992,58 +1992,58 @@
         <v>2</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
         <v>4</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2057,58 +2057,58 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
       </c>
       <c r="J21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V21">
         <v>4</v>
@@ -2125,7 +2125,7 @@
         <v>103</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2137,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -2152,7 +2152,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2161,25 +2161,25 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q22">
         <v>2</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2193,34 +2193,34 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>5</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K23">
         <v>7</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>7</v>
@@ -2229,22 +2229,22 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V23">
         <v>3</v>
@@ -2264,19 +2264,19 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2285,37 +2285,37 @@
         <v>4</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
       </c>
       <c r="N24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2332,40 +2332,40 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q25">
         <v>1</v>
@@ -2374,13 +2374,13 @@
         <v>3</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>6.5</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V25">
         <v>3</v>
@@ -2397,13 +2397,13 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2415,40 +2415,40 @@
         <v>5</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="T26">
         <v>5</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,61 +2465,61 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2533,13 +2533,13 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -2548,43 +2548,43 @@
         <v>2</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>6</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V28">
         <v>3</v>
@@ -2598,46 +2598,46 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -2646,13 +2646,13 @@
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="V29">
         <v>4</v>
@@ -2660,40 +2660,40 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
         <v>103</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K30">
         <v>6</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>6</v>
@@ -2705,131 +2705,131 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>102</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31">
         <v>4</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31">
         <v>3</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
         <v>3</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32">
         <v>2</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -2841,45 +2841,45 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
         <v>3</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
         <v>102</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2891,13 +2891,13 @@
         <v>7</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>7</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -2909,90 +2909,90 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3000,105 +3000,105 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>5</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>16</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>10</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L36">
         <v>4</v>
@@ -3107,13 +3107,13 @@
         <v>4</v>
       </c>
       <c r="N36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3122,30 +3122,30 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
         <v>103</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -3154,49 +3154,49 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37">
         <v>4</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="Q37">
         <v>1</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3204,120 +3204,120 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38">
         <v>4</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V38">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39">
         <v>6</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q39">
         <v>1</v>
@@ -3326,33 +3326,33 @@
         <v>3</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
         <v>102</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3364,43 +3364,43 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3408,16 +3408,16 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -3426,60 +3426,60 @@
         <v>3</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L41">
         <v>4</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <v>5</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
@@ -3491,87 +3491,87 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L42">
         <v>6</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43">
         <v>6</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43">
         <v>7</v>
@@ -3583,81 +3583,81 @@
         <v>7</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="Q43">
         <v>2</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3666,13 +3666,13 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="T44">
         <v>6</v>
       </c>
       <c r="U44">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V44">
         <v>3</v>
@@ -3680,34 +3680,34 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K45">
         <v>7</v>
@@ -3719,96 +3719,93 @@
         <v>6</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
-      <c r="P45">
-        <v>35</v>
-      </c>
       <c r="Q45">
         <v>1</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S46">
-        <v>6.4</v>
+        <v>10.2</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="V46">
         <v>4</v>
@@ -3816,176 +3813,173 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K47">
         <v>5</v>
       </c>
       <c r="L47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>2</v>
-      </c>
-      <c r="S47">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="T47">
         <v>5</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
         <v>103</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48">
         <v>3</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q48">
         <v>1</v>
       </c>
       <c r="R48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49">
         <v>7</v>
@@ -3997,22 +3991,22 @@
         <v>6</v>
       </c>
       <c r="P49">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4020,102 +4014,102 @@
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50">
         <v>6</v>
       </c>
       <c r="L50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M50">
         <v>4</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q50">
         <v>2</v>
       </c>
       <c r="R50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U50">
         <v>18</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K51">
         <v>4</v>
@@ -4124,96 +4118,96 @@
         <v>3</v>
       </c>
       <c r="M51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U51">
         <v>9</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J52">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M52">
         <v>7</v>
       </c>
       <c r="N52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
         <v>4</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U52">
         <v>16</v>
@@ -4224,10 +4218,10 @@
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
@@ -4236,28 +4230,28 @@
         <v>3</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G53">
         <v>4</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>5</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53">
         <v>4</v>
@@ -4269,7 +4263,7 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4278,81 +4272,81 @@
         <v>2</v>
       </c>
       <c r="S53">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="T53">
+        <v>5</v>
+      </c>
+      <c r="U53">
         <v>8</v>
       </c>
-      <c r="U53">
-        <v>18</v>
-      </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J54">
         <v>5</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="T54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U54">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4360,138 +4354,138 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>7.3</v>
+        <v>3</v>
       </c>
       <c r="T55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U55">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>4</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H56">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I56">
         <v>6</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K56">
         <v>6</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U56">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="V56">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4505,58 +4499,58 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J57">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="T57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U57">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4573,31 +4567,31 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M58">
         <v>4</v>
@@ -4609,25 +4603,25 @@
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S58">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U58">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V58">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4641,19 +4635,19 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I59">
         <v>6</v>
@@ -4665,34 +4659,34 @@
         <v>7</v>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U59">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="V59">
         <v>4</v>
@@ -4709,34 +4703,34 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N60">
         <v>6</v>
@@ -4745,25 +4739,25 @@
         <v>6</v>
       </c>
       <c r="P60">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S60">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="T60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V60">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4777,55 +4771,58 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J61">
         <v>5</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="S61">
+        <v>9.800000000000001</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U61">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4842,10 +4839,10 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -4854,43 +4851,43 @@
         <v>3</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K62">
         <v>5</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M62">
         <v>2</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>10.6</v>
+        <v>4.1</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U62">
         <v>14</v>
@@ -4910,43 +4907,43 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63">
         <v>3</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63">
         <v>4</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q63">
         <v>1</v>
@@ -4955,13 +4952,13 @@
         <v>3</v>
       </c>
       <c r="S63">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,43 +4975,43 @@
         <v>104</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H64">
         <v>4</v>
       </c>
       <c r="I64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q64">
         <v>1</v>
@@ -5023,10 +5020,10 @@
         <v>4</v>
       </c>
       <c r="S64">
-        <v>9.9</v>
+        <v>2.4</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U64">
         <v>22</v>
@@ -5046,16 +5043,16 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H65">
         <v>3</v>
@@ -5064,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K65">
         <v>2</v>
@@ -5073,10 +5070,10 @@
         <v>3</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5088,19 +5085,19 @@
         <v>1</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5114,28 +5111,28 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L66">
         <v>6</v>
@@ -5144,13 +5141,13 @@
         <v>6</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q66">
         <v>1</v>
@@ -5159,16 +5156,16 @@
         <v>3</v>
       </c>
       <c r="S66">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5182,58 +5179,58 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S67">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U67">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="V67">
         <v>4</v>
@@ -5250,28 +5247,28 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F68">
         <v>5</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H68">
         <v>3</v>
       </c>
       <c r="I68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L68">
         <v>2</v>
@@ -5280,31 +5277,31 @@
         <v>2</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="T68">
         <v>5</v>
       </c>
       <c r="U68">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V68">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5318,43 +5315,43 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L69">
         <v>5</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -5363,13 +5360,13 @@
         <v>3</v>
       </c>
       <c r="S69">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="T69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U69">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="V69">
         <v>3</v>
@@ -5389,16 +5386,16 @@
         <v>2</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F70">
         <v>2</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <v>6</v>
@@ -5407,37 +5404,37 @@
         <v>7</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M70">
         <v>7</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="T70">
         <v>5</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5454,43 +5451,43 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F71">
         <v>2</v>
       </c>
       <c r="G71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M71">
         <v>6</v>
       </c>
       <c r="N71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5499,13 +5496,13 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="T71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U71">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V71">
         <v>2</v>
@@ -5522,13 +5519,13 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72">
         <v>2</v>
@@ -5537,28 +5534,28 @@
         <v>3</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q72">
         <v>1</v>
@@ -5567,16 +5564,16 @@
         <v>3</v>
       </c>
       <c r="S72">
-        <v>4.6</v>
+        <v>10.3</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U72">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5590,37 +5587,37 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O73">
         <v>6</v>
@@ -5629,22 +5626,22 @@
         <v>39</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R73">
         <v>3</v>
       </c>
       <c r="S73">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V73">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5658,28 +5655,28 @@
         <v>102</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J74">
         <v>5</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L74">
         <v>5</v>
@@ -5688,28 +5685,28 @@
         <v>5</v>
       </c>
       <c r="N74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R74">
         <v>3</v>
       </c>
       <c r="S74">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="T74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U74">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="V74">
         <v>3</v>
@@ -5726,61 +5723,61 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G75">
         <v>2</v>
       </c>
       <c r="H75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K75">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M75">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S75">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U75">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,31 +5791,31 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J76">
         <v>5</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76">
         <v>4</v>
@@ -5830,7 +5827,7 @@
         <v>6</v>
       </c>
       <c r="P76">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q76">
         <v>2</v>
@@ -5839,16 +5836,16 @@
         <v>3</v>
       </c>
       <c r="S76">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U76">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="V76">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5862,61 +5859,61 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>2</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S77">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U77">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5930,43 +5927,43 @@
         <v>102</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q78">
         <v>1</v>
@@ -5975,16 +5972,16 @@
         <v>2</v>
       </c>
       <c r="S78">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="T78">
+        <v>5</v>
+      </c>
+      <c r="U78">
         <v>8</v>
       </c>
-      <c r="U78">
-        <v>18</v>
-      </c>
       <c r="V78">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -6001,58 +5998,58 @@
         <v>5</v>
       </c>
       <c r="E79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J79">
         <v>3</v>
       </c>
       <c r="K79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R79">
         <v>3</v>
       </c>
       <c r="S79">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="T79">
         <v>6</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V79">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6066,61 +6063,61 @@
         <v>104</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80">
         <v>3</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L80">
         <v>6</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
         <v>3</v>
       </c>
       <c r="S80">
-        <v>3.1</v>
+        <v>15.7</v>
       </c>
       <c r="T80">
         <v>7</v>
       </c>
       <c r="U80">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,43 +6131,43 @@
         <v>102</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q81">
         <v>1</v>
@@ -6179,16 +6176,16 @@
         <v>3</v>
       </c>
       <c r="S81">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="T81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U81">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V81">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6202,58 +6199,61 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82">
         <v>2</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K82">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N82">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R82">
         <v>4</v>
       </c>
+      <c r="S82">
+        <v>5.4</v>
+      </c>
       <c r="T82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U82">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="V82">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -97,223 +97,223 @@
     <t>B_L06</t>
   </si>
   <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
     <t>C_L19</t>
   </si>
   <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>X_L99</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
   </si>
   <si>
     <t>B_L22</t>
   </si>
   <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L14</t>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L02</t>
   </si>
   <si>
     <t>C_L07</t>
   </si>
   <si>
-    <t>B_L05</t>
-  </si>
-  <si>
     <t>C_L12</t>
   </si>
   <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L27</t>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L22</t>
   </si>
   <si>
     <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>X_L99</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L04</t>
   </si>
   <si>
     <t>A_L04</t>
@@ -771,13 +771,13 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -786,16 +786,16 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -804,25 +804,25 @@
         <v>6</v>
       </c>
       <c r="P2">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -836,13 +836,13 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -851,19 +851,19 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3">
         <v>7</v>
@@ -872,25 +872,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -904,58 +904,58 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
         <v>4</v>
@@ -972,58 +972,58 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1040,61 +1040,61 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1117,34 +1117,34 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -1153,16 +1153,16 @@
         <v>3</v>
       </c>
       <c r="S7">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,61 +1176,61 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1244,37 +1244,37 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1283,22 +1283,22 @@
         <v>31</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
         <v>5</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,61 +1312,61 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1380,28 +1380,28 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>3</v>
@@ -1410,31 +1410,31 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1448,16 +1448,16 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1466,16 +1466,16 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>4</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1484,25 +1484,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1516,61 +1516,61 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>5</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1584,28 +1584,28 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>3</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>4</v>
@@ -1614,13 +1614,13 @@
         <v>3</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1629,16 +1629,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,37 +1649,37 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>3</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -1688,22 +1688,22 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1720,16 +1720,16 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1738,22 +1738,22 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1762,16 +1762,16 @@
         <v>3</v>
       </c>
       <c r="S16">
-        <v>5.6</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1788,55 +1788,55 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,13 +1853,13 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1868,46 +1868,46 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>6</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18">
-        <v>12.7</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1921,34 +1921,34 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>7</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>7</v>
@@ -1957,25 +1957,25 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1989,61 +1989,61 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2057,61 +2057,61 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,28 +2128,28 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2161,25 +2161,25 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>4</v>
       </c>
       <c r="S22">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V22">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2193,43 +2193,43 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -2238,16 +2238,16 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>12.9</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,61 +2261,58 @@
         <v>104</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S24">
-        <v>1.9</v>
-      </c>
-      <c r="T24">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2338,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -2347,13 +2344,13 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>7</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2365,25 +2362,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2400,55 +2397,55 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>4</v>
       </c>
       <c r="S26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2468,58 +2465,58 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M27">
         <v>5</v>
       </c>
       <c r="N27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>3</v>
       </c>
       <c r="S27">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V27">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2533,61 +2530,61 @@
         <v>102</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>2</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2601,31 +2598,31 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2637,93 +2634,93 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
         <v>6</v>
       </c>
       <c r="U29">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
         <v>103</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>3</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <v>3</v>
       </c>
       <c r="S30">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2740,55 +2737,55 @@
         <v>3</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I31">
         <v>5</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31">
         <v>3</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="V31">
         <v>4</v>
@@ -2808,34 +2805,34 @@
         <v>2</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2844,19 +2841,19 @@
         <v>37</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="T32">
         <v>4</v>
       </c>
       <c r="U32">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V32">
         <v>4</v>
@@ -2879,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2897,7 +2894,7 @@
         <v>7</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -2909,22 +2906,22 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S33">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -2944,31 +2941,31 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>5</v>
@@ -2977,25 +2974,25 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3012,40 +3009,40 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>7</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -3054,16 +3051,16 @@
         <v>4</v>
       </c>
       <c r="S35">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3077,43 +3074,43 @@
         <v>104</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q36">
         <v>1</v>
@@ -3122,13 +3119,13 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V36">
         <v>3</v>
@@ -3145,34 +3142,34 @@
         <v>103</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37">
         <v>3</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N37">
         <v>3</v>
@@ -3181,22 +3178,22 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S37">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V37">
         <v>3</v>
@@ -3213,61 +3210,61 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q38">
         <v>2</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3284,55 +3281,55 @@
         <v>4</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39">
         <v>3</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>4</v>
@@ -3355,37 +3352,37 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40">
         <v>6</v>
       </c>
       <c r="J40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q40">
         <v>2</v>
@@ -3394,16 +3391,16 @@
         <v>3</v>
       </c>
       <c r="S40">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3420,25 +3417,25 @@
         <v>3</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>4</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>4</v>
@@ -3447,28 +3444,28 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V41">
         <v>3</v>
@@ -3485,7 +3482,7 @@
         <v>104</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -3497,7 +3494,7 @@
         <v>2</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42">
         <v>6</v>
@@ -3506,40 +3503,40 @@
         <v>5</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S42">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="T42">
         <v>7</v>
       </c>
       <c r="U42">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3559,55 +3556,55 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43">
         <v>6</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S43">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3624,40 +3621,40 @@
         <v>2</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3666,13 +3663,13 @@
         <v>3</v>
       </c>
       <c r="S44">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V44">
         <v>3</v>
@@ -3692,10 +3689,10 @@
         <v>2</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -3704,43 +3701,46 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
+      <c r="P45">
+        <v>55</v>
+      </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
         <v>5</v>
       </c>
       <c r="S45">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="T45">
         <v>5</v>
       </c>
       <c r="U45">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V45">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3754,7 +3754,7 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -3766,49 +3766,49 @@
         <v>2</v>
       </c>
       <c r="H46">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K46">
         <v>6</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>10.2</v>
+        <v>5.7</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3822,34 +3822,34 @@
         <v>104</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J47">
         <v>5</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3861,16 +3861,19 @@
         <v>34</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="S47">
+        <v>12</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U47">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3887,34 +3890,34 @@
         <v>103</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
         <v>4</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G48">
         <v>3</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48">
         <v>4</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -3923,22 +3926,22 @@
         <v>6</v>
       </c>
       <c r="P48">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q48">
         <v>1</v>
       </c>
       <c r="R48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S48">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U48">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V48">
         <v>3</v>
@@ -3958,28 +3961,28 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M49">
         <v>7</v>
@@ -4000,16 +4003,16 @@
         <v>4</v>
       </c>
       <c r="S49">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="T49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4023,58 +4026,58 @@
         <v>104</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M50">
         <v>4</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
         <v>4</v>
       </c>
       <c r="S50">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="V50">
         <v>4</v>
@@ -4091,13 +4094,13 @@
         <v>103</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -4109,43 +4112,43 @@
         <v>4</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M51">
         <v>5</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="S51">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V51">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4162,58 +4165,58 @@
         <v>1</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4227,28 +4230,28 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -4257,31 +4260,31 @@
         <v>4</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S53">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T53">
         <v>5</v>
       </c>
       <c r="U53">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V53">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4298,55 +4301,55 @@
         <v>3</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G54">
         <v>3</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L54">
         <v>5</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U54">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4363,34 +4366,34 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55">
         <v>4</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N55">
         <v>5</v>
@@ -4399,7 +4402,7 @@
         <v>6</v>
       </c>
       <c r="P55">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4408,13 +4411,13 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>3</v>
+        <v>10.3</v>
       </c>
       <c r="T55">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U55">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4431,61 +4434,61 @@
         <v>103</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E56">
         <v>4</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L56">
         <v>7</v>
       </c>
       <c r="M56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U56">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V56">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4502,40 +4505,40 @@
         <v>3</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F57">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I57">
         <v>2</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Q57">
         <v>1</v>
@@ -4544,13 +4547,13 @@
         <v>3</v>
       </c>
       <c r="S57">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U57">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4567,61 +4570,61 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L58">
         <v>6</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="T58">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U58">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V58">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4635,10 +4638,10 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4647,10 +4650,10 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J59">
         <v>7</v>
@@ -4659,37 +4662,37 @@
         <v>7</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="T59">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U59">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V59">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4706,58 +4709,58 @@
         <v>4</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U60">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V60">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4771,58 +4774,58 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61">
         <v>3</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M61">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="T61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,58 +4842,58 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N62">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62">
         <v>3</v>
       </c>
       <c r="S62">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="T62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V62">
         <v>3</v>
@@ -4910,55 +4913,55 @@
         <v>2</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L63">
         <v>4</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="T63">
         <v>4</v>
       </c>
       <c r="U63">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V63">
         <v>3</v>
@@ -4978,58 +4981,58 @@
         <v>2</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="T64">
         <v>6</v>
       </c>
       <c r="U64">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5043,61 +5046,61 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H65">
         <v>3</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S65">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="V65">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5111,19 +5114,19 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F66">
         <v>4</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I66">
         <v>4</v>
@@ -5132,37 +5135,34 @@
         <v>4</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
-      <c r="P66">
-        <v>32</v>
-      </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U66">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V66">
         <v>4</v>
@@ -5179,61 +5179,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M67">
         <v>4</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="T67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,61 +5247,61 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68">
         <v>5</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V68">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5315,61 +5315,61 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="T69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U69">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5386,55 +5386,55 @@
         <v>2</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H70">
         <v>2</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70">
         <v>3</v>
       </c>
       <c r="S70">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U70">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -5451,43 +5451,43 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5496,16 +5496,16 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="T71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U71">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,61 +5519,61 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>5</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S72">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="T72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,25 +5587,25 @@
         <v>104</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I73">
         <v>1</v>
       </c>
       <c r="J73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K73">
         <v>2</v>
@@ -5614,34 +5614,34 @@
         <v>3</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q73">
         <v>2</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S73">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5658,58 +5658,58 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R74">
         <v>3</v>
       </c>
       <c r="S74">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="T74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U74">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5723,10 +5723,10 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5738,43 +5738,43 @@
         <v>2</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V75">
         <v>3</v>
@@ -5791,61 +5791,61 @@
         <v>102</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E76">
         <v>2</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K76">
         <v>2</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q76">
         <v>2</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5859,31 +5859,31 @@
         <v>102</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77">
         <v>2</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H77">
         <v>2</v>
       </c>
       <c r="I77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J77">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M77">
         <v>6</v>
@@ -5895,22 +5895,22 @@
         <v>6</v>
       </c>
       <c r="P77">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q77">
         <v>2</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S77">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="T77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5927,61 +5927,61 @@
         <v>102</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78">
         <v>3</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L78">
         <v>5</v>
       </c>
       <c r="M78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T78">
         <v>5</v>
       </c>
       <c r="U78">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,34 +5995,34 @@
         <v>104</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
         <v>5</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K79">
         <v>4</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N79">
         <v>5</v>
@@ -6031,22 +6031,22 @@
         <v>6</v>
       </c>
       <c r="P79">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Q79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R79">
         <v>3</v>
       </c>
       <c r="S79">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="T79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V79">
         <v>4</v>
@@ -6072,13 +6072,13 @@
         <v>1</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J80">
         <v>4</v>
@@ -6090,7 +6090,7 @@
         <v>6</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N80">
         <v>6</v>
@@ -6099,25 +6099,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Q80">
         <v>2</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U80">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6134,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -6143,10 +6143,10 @@
         <v>4</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J81">
         <v>7</v>
@@ -6167,25 +6167,25 @@
         <v>6</v>
       </c>
       <c r="P81">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
       <c r="R81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="T81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U81">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V81">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6199,31 +6199,31 @@
         <v>102</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M82">
         <v>5</v>
@@ -6235,22 +6235,22 @@
         <v>6</v>
       </c>
       <c r="P82">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q82">
         <v>1</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S82">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U82">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="V82">
         <v>3</v>

--- a/data/T3_leader_raw.xlsx
+++ b/data/T3_leader_raw.xlsx
@@ -768,37 +768,37 @@
         <v>102</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -836,37 +836,37 @@
         <v>102</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>6</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -907,34 +907,34 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -972,37 +972,37 @@
         <v>103</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1040,37 +1040,37 @@
         <v>103</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1108,37 +1108,37 @@
         <v>104</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1176,37 +1176,37 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1244,19 +1244,19 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>4</v>
@@ -1268,13 +1268,13 @@
         <v>4</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1312,10 +1312,10 @@
         <v>102</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -1327,16 +1327,16 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>4</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M10">
         <v>4</v>
@@ -1380,31 +1380,31 @@
         <v>103</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>4</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H11">
         <v>4</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>5</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1448,10 +1448,10 @@
         <v>103</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1460,19 +1460,19 @@
         <v>2</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1519,16 +1519,16 @@
         <v>3</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -1537,16 +1537,16 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1584,37 +1584,37 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>3</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1652,31 +1652,31 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15">
         <v>4</v>
@@ -1717,28 +1717,28 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <v>4</v>
@@ -1788,34 +1788,34 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1853,37 +1853,37 @@
         <v>102</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1921,22 +1921,22 @@
         <v>104</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -1945,13 +1945,13 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1989,37 +1989,37 @@
         <v>102</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <v>2</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2057,34 +2057,34 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21">
         <v>5</v>
@@ -2125,34 +2125,34 @@
         <v>103</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>5</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2193,13 +2193,13 @@
         <v>104</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2208,13 +2208,13 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -2264,34 +2264,34 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2326,37 +2326,37 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2394,19 +2394,19 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26">
         <v>4</v>
@@ -2415,16 +2415,16 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2462,31 +2462,31 @@
         <v>104</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2533,16 +2533,16 @@
         <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -2551,13 +2551,13 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -2598,37 +2598,37 @@
         <v>103</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L29">
         <v>4</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2666,37 +2666,37 @@
         <v>103</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>2</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>3</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O30">
         <v>6</v>
@@ -2734,22 +2734,22 @@
         <v>102</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J31">
         <v>4</v>
@@ -2758,13 +2758,13 @@
         <v>4</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2802,37 +2802,37 @@
         <v>104</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32">
         <v>3</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2870,37 +2870,37 @@
         <v>102</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -2941,34 +2941,34 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J34">
         <v>5</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3006,37 +3006,37 @@
         <v>103</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>5</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3074,37 +3074,37 @@
         <v>104</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36">
         <v>4</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3142,37 +3142,37 @@
         <v>103</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
         <v>2</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -3210,37 +3210,37 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>5</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3278,37 +3278,37 @@
         <v>104</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39">
         <v>3</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39">
         <v>3</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L39">
         <v>3</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3346,10 +3346,10 @@
         <v>102</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -3361,22 +3361,22 @@
         <v>3</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3414,37 +3414,37 @@
         <v>104</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3482,37 +3482,37 @@
         <v>104</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
         <v>2</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>6</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3550,37 +3550,37 @@
         <v>103</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>2</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43">
         <v>6</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3621,34 +3621,34 @@
         <v>2</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>2</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>5</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L44">
         <v>5</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O44">
         <v>6</v>
@@ -3686,34 +3686,34 @@
         <v>104</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N45">
         <v>3</v>
@@ -3754,37 +3754,37 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
         <v>2</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O46">
         <v>6</v>
@@ -3822,37 +3822,37 @@
         <v>104</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47">
         <v>3</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47">
         <v>4</v>
       </c>
       <c r="L47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -3893,31 +3893,31 @@
         <v>2</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L48">
         <v>5</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -3958,37 +3958,37 @@
         <v>102</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49">
         <v>2</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -4026,19 +4026,19 @@
         <v>104</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50">
         <v>4</v>
@@ -4047,16 +4047,16 @@
         <v>4</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -4094,37 +4094,37 @@
         <v>103</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>2</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K51">
         <v>6</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O51">
         <v>6</v>
@@ -4162,37 +4162,37 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52">
         <v>2</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -4304,16 +4304,16 @@
         <v>2</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54">
         <v>3</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J54">
         <v>4</v>
@@ -4322,13 +4322,13 @@
         <v>5</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54">
         <v>4</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4366,16 +4366,16 @@
         <v>103</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>2</v>
@@ -4387,16 +4387,16 @@
         <v>4</v>
       </c>
       <c r="K55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
@@ -4434,37 +4434,37 @@
         <v>103</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O56">
         <v>6</v>
@@ -4502,37 +4502,37 @@
         <v>103</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M57">
         <v>6</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
@@ -4570,37 +4570,37 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58">
         <v>3</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O58">
         <v>6</v>
@@ -4641,7 +4641,7 @@
         <v>2</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4650,25 +4650,25 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M59">
         <v>6</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4706,37 +4706,37 @@
         <v>104</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60">
         <v>3</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O60">
         <v>6</v>
@@ -4774,10 +4774,10 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -4789,19 +4789,19 @@
         <v>3</v>
       </c>
       <c r="I61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N61">
         <v>5</v>
@@ -4842,37 +4842,37 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K62">
         <v>3</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4910,37 +4910,37 @@
         <v>104</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4981,34 +4981,34 @@
         <v>2</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
         <v>2</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
@@ -5046,13 +5046,13 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65">
         <v>4</v>
@@ -5061,22 +5061,22 @@
         <v>3</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J65">
         <v>4</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M65">
         <v>4</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5114,34 +5114,34 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G66">
         <v>2</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L66">
         <v>5</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N66">
         <v>5</v>
@@ -5179,37 +5179,37 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J67">
         <v>5</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -5247,37 +5247,37 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E68">
         <v>4</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J68">
         <v>4</v>
       </c>
       <c r="K68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
@@ -5318,22 +5318,22 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K69">
         <v>5</v>
@@ -5342,10 +5342,10 @@
         <v>6</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N69">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5383,37 +5383,37 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
@@ -5451,34 +5451,34 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71">
         <v>4</v>
       </c>
       <c r="K71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N71">
         <v>4</v>
@@ -5519,34 +5519,34 @@
         <v>103</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I72">